--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="军火榜" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'军火榜'!$A$2:$V$62</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -61,6 +61,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -109,6 +114,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -476,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -506,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-02 · 共 22 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-09 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -625,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>subsy/skill-cabinet</t>
+          <t>multica-ai/andrej-karpathy-skills</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>328</v>
+        <v>211865</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1148</v>
+        <v>6591.3</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Skill 展示柜
-【依据】skill-cabinet</t>
+          <t>改进 Claude Code 行为的 CLAUDE.md 文件
+【原文】A single CLAUDE.md file to improve Claude Code behavior, derived from Andrej Karpathy's observations on LLM coding pitfalls.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -647,12 +655,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -662,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/subsy/skill-cabinet</t>
+          <t>https://github.com/multica-ai/andrej-karpathy-skills</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -671,18 +679,14 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>164</v>
+        <v>941.62</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>JavaScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr"/>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -696,20 +700,20 @@
       <c r="P3" s="6" t="inlineStr"/>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
+        <v>225</v>
+      </c>
+      <c r="T3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" s="3" t="n">
-        <v>1</v>
-      </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
           <t>category</t>
@@ -717,36 +721,37 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
+          <t>skill in:name,description stars:&gt;50000</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>jub0t/Concat</t>
+          <t>Player-YN/PawWork_ZhuaZhua</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>1056</v>
+        <v>2277</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>924</v>
+        <v>1328.2</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>提供免费且开源的视频编辑替代品
-【原文】Free &amp; Open-Source CapCut replacement. (formerly WolfCut)</t>
+          <t>Paw Work - Chrome浏览器选择优先的Web代理
+【原文】Paw Work - selection-first web agent for Chrome: select on the live page, describe the outcome, take away an editable office file. BYOK, sandboxed, no server.
+【依据】topics: ai-agent, browser-agent, chrome-extension, llm</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -761,7 +766,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jub0t/Concat</t>
+          <t>https://github.com/Player-YN/PawWork_ZhuaZhua</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -770,16 +775,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>132</v>
+        <v>189.75</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MPL-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -794,21 +799,21 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>audio-processor, auto-caption, automation, capcut, capcut-alternative, content-creation, cross-platform, desktop-app, ffmpeg, free-video-editor, non-linear-editor, offline-first</t>
+          <t>ai-agent, browser-agent, byok, chrome-extension, llm, pptx, tldraw, univer</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -820,36 +825,36 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:content-creation stars:&gt;1000 pushed:&gt;2026-06-04</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>liyue-aigc/seedance-2-5-video-director</t>
+          <t>bytedance/deer-flow</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>254</v>
+        <v>82135</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>118.5</v>
+        <v>1173.3</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>Seedance 2.5 视频导演 Skill，提供视频提示词、脚本等功能
-【原文】Seedance 2.5 视频导演 Skill：提示词、脚本、诊断、人物锁定、续写、编辑、转场与首次使用指导</t>
+          <t>开源长周期 SuperAgent 框架，用于研究和创建
+【原文】An open-source long-horizon SuperAgent harness that researches, codes, and creates. With the help of sandboxes, memories, tools, skill, subagents and message gateway, it handles different levels of tasks that could take minutes to hours.</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/技能包/架构参考/可部署服务</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -864,7 +869,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/liyue-aigc/seedance-2-5-video-director</t>
+          <t>https://github.com/bytedance/deer-flow</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -873,7 +878,7 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>16.93</v>
+        <v>167.62</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
@@ -897,52 +902,52 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>ai-video, codex-skill, dreamina, seedance, video-prompt</t>
+          <t>agent, agentic, agentic-framework, agentic-workflow, ai, ai-agents, deep-research, harness, langchain, langgraph, langmanus, llm</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>15</v>
+        <v>490</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-04</t>
+          <t>skill in:name,description stars:&gt;50000</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>sindresorhus/awesome-nodejs</t>
+          <t>genspark-ai/genoffice</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>66678</v>
+        <v>6304</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>105.2</v>
+        <v>1103.2</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供 Node.js 包和资源的列表
-【原文】:zap: Delightful Node.js packages and resources [BECAUSE OF TOO MUCH SPAM AND LOW-QUALITY SUBMISSIONS, SUBMISSIONS ARE PAUSED UNTIL JULY]</t>
+          <t>提供类似 Microsoft Office 的 AI 办公软件替代品。
+【原文】Free, open-source alternative to Microsoft Office with built-in AI agents — Word (.docx), Excel (.xlsx), PowerPoint (.pptx), PDF and Markdown editing for macOS, Windows &amp; Linux.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -952,7 +957,7 @@
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>可部署服务/代码库</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -967,7 +972,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sindresorhus/awesome-nodejs</t>
+          <t>https://github.com/genspark-ai/genoffice</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -976,14 +981,18 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>15.03</v>
+        <v>157.6</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -996,62 +1005,62 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, javascript, list, node, nodejs</t>
+          <t>agent, agentic, ai, ai-agent, ai-agents, ai-office, docx, excel, markdown-editor, microsoft-office, office, office-agent</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2014-07-11</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>4436</v>
+        <v>40</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>21st-dev/magic-mcp</t>
+          <t>Vincentwei1021/video-shotcraft</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>5775</v>
+        <v>7902</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>72.2</v>
+        <v>1063.7</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>提供类似于 v0 的功能，但集成在 Cursor / Claude Code / Windsurf 中
-【原文】It's like v0, but in your Cursor / Claude Code / Windsurf: search 10,000+ React/Tailwind components, generate new UI with AI, and publish your own — right from your editor. Magic MCP is now the 21st MCP; this package keeps old configs working. Setup: 21st.dev/mcp</t>
+          <t>为 Claude Code &amp; Codex 提供AI视频技能，制作产品视频
+【原文】AI video skill for Claude Code &amp; Codex — cinematic product videos with Remotion: 152 shot recipe cards, 209 motion previews, a production-ready template</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1066,7 +1075,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/21st-dev/magic-mcp</t>
+          <t>https://github.com/Vincentwei1021/video-shotcraft</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1075,11 +1084,11 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>10.31</v>
+        <v>151.96</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>ISC</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
@@ -1099,67 +1108,66 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>21st, claude, cursor, mcp, model-context-protocol, react, tailwindcss, ui-components</t>
+          <t>agent-skills, ai-agents, ai-video, claude-code, claude-code-skills, claude-skills, codex, motion-design, motion-graphics, product-video, promo-video, remotion</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>560</v>
+        <v>52</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>steven2358/awesome-generative-ai</t>
+          <t>yang0/handraw-style</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>12552</v>
+        <v>604</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>62.2</v>
+        <v>1057</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供现代生成式人工智能项目和服务的精选列表
-【原文】A curated list of modern Generative Artificial Intelligence projects and services</t>
+          <t>提供手绘风格编号画廊与双语提示词 Skill</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1169,7 +1177,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/steven2358/awesome-generative-ai</t>
+          <t>https://github.com/yang0/handraw-style</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1178,14 +1186,18 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>8.880000000000001</v>
+        <v>151</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>HTML</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1196,54 +1208,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>ai, artificial-intelligence, awesome, awesome-list, generative-ai, generative-art, large-language-models, llm</t>
-        </is>
-      </c>
+      <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>1413</v>
+        <v>4</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>edoardottt/awesome-hacker-search-engines</t>
+          <t>MDX-Tom/gpt-instruct</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>11117</v>
+        <v>7940</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>50.7</v>
+        <v>926.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>收集渗透测试、漏洞评估、红蓝队操作、赏金猎人等领域的搜索引擎列表
-【原文】A curated list of awesome search engines useful during Penetration testing, Vulnerability assessments, Red/Blue Team operations, Bug Bounty and more</t>
+          <t>提供针对 gpt 系列的 Codex 破甲提示词与测试包
+【原文】A Codex jailbreak prompt and test pack for gpt. 针对 gpt 系列的 Codex 破甲提示词与测试包。</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1268,7 +1276,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/edoardottt/awesome-hacker-search-engines</t>
+          <t>https://github.com/MDX-Tom/gpt-instruct</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1277,7 +1285,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>7.24</v>
+        <v>132.33</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1286,7 +1294,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -1299,54 +1307,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>awesome, awesome-list, awesome-lists, bugbounty, cve, dns, exploit, hacking, hacking-tools, hacktoberfest, osint, osint-tool</t>
-        </is>
-      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2022-06-20</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>1535</v>
+        <v>60</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>Rzna-5559/Mrite</t>
+          <t>EvoLinkAI/awesome-gpt-image-2-API-and-Prompts</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>445</v>
+        <v>17139</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>36.7</v>
+        <v>833.1</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>内置 Skill 的数模智能体
-【原文】全网最强数模智能体内置Skill</t>
+          <t>提供 GPT-Image-2 API 和提示词
+【原文】GPT-Image-2 API and Prompts</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1356,12 +1360,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1371,7 +1375,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Rzna-5559/Mrite</t>
+          <t>https://github.com/EvoLinkAI/awesome-gpt-image-2-API-and-Prompts</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1380,16 +1384,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>5.24</v>
+        <v>119.02</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>CC0-1.0</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>TeX</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1402,55 +1406,59 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P10" s="6" t="inlineStr"/>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>ai-art, api, awesome-list, awesome-lists, chatgpt, creative-tools, generative-ai, gpt-image-2, gpt-image-2-api, gpt-image-2-prompts, gptimage2, image-generation</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-04-18</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>85</v>
+        <v>144</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>budtmo/docker-android</t>
+          <t>hacksider/Deep-Live-Cam</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>15799</v>
+        <v>96578</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>31.2</v>
+        <v>625.4</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>提供 Android 在 Docker 中的解决方案，支持视频录制和 MCP 服务器
-【原文】Android in docker solution with noVNC supported, video recording and mcp server</t>
+          <t>实现实时面部交换和一键视频深度伪造
+【原文】real time face swap and one-click video deepfake with only a single image</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1458,9 +1466,9 @@
           <t>可部署服务</t>
         </is>
       </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1470,7 +1478,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/budtmo/docker-android</t>
+          <t>https://github.com/hacksider/Deep-Live-Cam</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1479,11 +1487,11 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>4.46</v>
+        <v>89.34</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1503,62 +1511,62 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>android, android-emulator, aws, azure, cloud, docker, docker-android, emulator, gcp, genymotion, jenkins, kubernetes</t>
+          <t>ai, ai-deep-fake, ai-face, ai-webcam, artificial-intelligence, deep-fake, deepfake, deepfake-webcam, faceswap, fake-webcam, gan, real-time-deepfake</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2016-12-22</t>
+          <t>2023-09-24</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>3541</v>
+        <v>1081</v>
       </c>
       <c r="T11" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-08-03</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>scaccogatto/okf-skills</t>
+          <t>unslothai/unsloth</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>353</v>
+        <v>75948</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>30.9</v>
+        <v>523.8</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>Claude Code 工具包，用于创建、维护和验证 Open Knowledge Format 包
-【原文】The OKF toolkit for Claude Code — author, maintain, validate &amp; visualize Open Knowledge Format bundles. Plugin, agent skills, and a GitHub Action.</t>
+          <t>提供本地 UI 运行和训练 LLMs 和扩散模型。
+【原文】Local UI to run and train LLMs and diffusion models. Supports GGUF, MLX, Qwen3.8, DeepSeek-V4, MiniMax-H3, Gemma 4, FLUX and more.</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1573,7 +1581,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/scaccogatto/okf-skills</t>
+          <t>https://github.com/unslothai/unsloth</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1582,11 +1590,11 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>4.41</v>
+        <v>74.83</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1606,21 +1614,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, claude-code, claude-code-plugin, developer-tools, knowledge-graph, knowledge-management, llm-tools, markdown, mcp, okf, open-knowledge-format</t>
+          <t>agent, ai, chatgpt, deepseek, fine-tuning, gemma, image-generation, llama, llm, llms, openai, python</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2023-11-29</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>80</v>
+        <v>1015</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1632,41 +1640,40 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ZeKaiNie/universal-examprep-skill</t>
+          <t>yilujian/easy-writing</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>277</v>
+        <v>506</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>27.7</v>
+        <v>393.5</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Agent Skill 的考试冲刺教练功能
-【原文】Last-night exam-cram coach as a Claude Agent Skill: turns your slides, notes and past papers into a chaptered knowledge base + quiz bank, teaches only what's in your materials, and never fabricates (measured 100% out-of-scope abstention). Bilingual EN/中文 — the 期末极速备考 skill.</t>
+          <t>纯本地、开源的 AI 网文写作桌面软件</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包/代码库</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1676,7 +1683,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ZeKaiNie/universal-examprep-skill</t>
+          <t>https://github.com/yilujian/easy-writing</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1685,16 +1692,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>3.96</v>
+        <v>56.22</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1709,62 +1716,62 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, ai-tutor, anthropic, anti-hallucination, claude, claude-code, claude-skill, cram, edtech, education, exam-prep, llm</t>
+          <t>ai-writing, ai-writing-assistant, byok, creative-writing, desktop-app, local-first, novel-writing, openai-compatible, tauri, vue3, web-novel, writing-tools</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>70</v>
+        <v>9</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>lgazo/drawio-mcp-server</t>
+          <t>nexu-io/html-video</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>1455</v>
+        <v>4559</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>20.4</v>
+        <v>303.9</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Draw.io Model Context Protocol (MCP) 服务器
-【原文】Draw.io Model Context Protocol (MCP) Server</t>
+          <t>将 HTML、CSS 和数据转换为 MP4 视频的编程工具
+【原文】Programmatic video for coding agents — HTML to video on your laptop. Turn HTML, CSS &amp; data into real MP4s with pluggable render engines, 21 templates, AI soundtrack. Apache-2.0, no per-render fees. An official project by the Open Design team.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1779,7 +1786,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lgazo/drawio-mcp-server</t>
+          <t>https://github.com/nexu-io/html-video</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1788,16 +1795,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>2.92</v>
+        <v>43.42</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1810,19 +1817,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P14" s="6" t="inlineStr"/>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, apache-2, coding-agent, css, ffmpeg, html, html-to-video, hyperframes, mp4, open-design, open-source, programmatic-video</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>499</v>
+        <v>105</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1834,26 +1845,26 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-03</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Calinou/awesome-godot</t>
+          <t>florinpop17/app-ideas</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>10677</v>
+        <v>97431</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>18</v>
+        <v>247.7</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>Godot 引擎插件、脚本和附加组件列表
-【原文】A curated list of free/libre plugins, scripts and add-ons for Godot</t>
+          <t>收集应用想法以提升编码技能
+【原文】A Collection of application ideas which can be used to improve your coding skills.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1863,12 +1874,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1878,7 +1889,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Calinou/awesome-godot</t>
+          <t>https://github.com/florinpop17/app-ideas</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1887,11 +1898,11 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>2.57</v>
+        <v>35.39</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>CC-BY-4.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr"/>
@@ -1907,21 +1918,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, game-development, godot, godot-engine</t>
+          <t>applications, coding, codingchallenges, css, hacktoberfest, html, ideas, javascript, practice</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2015-04-12</t>
+          <t>2019-02-25</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2025-10-11</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>4161</v>
+        <v>2753</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1933,26 +1944,25 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>skill in:name,description stars:&gt;50000</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Taxuspt/garmin_mcp</t>
+          <t>LancelotRar/best-cf-ips</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1102</v>
+        <v>1159</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>14.2</v>
+        <v>165.5</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>访问 Garmin 数据的 MCP 服务器
-【原文】MCP server to access Garmin data</t>
+          <t>提供自动更新的 Cloudflare 优选 IP API</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1962,12 +1972,12 @@
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>MCP服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1977,7 +1987,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Taxuspt/garmin_mcp</t>
+          <t>https://github.com/LancelotRar/best-cf-ips</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1986,18 +1996,14 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>2.03</v>
+        <v>23.65</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr"/>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2011,57 +2017,57 @@
       <c r="P16" s="6" t="inlineStr"/>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2025-03-08</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>543</v>
+        <v>49</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-03</t>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>yushui2022/MathModel-Skill</t>
+          <t>HKUDS/ViMax</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>332</v>
+        <v>12313</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>10.8</v>
+        <v>163.2</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>提供数学建模工作流程技能，涵盖问题解析、建模、代码生成等
-【原文】Agent-native mathematical modeling workflow skills for Trae, Claude Code, and Codex, covering problem parsing, modeling, code generation, evidence checks, paper writing, and Word delivery.</t>
+          <t>全功能视频生成系统，包括导演、编剧、制片人和视频生成
+【原文】"ViMax: Agentic Video Generation (Director, Screenwriter, Producer, and Video Generator All-in-One)"</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2076,7 +2082,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yushui2022/MathModel-Skill</t>
+          <t>https://github.com/HKUDS/ViMax</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2085,7 +2091,7 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>1.54</v>
+        <v>23.32</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2107,19 +2113,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P17" s="6" t="inlineStr"/>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>agentic-aigc, video-generation</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>216</v>
+        <v>528</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2131,36 +2141,37 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>realZillionX/InspireSkill</t>
+          <t>Anil-matcha/Open-Generative-AI</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>201</v>
+        <v>28193</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>10.4</v>
+        <v>161.9</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>提供启智平台的 Agent 驾驶舱，支持 Skill 和 CLI 操作
-【原文】启智平台的 Agent 驾驶舱：Skill + CLI，一条命令直达。Agent cockpit for the Inspire ML platform: one command, every operation, straight from chat.</t>
+          <t>开源AI视频平台替代品，提供图像和视频生成
+【原文】Unrestricted Open-source alternative to AI video platforms — Free AI image &amp; video generation studio with 600+ models (Flux, Midjourney, Kling, Sora, Veo). No content filters. Self-hosted, MIT licensed.
+【依据】topics: ai-art-generator, ai-image-generation, ai-video-generation, creative-tools, image-to-video</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2175,7 +2186,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/realZillionX/InspireSkill</t>
+          <t>https://github.com/Anil-matcha/Open-Generative-AI</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2184,7 +2195,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>1.49</v>
+        <v>23.13</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2193,7 +2204,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2206,22 +2217,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P18" s="6" t="inlineStr"/>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>ai-art-generator, ai-image-generation, ai-video-generation, creative-tools, fal-ai-alternative, generative-ai, image-to-video, invideo-alternative, javascript, kling-ai, lipsync, midjourney-alternative</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2023-05-09</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>135</v>
+        <v>1219</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
@@ -2230,31 +2245,31 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
+          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>VkRainB/ccMesh</t>
+          <t>3b1b/manim</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>119</v>
+        <v>93637</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>9.800000000000001</v>
+        <v>156.5</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude Code / Codex 的本地 AI 代理网关桌面应用程序
-【原文】Claude Code / Codex local AI proxy gateway desktop app (Tauri). Anthropic Messages &lt;-&gt; OpenAI-compatible protocol transform, model mapping, endpoint rotation/failover. 本地桌面代理网关：协议转换、模型映射、多端点轮换/熔断，对接官方 API 或中转站，不改客户端。Windows/macOS/Linux.</t>
+          <t>用于制作解释性数学视频的动画引擎
+【原文】Animation engine for explanatory math videos</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -2274,7 +2289,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/VkRainB/ccMesh</t>
+          <t>https://github.com/3b1b/manim</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2283,16 +2298,16 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>1.4</v>
+        <v>22.35</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2307,62 +2322,62 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>claude, desktop-app, gateway, llm, local-proxy, protocol-conversion, tauri2</t>
+          <t>3b1b-videos, animation, explanatory-math-videos, python</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2015-03-22</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>85</v>
+        <v>4189</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-04</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>dodolalorc/astro-navfolio</t>
+          <t>huggingface/diffusers</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>101</v>
+        <v>34475</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>6.2</v>
+        <v>154.4</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>提供基于 Astro 的个人发布主题
-【原文】🌿 基于 Astro 的静谧个人发布主题，融合主页、博客、作品集的数字花园。✨🌿 A serene Astro theme for personal publishing—bringing your homepage, blog, portfolio, and digital garden together. ✨</t>
+          <t>提供 PyTorch 中的图像、视频和音频生成模型
+【原文】🤗 Diffusers: State-of-the-art diffusion models for image, video, and audio generation in PyTorch.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线/图文产线</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>可部署服务/代码库</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2377,7 +2392,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dodolalorc/astro-navfolio</t>
+          <t>https://github.com/huggingface/diffusers</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2386,16 +2401,16 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.89</v>
+        <v>22.06</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Astro</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2410,52 +2425,52 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>astro, blog-theme</t>
+          <t>deep-learning, diffusion, flux, image-generation, image2image, image2video, latent-diffusion-models, pytorch, qwen-image, score-based-generative-modeling, stable-diffusion, stable-diffusion-diffusers</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2022-05-30</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>114</v>
+        <v>1563</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-04</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>81NewArk/AntiCAP-WebApi</t>
+          <t>khoj-ai/khoj</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>366</v>
+        <v>37229</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>5.6</v>
+        <v>140.8</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供基于 AntiCAP 开发的多类型验证码识别网站
-【原文】基于AntiCAP开发的多类型验证码识别网站，支持点选 滑块 算术 旋转 OCR</t>
+          <t>提供个人 AI 助手，可自托管。
+【原文】Your AI second brain. Self-hostable. Get answers from the web or your docs. Build custom agents, schedule automations, do deep research. Turn any online or local LLM into your personal, autonomous AI (gpt, claude, gemini, llama, qwen, mistral). Get started - free.</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2465,12 +2480,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G21" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2480,7 +2495,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/81NewArk/AntiCAP-WebApi</t>
+          <t>https://github.com/khoj-ai/khoj</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2489,16 +2504,16 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.8</v>
+        <v>20.12</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
@@ -2511,65 +2526,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P21" s="6" t="inlineStr"/>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>agent, ai, assistant, chat, chatgpt, emacs, image-generation, llama3, llamacpp, llm, obsidian, obsidian-md</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2021-08-16</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>460</v>
+        <v>1850</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-04</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>mikalv/awesome-qt-qml</t>
+          <t>Robbyant/lingbot-world</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>2605</v>
+        <v>4423</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>5.5</v>
+        <v>138.2</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Qt 和 QML 库、资源、项目列表
-【原文】A curated list of awesome Qt and QML libraries, resources, projects, and shiny things.</t>
+          <t>推进开源世界模型的发展
+【原文】Advancing Open-source World Models</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H22" s="7" t="inlineStr">
@@ -2579,7 +2598,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mikalv/awesome-qt-qml</t>
+          <t>https://github.com/Robbyant/lingbot-world</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2588,14 +2607,18 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.78</v>
+        <v>19.75</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M22" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2608,21 +2631,21 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, cpp, javascript, qml, qml-bindings, qpm, qt, qt-quick, qt4, qt5, qtcreator</t>
+          <t>aigc, image-to-video, lingbot-world, video-generation, world-models</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2017-06-25</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>3356</v>
+        <v>224</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2634,41 +2657,41 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>curiositech/some_claude_skills</t>
+          <t>Tencent-Hunyuan/HunyuanVideo</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>209</v>
+        <v>12508</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>5</v>
+        <v>134.7</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>提供 Claude skills，简化生活操作
-【原文】Claude skills that make my life easier.</t>
+          <t>大型视频生成模型系统框架
+【原文】HunyuanVideo: A Systematic Framework For Large Video Generation Model</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -2678,7 +2701,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/curiositech/some_claude_skills</t>
+          <t>https://github.com/Tencent-Hunyuan/HunyuanVideo</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2687,16 +2710,16 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>0.72</v>
+        <v>19.24</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2709,19 +2732,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P23" s="6" t="inlineStr"/>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>diffusion-models, diffusion-transformer, video-generation</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>290</v>
+        <v>650</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2733,36 +2760,36 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-03</t>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>tmcw/awesome-geojson</t>
+          <t>invoke-ai/InvokeAI</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>2535</v>
+        <v>28173</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>4.3</v>
+        <v>132.9</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>GeoJSON 工具库，简化操作
-【原文】GeoJSON utilities that will make your life easier.</t>
+          <t>提供 Stable Diffusion 模型的创意引擎
+【原文】Invoke is a leading creative engine for Stable Diffusion models, empowering professionals, artists, and enthusiasts to generate and create visual media using the latest AI-driven technologies. The solution offers an industry leading WebUI, and serves as the foundation for multiple commercial products.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>可部署服务/代码库/技能包</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2777,7 +2804,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tmcw/awesome-geojson</t>
+          <t>https://github.com/invoke-ai/InvokeAI</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2786,14 +2813,18 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>0.62</v>
+        <v>18.98</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M24" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2806,21 +2837,21 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, geojson, list</t>
+          <t>ai-art, artificial-intelligence, generative-art, image-generation, img2img, inpainting, latent-diffusion, linux, macos, outpainting, stable-diffusion, txt2img</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2015-05-28</t>
+          <t>2022-08-17</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>4115</v>
+        <v>1484</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2832,12 +2863,3862 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-03</t>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="150" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>oritera/Cairn</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n">
+        <v>2709</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>132.6</v>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>提供 AI 辅助的渗透测试工具。
+【原文】A AI general-purpose state-space search engine, validated first on autonomous penetration testing.</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/技能包</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/oritera/Cairn</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>18.94</v>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agent, ai-cybersecurity, ai-hacker, ai-hacking, blackbox-testing, ctf, ctf-tools, llm, penetration-testing, pentesting, red-teaming</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-19</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>143</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="V25" s="6" t="inlineStr">
+        <is>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="150" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>ciembor/agent-rules-books</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="n">
+        <v>2732</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>131</v>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>AI编码代理的规则/技能
+【原文】AGENTS.md rules / skills for AI coding agents: Codex, Cursor &amp; Claude Code. Inspired by Clean Code, Refactoring, DDD, Clean Architecture and DDIA programming books.
+【依据】topics: agent-rules, agent-skills, claude-code, claude-code-skills</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I26" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ciembor/agent-rules-books</t>
+        </is>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>18.71</v>
+      </c>
+      <c r="L26" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr"/>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>agent-rules, agent-skills, agent-skills-manager, agents-md, agents-rules, agents-skills, agentsmd, ai-agent, ai-skills, claude-code, claude-code-skills, code-quality</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>146</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="V26" s="6" t="inlineStr">
+        <is>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="150" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>vllm-project/vllm-omni</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n">
+        <v>6739</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>高效模型推理框架，支持多种模态模型
+【原文】A framework for efficient model inference with omni-modality models</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/vllm-project/vllm-omni</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>18.56</v>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>audio-generation, diffusion, image-generation, inference, model-serving, multimodal, pytorch, transformer, video-generation, world-model</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2025-09-11</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>363</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V27" s="6" t="inlineStr">
+        <is>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="150" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>FailproofAI/failproofai</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n">
+        <v>2526</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>113.3</v>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>AI代理可观察性和执行策略
+【原文】Observability and enforcement for AI agent harnesses. Capture every run and runtime reliability with policy enforcement.  40 built-in policies, a local dashboard, no account required with a generous free cloud plan
+【依据】topics: agent-failure, agent-harness, agent-observability, agent-reliability</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I28" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/FailproofAI/failproofai</t>
+        </is>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>MDX</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O28" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>agent-failure, agent-harness, agent-observability, agent-reliability, agent-tracing, ai-agent, claude-code, codex, enforcement, evals, guardrails, hermes</t>
+        </is>
+      </c>
+      <c r="Q28" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="R28" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S28" s="3" t="n">
+        <v>156</v>
+      </c>
+      <c r="T28" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" s="3" t="inlineStr">
+        <is>
+          <t>stock</t>
+        </is>
+      </c>
+      <c r="V28" s="6" t="inlineStr">
+        <is>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="150" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>peter123023/awesome-free-llm-api</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>96.2</v>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>导航免费大模型 API
+【原文】免费大模型 API 导航 · 只收录能通过 API Key 和 endpoint 调用的永久免费 / 限时免费接口｜A curated list of free LLM APIs — permanently free tiers and limited-time free models, all callable via API key and endpoint. Channel-first, with a model index for DeepSeek, GLM, Qwen and more</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I29" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/peter123023/awesome-free-llm-api</t>
+        </is>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>13.75</v>
+      </c>
+      <c r="L29" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr"/>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O29" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P29" s="6" t="inlineStr"/>
+      <c r="Q29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="R29" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V29" s="6" t="inlineStr">
+        <is>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="150" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>NVlabs/Sana</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="n">
+        <v>9018</v>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>90.40000000000001</v>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>基于线性扩散变换器的图像合成系统
+【原文】SANA: Efficient High-Resolution Image Synthesis with Linear Diffusion Transformer
+【依据】topics: diffusion, dit, linear-transformer, pytorch, text-to-image-generation</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I30" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/NVlabs/Sana</t>
+        </is>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="L30" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O30" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>diffusion, dit, linear-transformer, nvfp4, pytorch, reinforcement-learning, sana, streaming-video, system-algorithm-deisgn, text-to-image-generation, text-to-video, transformers</t>
+        </is>
+      </c>
+      <c r="Q30" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="R30" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>698</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V30" s="6" t="inlineStr">
+        <is>
+          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="150" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>GVCLab/PersonaLive</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="n">
+        <v>3690</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>生成直播中的表情丰富的肖像图像动画
+【原文】[CVPR 2026] PersonaLive! : Expressive Portrait Image Animation for Live Streaming</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/GVCLab/PersonaLive</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>12.81</v>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O31" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>cvpr, cvpr2026, talking-head, video-generation</t>
+        </is>
+      </c>
+      <c r="Q31" s="3" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="R31" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>288</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V31" s="6" t="inlineStr">
+        <is>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="150" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>jujumilk3/leaked-system-prompts</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n">
+        <v>14924</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>86.2</v>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>收集泄露的系统提示词
+【原文】Collection of leaked system prompts</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I32" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/jujumilk3/leaked-system-prompts</t>
+        </is>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>12.31</v>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr"/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>ai, document, llm, prompt</t>
+        </is>
+      </c>
+      <c r="Q32" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-16</t>
+        </is>
+      </c>
+      <c r="R32" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V32" s="6" t="inlineStr">
+        <is>
+          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="150" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>PKU-YuanGroup/Helios</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>2143</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>78.5</v>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>提供实时长视频生成模型。
+【原文】Helios: Real Real-Time Long Video Generation Model</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/PKU-YuanGroup/Helios</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>11.22</v>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>acceleration, diffusion, diffusion-model, diffusion-models, efficient-tuning, high-quality, image-to-video, image2video, interactive, long-context, long-video-generation, real-time</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>191</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V33" s="6" t="inlineStr">
+        <is>
+          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="150" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>zjp1997720/zhijian-ai-bluebook-workbuddy-harness</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n">
+        <v>204</v>
+      </c>
+      <c r="C34" s="5" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>拆解 WorkBuddy 的提示词、记忆、插件等
+【原文】智见 AI 蓝皮书：拆解 WorkBuddy 的提示词、记忆、插件、专家、Skill 与安全边界。</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/zjp1997720/zhijian-ai-bluebook-workbuddy-harness</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr"/>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, bluebook, harness, workbuddy, zhijian-ai</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V34" s="6" t="inlineStr">
+        <is>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="150" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>vercel/satori</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="n">
+        <v>13927</v>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>57.8</v>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>将 HTML 和 CSS 转换为 SVG
+【原文】Enlightened library to convert HTML and CSS to SVG</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>图文产线</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/vercel/satori</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t>MPL-2.0</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>css, image, image-generation, image-generator, jsx, opengraph-images, satori, svg, vercel</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
+          <t>2022-01-27</t>
+        </is>
+      </c>
+      <c r="R35" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="S35" s="3" t="n">
+        <v>1686</v>
+      </c>
+      <c r="T35" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V35" s="6" t="inlineStr">
+        <is>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="150" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>digitalsamba/claude-code-video-toolkit</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="n">
+        <v>2061</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>AI原生视频生产工具包，支持Claude Code
+【原文】AI-native video production toolkit for Claude Code
+【依据】topics: ai-video-generator, claude-code, programmatic-video, text-to-speech, video-editing</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/digitalsamba/claude-code-video-toolkit</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>7.52</v>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>ai-video-generator, claude-code, developer-tools, elevenlabs, open-source, openclaw, playwright, programmatic-video, qwen-tts, remotion, text-to-speech, video-editing</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="n">
+        <v>274</v>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V36" s="6" t="inlineStr">
+        <is>
+          <t>topic:ai-video-generator stars:&gt;2000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="150" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>SandAI-org/MAGI-1</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="n">
+        <v>3782</v>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>52.3</v>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>实现大规模自回归视频生成
+【原文】MAGI-1: Autoregressive Video Generation at Scale</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G37" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I37" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/SandAI-org/MAGI-1</t>
+        </is>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>7.47</v>
+      </c>
+      <c r="L37" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O37" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>autoregressive, diffusion-models, video-generation</t>
+        </is>
+      </c>
+      <c r="Q37" s="3" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="n">
+        <v>506</v>
+      </c>
+      <c r="T37" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V37" s="6" t="inlineStr">
+        <is>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="150" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Feelingeouncouple/Canva-Professional</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="n">
+        <v>598</v>
+      </c>
+      <c r="C38" s="5" t="n">
+        <v>48.1</v>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>Canva Pro云端工具包与自动化工作室
+【原文】Canva Pro Cloud Toolkit &amp; Automation Studio. Advanced graphic design assets, team collaboration workflows, premium template management, and visual content creation tools.
+【依据】topics: canva-app, canva-editor-tools, canva-export-tools, canva-free, canva-pro</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I38" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Feelingeouncouple/Canva-Professional</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="L38" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr"/>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O38" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>canva-app, canva-bulk-create, canva-editor-tools, canva-export-tools, canva-free, canva-full, canva-hack, canva-pro, canva-pro-team-2026, followers-ig, social-media-app, social-media-design</t>
+        </is>
+      </c>
+      <c r="Q38" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="R38" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S38" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="T38" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V38" s="6" t="inlineStr">
+        <is>
+          <t>content automation in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="150" customHeight="1">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>hao-ai-lab/FastVideo</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n">
+        <v>4363</v>
+      </c>
+      <c r="C39" s="5" t="n">
+        <v>44.6</v>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>加速视频生成的统一推理和后训练框架
+【原文】A unified inference and post-training framework for accelerated video generation.</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/hao-ai-lab/FastVideo</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>6.37</v>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>diffusers, diffusion-models, distillation, inference, post-training, video-generation</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2024-10-24</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="n">
+        <v>685</v>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V39" s="6" t="inlineStr">
+        <is>
+          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="150" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>leejet/stable-diffusion.cpp</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="n">
+        <v>6948</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>43.3</v>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>提供纯 C/C++ 的扩散模型推理
+【原文】Diffusion model(SD,Flux,Wan,Qwen Image,Z-Image,...) inference in pure C/C++</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="inlineStr">
+        <is>
+          <t>图文产线</t>
+        </is>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I40" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/leejet/stable-diffusion.cpp</t>
+        </is>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="L40" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>ai, cplusplus, diffusion, flux, flux-dev, ggml, image-generation, image2image, img2img, latent-diffusion, ltx-video, qwen-image</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t>2023-08-13</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>1123</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V40" s="6" t="inlineStr">
+        <is>
+          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="150" customHeight="1">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>strawberrynine/ZiWeiDouShu-Master</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>提供紫微斗数大师级分析
+【原文】紫微斗数大师级分析，基于古籍 希夷先生《紫微斗数》，融合倪海厦《天纪》体系，含完整排盘算法、四化系统、格局知识库，可以算任意一年/月/日的感情/健康/财运/事业运/学业运/移民运。需要提供具体到小时的出生时间，和具体到市的出生地点。</t>
+        </is>
+      </c>
+      <c r="E41" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F41" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G41" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I41" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/strawberrynine/ZiWeiDouShu-Master</t>
+        </is>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="L41" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr"/>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O41" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P41" s="6" t="inlineStr"/>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V41" s="6" t="inlineStr">
+        <is>
+          <t>古籍 in:name,description stars:&gt;20</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="150" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>ModelEngine-Group/app-platform</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="n">
+        <v>1454</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>提供大模型应用开发的集成声明式编程和低代码配置工具
+【原文】AppPlatform 是一个前沿的大模型应用工程，旨在通过集成的声明式编程和低代码配置工具，简化和优化大模型的训练与推理应用的开发过程。本工程为软件工程师和产品经理提供一个强大的、可扩展的环境，以支持从概念到部署的全流程 AI 应用开发。</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="inlineStr">
+        <is>
+          <t>视频产线/AI免费池</t>
+        </is>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>MCP服务/技能包/架构参考/可部署服务</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/ModelEngine-Group/app-platform</t>
+        </is>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="L42" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>Java</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O42" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>agent, agentic-ai, agentic-workflow, ai, java, low-code</t>
+        </is>
+      </c>
+      <c r="Q42" s="3" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="R42" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>527</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V42" s="6" t="inlineStr">
+        <is>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="150" customHeight="1">
+      <c r="A43" s="3" t="inlineStr">
+        <is>
+          <t>the-wayee/OpenTV</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>短视频内容的策划与生产工具</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F43" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/技能包</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/the-wayee/OpenTV</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P43" s="6" t="inlineStr"/>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V43" s="6" t="inlineStr">
+        <is>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="150" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>18534516725/llm-api-setup-guides</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="n">
+        <v>138</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>中文AI API中转站与工具配置教程
+【原文】88篇中文 AI API中转站与工具配置教程：Codex API、Claude Code API、OpenAI-compatible API、Base URL、Cursor、Cherry Studio、计费验证与错误排查。
+【依据】topics: ai-api, api-proxy, api-relay, api-testing, cherry-studio, claude-api</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/18534516725/llm-api-setup-guides</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>ai-api, api-proxy, api-relay, api-testing, cherry-studio, chinese-tutorial, claude-api, claude-code, cline, codex-api, codex-cli, cursor</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="R44" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>57</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V44" s="6" t="inlineStr">
+        <is>
+          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="150" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
+        <is>
+          <t>rfhdw0102/YouDaoNoteLM</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="n">
+        <v>201</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>有道云笔记等内容的自动知识库沉淀与智能问答
+【原文】接入有道云笔记、本地文件、网页与音视频等内容，自动沉淀为可检索知识库；基于 RAG 精准引用你的资料，提供可靠的智能问答与内容生成。兼容主流大模型和向量模型，让知识真正为你所用。
+【依据】topics: YouDaoNoteLM, RAG, 智能问答</t>
+        </is>
+      </c>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F45" s="3" t="inlineStr">
+        <is>
+          <t>数据集</t>
+        </is>
+      </c>
+      <c r="G45" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I45" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/rfhdw0102/YouDaoNoteLM</t>
+        </is>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="L45" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O45" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P45" s="6" t="inlineStr"/>
+      <c r="Q45" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>87</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V45" s="6" t="inlineStr">
+        <is>
+          <t>RAG 知识库 in:name,description stars:&gt;200</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="150" customHeight="1">
+      <c r="A46" s="3" t="inlineStr">
+        <is>
+          <t>FurkanGozukara/Stable-Diffusion</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="n">
+        <v>2765</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>提供 AI 艺术生成和深度伪造工具。
+【原文】FLUX, Stable Diffusion, SDXL, SD3, LoRA, Fine Tuning, DreamBooth, Training, Automatic1111, Forge WebUI, SwarmUI, DeepFake, TTS, Animation, Text To Video, Tutorials, Guides, Lectures, Courses, ComfyUI, Google Colab, RunPod, Kaggle, NoteBooks, ControlNet, TTS, Voice Cloning, AI, AI News, ML, ML News, News, Tech, Tech News, Kohya, Midjourney, RunPod</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="inlineStr">
+        <is>
+          <t>图文产线/AI免费池</t>
+        </is>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/代码库</t>
+        </is>
+      </c>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I46" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/FurkanGozukara/Stable-Diffusion</t>
+        </is>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>Jupyter Notebook</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>ai-art, coding, deepfake-generation, dreambooth, education, flux-dev, flux-lora, generative-ai, guides, how-to, image-to-video-generation, kohya-webui</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-01</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>1227</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="V46" s="6" t="inlineStr">
+        <is>
+          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="150" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>nndl/llm-beginner</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="n">
+        <v>6730</v>
+      </c>
+      <c r="C47" s="5" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>提供大模型与智能体电子书和编程任务
+【原文】《大模型与智能体》电子书与 6 个编程任务：Transformer、mini-GPT、SFT/DPO、RAG、工具调用与编程智能体。</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F47" s="3" t="inlineStr">
+        <is>
+          <t>数据集/代码库</t>
+        </is>
+      </c>
+      <c r="G47" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I47" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/nndl/llm-beginner</t>
+        </is>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L47" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O47" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>agent, fudannlp, llm, openmoss, step-by-step</t>
+        </is>
+      </c>
+      <c r="Q47" s="3" t="inlineStr">
+        <is>
+          <t>2017-03-29</t>
+        </is>
+      </c>
+      <c r="R47" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>3451</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V47" s="6" t="inlineStr">
+        <is>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="150" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>GalTransl/GalTransl</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="n">
+        <v>2263</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>支持大语言模型的 Galgame 自动化翻译解决方案
+【原文】支持GPT-4/Claude/Deepseek/Sakura等大语言模型的Galgame自动化翻译解决方案  Automated translation solution for visual novels supporting GPT-4/Claude/Deepseek/Sakura</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I48" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/GalTransl/GalTransl</t>
+        </is>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="L48" s="3" t="inlineStr">
+        <is>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O48" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>ai, galgame, translater</t>
+        </is>
+      </c>
+      <c r="Q48" s="3" t="inlineStr">
+        <is>
+          <t>2023-05-31</t>
+        </is>
+      </c>
+      <c r="R48" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>1197</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V48" s="6" t="inlineStr">
+        <is>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="150" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Pangu-Immortal/hunter-ai-content-factory</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="n">
+        <v>391</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>自动从多个平台采集热点，生成文章和插图。
+【原文】自动发布 24 小时情报系统：好文章的 80% 在于选题。Hunter AI 自动从 GitHub Trending、Twitter、HackerNews Reddit 等平台采集热点，用 AI 判断哪些值得写，自动生成文章和插图，自动发布。</t>
+        </is>
+      </c>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F49" s="3" t="inlineStr">
+        <is>
+          <t>可部署服务/技能包</t>
+        </is>
+      </c>
+      <c r="G49" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I49" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Pangu-Immortal/hunter-ai-content-factory</t>
+        </is>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L49" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O49" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P49" s="6" t="inlineStr"/>
+      <c r="Q49" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-22</t>
+        </is>
+      </c>
+      <c r="R49" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>230</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V49" s="6" t="inlineStr">
+        <is>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="150" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>sollyu/AndroidStudioChineseLanguagePack</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="n">
+        <v>2494</v>
+      </c>
+      <c r="C50" s="5" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>提供 AndroidStudio 中文插件
+【原文】AndroidStudio中文插件(官方修改版本）</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I50" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/sollyu/AndroidStudioChineseLanguagePack</t>
+        </is>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="L50" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr"/>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O50" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>android-studio, chinese, plugins</t>
+        </is>
+      </c>
+      <c r="Q50" s="3" t="inlineStr">
+        <is>
+          <t>2022-03-21</t>
+        </is>
+      </c>
+      <c r="R50" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>1633</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V50" s="6" t="inlineStr">
+        <is>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="150" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>wfcz10086/AI-automatically-generates-novels</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="n">
+        <v>936</v>
+      </c>
+      <c r="C51" s="5" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>基于 AI 和提示词的 AIGC 创作生产力工具
+【原文】一个基于ai +提示词 的aigc创作生产力工具， 已经有数百家工作室和个人作者通过该工具实现了快速、批量生成小说、剧本、镜头。</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I51" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/wfcz10086/AI-automatically-generates-novels</t>
+        </is>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="L51" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O51" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P51" s="6" t="inlineStr"/>
+      <c r="Q51" s="3" t="inlineStr">
+        <is>
+          <t>2024-12-04</t>
+        </is>
+      </c>
+      <c r="R51" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S51" s="3" t="n">
+        <v>644</v>
+      </c>
+      <c r="T51" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V51" s="6" t="inlineStr">
+        <is>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="150" customHeight="1">
+      <c r="A52" s="3" t="inlineStr">
+        <is>
+          <t>lornshrimp/Lorn.NovelWriteSkills</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="n">
+        <v>205</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>提供围绕小说创作工作流的AI写作资产库
+【原文】一个面向长篇网文 / 小说创作工作流的 AI 写作资产库。它不是“随手堆提示词”的仓库，而是一套围绕 题材设计 → 大纲搭建 → 章节创作 → 审阅润色 → 多平台改写 → 质量门禁 → 分发落盘 搭起来的可复用写作系统。</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>技能包/代码库</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I52" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/lornshrimp/Lorn.NovelWriteSkills</t>
+        </is>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="L52" s="3" t="inlineStr">
+        <is>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>PowerShell</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O52" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>agent-skills, ai, novel, skills, writing-assistant</t>
+        </is>
+      </c>
+      <c r="Q52" s="3" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="R52" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S52" s="3" t="n">
+        <v>148</v>
+      </c>
+      <c r="T52" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V52" s="6" t="inlineStr">
+        <is>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="150" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>metasequoiaime/MSIME-Windows</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="n">
+        <v>1335</v>
+      </c>
+      <c r="C53" s="5" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>提供水杉输入法 Windows 产品
+【原文】水杉输入法 Windows 产品：TSF、Server、GUI、设置页与安装器。内测：tg: https://t.me/msimegroup QQ Group: 829919142</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G53" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I53" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/metasequoiaime/MSIME-Windows</t>
+        </is>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="L53" s="3" t="inlineStr">
+        <is>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>C++</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O53" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>chinese, ime, input-method, japanese, metasequoia, tsf, windows, windows-11</t>
+        </is>
+      </c>
+      <c r="Q53" s="3" t="inlineStr">
+        <is>
+          <t>2023-10-14</t>
+        </is>
+      </c>
+      <c r="R53" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S53" s="3" t="n">
+        <v>1061</v>
+      </c>
+      <c r="T53" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V53" s="6" t="inlineStr">
+        <is>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="150" customHeight="1">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>renmengwen/MuseDock</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="C54" s="5" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>AI短视频创作与编辑工作台，整理来源，生成视频
+【原文】MuseDock 是一个本地优先的 AI 短视频创作与编辑工作台。输入一个选题，粘贴文章、GitHub 或抖音链接，也可以直接上传图片；MuseDock 会整理来源、补充研究、规划脚本与镜头，生成配音和 HTML 动画帧，最后在本机渲染成视频。</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/renmengwen/MuseDock</t>
+        </is>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="L54" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O54" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P54" s="6" t="inlineStr"/>
+      <c r="Q54" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="R54" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-26</t>
+        </is>
+      </c>
+      <c r="S54" s="3" t="n">
+        <v>95</v>
+      </c>
+      <c r="T54" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V54" s="6" t="inlineStr">
+        <is>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="150" customHeight="1">
+      <c r="A55" s="3" t="inlineStr">
+        <is>
+          <t>Java-Edge/Java-Interview-Tutorial</t>
+        </is>
+      </c>
+      <c r="B55" s="4" t="n">
+        <v>2860</v>
+      </c>
+      <c r="C55" s="5" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>Java/数据库/DDD/设计模式/微服务/中间件/AI大模型应用/区块链开发最佳实践教程
+【原文】请star，勿fork，因为爱force push！涵盖国际大厂Java/数据库/DDD/设计模式/微服务/中间件/AI大模型应用/区块链开发最佳实践。关注公众号【JavaEdge】，一起交流学习！</t>
+        </is>
+      </c>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F55" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G55" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I55" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/Java-Edge/Java-Interview-Tutorial</t>
+        </is>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L55" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>Shell</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O55" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>architecture, blockchain, ddd, java</t>
+        </is>
+      </c>
+      <c r="Q55" s="3" t="inlineStr">
+        <is>
+          <t>2019-07-22</t>
+        </is>
+      </c>
+      <c r="R55" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="S55" s="3" t="n">
+        <v>2606</v>
+      </c>
+      <c r="T55" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V55" s="6" t="inlineStr">
+        <is>
+          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="150" customHeight="1">
+      <c r="A56" s="3" t="inlineStr">
+        <is>
+          <t>go-ego/gse</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="n">
+        <v>2841</v>
+      </c>
+      <c r="C56" s="5" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>提供多语言 NLP 和文本分割工具
+【原文】Go efficient multilingual NLP and text segmentation; support English, Chinese, Japanese and others.</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I56" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/go-ego/gse</t>
+        </is>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="L56" s="3" t="inlineStr">
+        <is>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Go</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O56" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>chinese, english, go, gse, hmm, hmm-viterbi-algorithm, japanese, jieba, nlp, segment, trie</t>
+        </is>
+      </c>
+      <c r="Q56" s="3" t="inlineStr">
+        <is>
+          <t>2017-06-23</t>
+        </is>
+      </c>
+      <c r="R56" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="S56" s="3" t="n">
+        <v>3365</v>
+      </c>
+      <c r="T56" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V56" s="6" t="inlineStr">
+        <is>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="150" customHeight="1">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>AIPMAndy/FreeToken</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="n">
+        <v>105</v>
+      </c>
+      <c r="C57" s="5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>收集免费 API Token 的获取方法和使用指南
+【原文】🎁 收集各种免费 API Token 的获取方法和使用指南</t>
+        </is>
+      </c>
+      <c r="E57" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="inlineStr">
+        <is>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I57" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/AIPMAndy/FreeToken</t>
+        </is>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="L57" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr"/>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O57" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P57" s="6" t="inlineStr"/>
+      <c r="Q57" s="3" t="inlineStr">
+        <is>
+          <t>2026-05-04</t>
+        </is>
+      </c>
+      <c r="R57" s="3" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="S57" s="3" t="n">
+        <v>128</v>
+      </c>
+      <c r="T57" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V57" s="6" t="inlineStr">
+        <is>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="150" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>lihanghang/NLP-Knowledge-Graph</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="n">
+        <v>1766</v>
+      </c>
+      <c r="C58" s="5" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>自然语言处理、知识图谱、对话系统技术研究与应用
+【原文】自然语言处理、知识图谱、对话系统，大模型等技术研究与应用。
+【依据】topics: bert, deep-learning, knowledge-graph, llm, nlp</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>RAG检索线</t>
+        </is>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>代码库/架构参考</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I58" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/lihanghang/NLP-Knowledge-Graph</t>
+        </is>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="L58" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O58" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>agent, agentic-ai, bert, deep-learning, ernie, event-driven, kbqa, knowledge-graph, llm, machine-learning, ner, nlp</t>
+        </is>
+      </c>
+      <c r="Q58" s="3" t="inlineStr">
+        <is>
+          <t>2019-01-29</t>
+        </is>
+      </c>
+      <c r="R58" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="S58" s="3" t="n">
+        <v>2780</v>
+      </c>
+      <c r="T58" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V58" s="6" t="inlineStr">
+        <is>
+          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="150" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
+        <is>
+          <t>neopen/story-shot-agent</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="n">
+        <v>183</v>
+      </c>
+      <c r="C59" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D59" s="6" t="inlineStr">
+        <is>
+          <t>自动解析剧本，生成视频提示词，支持角色和剧情一致性保持
+【原文】剧本分镜智能体（PenShot）：电影/动漫/短剧/小说→分镜→提示词→视频。| 基于LLM 通过 LangGraph+LlamaIndex实现任意格式剧本的自动解析，生成 Sora/Veo/Runway 等模型可用的连贯text-to-video提示词。保持角色/剧情跨片段一致，支持 MCP/REST API/Function Calls/A2A 多方式集成。（LLM-powered text-to-video-prompt agent. Break scripts into Sora/Veo-ready shots with character consistency）</t>
+        </is>
+      </c>
+      <c r="E59" s="3" t="inlineStr">
+        <is>
+          <t>视频产线</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="inlineStr">
+        <is>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G59" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I59" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/neopen/story-shot-agent</t>
+        </is>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="L59" s="3" t="inlineStr">
+        <is>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O59" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>agent-to-agent, ai-filmmaking, ai-video-generation, character-consistency, function-calling, kling-ai, langgraph-agent, llm-agent, pika-labs, prompt-engineering, rag, screenplay</t>
+        </is>
+      </c>
+      <c r="Q59" s="3" t="inlineStr">
+        <is>
+          <t>2025-10-23</t>
+        </is>
+      </c>
+      <c r="R59" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="S59" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="T59" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V59" s="6" t="inlineStr">
+        <is>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="150" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>MoFox-Studio/Neo-MoFox</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="n">
+        <v>101</v>
+      </c>
+      <c r="C60" s="5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="D60" s="6" t="inlineStr">
+        <is>
+          <t>提供 AI 聊天机器人框架，旨在创造数字生命体。
+【原文】一个全新重构的 AI 聊天机器人框架，它的目标不仅仅是回答问题，而是创造一个真正的数字生命体。
+【依据】旨在创造一个真正的数字生命体。</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I60" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/MoFox-Studio/Neo-MoFox</t>
+        </is>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L60" s="3" t="inlineStr">
+        <is>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O60" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>agent, ai, bot, chatbot</t>
+        </is>
+      </c>
+      <c r="Q60" s="3" t="inlineStr">
+        <is>
+          <t>2026-01-28</t>
+        </is>
+      </c>
+      <c r="R60" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="S60" s="3" t="n">
+        <v>224</v>
+      </c>
+      <c r="T60" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V60" s="6" t="inlineStr">
+        <is>
+          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="150" customHeight="1">
+      <c r="A61" s="3" t="inlineStr">
+        <is>
+          <t>unraous/uxuescript</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="n">
+        <v>170</v>
+      </c>
+      <c r="C61" s="5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="D61" s="6" t="inlineStr">
+        <is>
+          <t>提供学习通自动刷课脚本。
+【原文】学习通一键全自动刷课脚本，支持后台刷课、倍速播放、自动回答互动题目，截止 2026/09/09 可用。（免安装打包版已发布至Release）</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>未归类</t>
+        </is>
+      </c>
+      <c r="F61" s="3" t="inlineStr">
+        <is>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I61" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/unraous/uxuescript</t>
+        </is>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="L61" s="3" t="inlineStr">
+        <is>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O61" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>chaoxing, education, javascript, xuexitong</t>
+        </is>
+      </c>
+      <c r="Q61" s="3" t="inlineStr">
+        <is>
+          <t>2025-05-28</t>
+        </is>
+      </c>
+      <c r="R61" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="S61" s="3" t="n">
+        <v>469</v>
+      </c>
+      <c r="T61" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V61" s="6" t="inlineStr">
+        <is>
+          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="150" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>mofahuizhang/Gn</t>
+        </is>
+      </c>
+      <c r="B62" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="6" t="inlineStr">
+        <is>
+          <t>提供中医病机分析框架。
+【原文】Gn 通用病机分析框架——中医理论现代化、结构化与AI大模型结构复用</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>方剂知识线</t>
+        </is>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>架构参考</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t>https://github.com/mofahuizhang/Gn</t>
+        </is>
+      </c>
+      <c r="J62" s="3" t="inlineStr">
+        <is>
+          <t>估算(生涯日均×7)</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="3" t="inlineStr">
+        <is>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="O62" s="3" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="P62" s="6" t="inlineStr"/>
+      <c r="Q62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="R62" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="S62" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T62" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" s="3" t="inlineStr">
+        <is>
+          <t>chinese</t>
+        </is>
+      </c>
+      <c r="V62" s="6" t="inlineStr">
+        <is>
+          <t>中医 大模型 in:name,description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A2:V24"/>
+  <autoFilter ref="A2:V62"/>
   <mergeCells count="1">
     <mergeCell ref="A1:V1"/>
   </mergeCells>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -633,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>multica-ai/andrej-karpathy-skills</t>
+          <t>ruvnet/RuView</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>211865</v>
+        <v>92914</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>6591.3</v>
+        <v>1417</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>改进 Claude Code 行为的 CLAUDE.md 文件
-【原文】A single CLAUDE.md file to improve Claude Code behavior, derived from Andrej Karpathy's observations on LLM coding pitfalls.</t>
+          <t>将WiFi信号转换为实时空间智能、生命体征监测和存在检测
+【原文】π RuView turns commodity WiFi signals into real-time spatial intelligence, vital sign monitoring, and presence detection — all without a single pixel of video.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -655,12 +655,12 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H3" s="7" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/multica-ai/andrej-karpathy-skills</t>
+          <t>https://github.com/ruvnet/RuView</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,14 +679,18 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>941.62</v>
+        <v>202.43</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -697,22 +701,26 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P3" s="6" t="inlineStr"/>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>awesome, claude, densepose, esp32, firmware, home-assistant, home-automation, iot, monitoring, networking, npm, pose-estimation</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2025-06-07</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>225</v>
+        <v>459</v>
       </c>
       <c r="T3" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U3" s="3" t="inlineStr">
         <is>
@@ -721,42 +729,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>skill in:name,description stars:&gt;50000</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Player-YN/PawWork_ZhuaZhua</t>
+          <t>tinyhumansai/openhuman</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>2277</v>
+        <v>39576</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1328.2</v>
+        <v>1364.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Paw Work - Chrome浏览器选择优先的Web代理
-【原文】Paw Work - selection-first web agent for Chrome: select on the live page, describe the outcome, take away an editable office file. BYOK, sandboxed, no server.
-【依据】topics: ai-agent, browser-agent, chrome-extension, llm</t>
+          <t>开源个人AI，支持本地存储和代理编排
+【原文】OpenHuman is an open source personal AI for Mac, Windows and Linux — local-first memory, agent orchestration, and deep research.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>MCP服务/技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -766,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Player-YN/PawWork_ZhuaZhua</t>
+          <t>https://github.com/tinyhumansai/openhuman</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -775,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>189.75</v>
+        <v>194.96</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -799,12 +806,12 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, browser-agent, byok, chrome-extension, llm, pptx, tldraw, univer</t>
+          <t>agent-orchestration, ai-agents, ai-assistant, desktop, llm, local-first, mcp, personal-ai, privacy, rust, second-brain, tauri</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
@@ -813,7 +820,7 @@
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>12</v>
+        <v>203</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>1</v>
@@ -825,41 +832,42 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>bytedance/deer-flow</t>
+          <t>codecrafters-io/build-your-own-x</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>82135</v>
+        <v>546232</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1173.3</v>
+        <v>1255.7</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>开源长周期 SuperAgent 框架，用于研究和创建
-【原文】An open-source long-horizon SuperAgent harness that researches, codes, and creates. With the help of sandboxes, memories, tools, skill, subagents and message gateway, it handles different levels of tasks that could take minutes to hours.</t>
+          <t>编程技术教程
+【原文】Master programming by recreating your favorite technologies from scratch.
+【依据】programming, tutorial-code, tutorials</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考/可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -869,7 +877,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/bytedance/deer-flow</t>
+          <t>https://github.com/codecrafters-io/build-your-own-x</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -878,16 +886,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>167.62</v>
+        <v>179.39</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Markdown</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -902,21 +910,21 @@
       </c>
       <c r="P5" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic, agentic-framework, agentic-workflow, ai, ai-agents, deep-research, harness, langchain, langgraph, langmanus, llm</t>
+          <t>awesome-list, free, programming, tutorial-code, tutorial-exercises, tutorials</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>490</v>
+        <v>3045</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -928,36 +936,36 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>skill in:name,description stars:&gt;50000</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>genspark-ai/genoffice</t>
+          <t>truefoundry/trueforge</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>6304</v>
+        <v>5349</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1103.2</v>
+        <v>780.1</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供类似 Microsoft Office 的 AI 办公软件替代品。
-【原文】Free, open-source alternative to Microsoft Office with built-in AI agents — Word (.docx), Excel (.xlsx), PowerPoint (.pptx), PDF and Markdown editing for macOS, Windows &amp; Linux.</t>
+          <t>将LLM转换为工作代理的开源代理 harness
+【原文】The open-source agent harness - the runtime layer that turns an LLM into a working agent.</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -972,7 +980,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/genspark-ai/genoffice</t>
+          <t>https://github.com/truefoundry/trueforge</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -981,11 +989,11 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>157.6</v>
+        <v>111.44</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1005,12 +1013,12 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic, ai, ai-agent, ai-agents, ai-office, docx, excel, markdown-editor, microsoft-office, office, office-agent</t>
+          <t>agent, agentic-ai, agents, harness, harness-engineering</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
@@ -1019,53 +1027,54 @@
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Vincentwei1021/video-shotcraft</t>
+          <t>donnemartin/system-design-primer</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>7902</v>
+        <v>369020</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1063.7</v>
+        <v>741.9</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>为 Claude Code &amp; Codex 提供AI视频技能，制作产品视频
-【原文】AI video skill for Claude Code &amp; Codex — cinematic product videos with Remotion: 152 shot recipe cards, 209 motion previews, a production-ready template</t>
+          <t>系统设计学习资源
+【原文】Learn how to design large-scale systems. Prep for the system design interview.  Includes Anki flashcards.
+【依据】design, system, web-application</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1075,7 +1084,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Vincentwei1021/video-shotcraft</t>
+          <t>https://github.com/donnemartin/system-design-primer</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1084,16 +1093,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>151.96</v>
+        <v>105.98</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1108,21 +1117,21 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, ai-video, claude-code, claude-code-skills, claude-skills, codex, motion-design, motion-graphics, product-video, promo-video, remotion</t>
+          <t>design, design-patterns, design-system, development, interview, interview-practice, interview-questions, programming, python, system, web, web-application</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2017-02-26</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>52</v>
+        <v>3482</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1134,40 +1143,42 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>yang0/handraw-style</t>
+          <t>996icu/996.ICU</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>604</v>
+        <v>276933</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1057</v>
+        <v>711.6</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供手绘风格编号画廊与双语提示词 Skill</t>
+          <t>统计贡献者仓库
+【原文】Repo for counting stars and contributing. Press F to pay respect to glorious developers.
+【依据】-</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1177,7 +1188,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yang0/handraw-style</t>
+          <t>https://github.com/996icu/996.ICU</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1186,18 +1197,14 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>151</v>
+        <v>101.66</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>HTML</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr"/>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1211,47 +1218,48 @@
       <c r="P8" s="6" t="inlineStr"/>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2019-03-26</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>4</v>
+        <v>2724</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>MDX-Tom/gpt-instruct</t>
+          <t>jwasham/coding-interview-university</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>7940</v>
+        <v>360645</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>926.3</v>
+        <v>673.8</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>提供针对 gpt 系列的 Codex 破甲提示词与测试包
-【原文】A Codex jailbreak prompt and test pack for gpt. 针对 gpt 系列的 Codex 破甲提示词与测试包。</t>
+          <t>软件工程师学习计划
+【原文】A complete computer science study plan to become a software engineer.
+【依据】algorithm, coding-interview, software-engineering</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1261,12 +1269,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1276,7 +1284,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MDX-Tom/gpt-instruct</t>
+          <t>https://github.com/jwasham/coding-interview-university</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1285,18 +1293,14 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>132.33</v>
+        <v>96.25</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>CC-BY-SA-4.0</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr"/>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1307,50 +1311,55 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>algorithm, algorithms, coding-interview, coding-interviews, computer-science, data-structures, interview, interview-prep, interview-preparation, programming-interviews, software-engineering, study-plan</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2016-06-06</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>60</v>
+        <v>3747</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>EvoLinkAI/awesome-gpt-image-2-API-and-Prompts</t>
+          <t>trimstray/the-book-of-secret-knowledge</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>17139</v>
+        <v>242884</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>833.1</v>
+        <v>566.7</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供 GPT-Image-2 API 和提示词
-【原文】GPT-Image-2 API and Prompts</t>
+          <t>收集技术资源列表
+【原文】A collection of inspiring lists, manuals, cheatsheets, blogs, hacks, one-liners, cli/web tools and more.
+【依据】awesome, cheatsheets, devops</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1360,7 +1369,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1375,7 +1384,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/EvoLinkAI/awesome-gpt-image-2-API-and-Prompts</t>
+          <t>https://github.com/trimstray/the-book-of-secret-knowledge</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1384,18 +1393,14 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>119.02</v>
+        <v>80.95999999999999</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>CC0-1.0</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M10" s="3" t="inlineStr"/>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1408,21 +1413,21 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>ai-art, api, awesome-list, awesome-lists, chatgpt, creative-tools, generative-ai, gpt-image-2, gpt-image-2-api, gpt-image-2-prompts, gptimage2, image-generation</t>
+          <t>awesome, awesome-list, bsd, cheatsheets, devops, guidelines, hacking, hacks, howtos, linux, lists, manuals</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2018-06-23</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2024-11-19</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>144</v>
+        <v>3000</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1434,26 +1439,27 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>hacksider/Deep-Live-Cam</t>
+          <t>massgravel/Microsoft-Activation-Scripts</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>96578</v>
+        <v>189923</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>625.4</v>
+        <v>546.6</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>实现实时面部交换和一键视频深度伪造
-【原文】real time face swap and one-click video deepfake with only a single image</t>
+          <t>Windows 和 Office 激活脚本
+【原文】Open-source Windows and Office activator featuring HWID, Ohook, TSforge, and Online KMS activation methods, along with advanced troubleshooting.
+【依据】activator, hwid, kms</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
@@ -1463,7 +1469,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1478,7 +1484,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hacksider/Deep-Live-Cam</t>
+          <t>https://github.com/massgravel/Microsoft-Activation-Scripts</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1487,16 +1493,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>89.34</v>
+        <v>78.09</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Batchfile</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1511,21 +1517,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-deep-fake, ai-face, ai-webcam, artificial-intelligence, deep-fake, deepfake, deepfake-webcam, faceswap, fake-webcam, gan, real-time-deepfake</t>
+          <t>activator, hwid, kms, kms38, massgrave, massgravel, microsoft, microsoft365, office, office365, ohook, powershell</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2023-09-24</t>
+          <t>2020-01-12</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1081</v>
+        <v>2432</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1537,26 +1543,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>unslothai/unsloth</t>
+          <t>charmbracelet/crush</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>75948</v>
+        <v>27978</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>523.8</v>
+        <v>411.5</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>提供本地 UI 运行和训练 LLMs 和扩散模型。
-【原文】Local UI to run and train LLMs and diffusion models. Supports GGUF, MLX, Qwen3.8, DeepSeek-V4, MiniMax-H3, Gemma 4, FLUX and more.</t>
+          <t>用于所有AI代理的华丽编码工具
+【原文】Glamourous agentic coding for all 💘</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1566,12 +1572,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1581,7 +1587,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/unslothai/unsloth</t>
+          <t>https://github.com/charmbracelet/crush</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1590,16 +1596,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>74.83</v>
+        <v>58.78</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1614,12 +1620,12 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, chatgpt, deepseek, fine-tuning, gemma, image-generation, llama, llm, llms, openai, python</t>
+          <t>agentic-ai, ai, llms, ravishing</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2023-11-29</t>
+          <t>2025-05-21</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
@@ -1628,7 +1634,7 @@
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>1015</v>
+        <v>476</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1640,40 +1646,41 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>yilujian/easy-writing</t>
+          <t>ZJU-REAL/Easel</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>506</v>
+        <v>700</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>393.5</v>
+        <v>408.3</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>纯本地、开源的 AI 网文写作桌面软件</t>
+          <t>社交媒体AI智能体，用于内容创作和发布
+【原文】An open-source AI agent for social media — discover trends, create content, publish everywhere, and learn what works across Xiaohongshu, Douyin, Zhihu, Bilibili, and more.🎨一个开源的 AI 社交媒体智能体——发现热点趋势、创作内容、一键发布至各大平台，并学习分析哪些内容真正有效，覆盖小红书、抖音、知乎、哔哩哔哩等平台。</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>视频产线/未归类</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>MCP服务/技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1683,7 +1690,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yilujian/easy-writing</t>
+          <t>https://github.com/ZJU-REAL/Easel</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1692,16 +1699,16 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>56.22</v>
+        <v>58.33</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -1716,21 +1723,21 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>ai-writing, ai-writing-assistant, byok, creative-writing, desktop-app, local-first, novel-writing, openai-compatible, tauri, vue3, web-novel, writing-tools</t>
+          <t>agent, agent-skill, content-automation, content-creation, content-generation, mcp, openclaw, social-media, social-media-management</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1742,36 +1749,36 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>nexu-io/html-video</t>
+          <t>run-llama/liteparse</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>4559</v>
+        <v>12278</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>303.9</v>
+        <v>405.4</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>将 HTML、CSS 和数据转换为 MP4 视频的编程工具
-【原文】Programmatic video for coding agents — HTML to video on your laptop. Turn HTML, CSS &amp; data into real MP4s with pluggable render engines, 21 templates, AI soundtrack. Apache-2.0, no per-render fees. An official project by the Open Design team.</t>
+          <t>快速、有用的开源文档解析器
+【原文】A fast, helpful, and open-source document parser</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1786,7 +1793,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/nexu-io/html-video</t>
+          <t>https://github.com/run-llama/liteparse</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1795,7 +1802,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>43.42</v>
+        <v>57.92</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1804,7 +1811,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1819,21 +1826,21 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, apache-2, coding-agent, css, ffmpeg, html, html-to-video, hyperframes, mp4, open-design, open-source, programmatic-video</t>
+          <t>document-ocr, document-processing, ocr, ocr-recognition, pdf, pdf-parser, text-extraction</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>105</v>
+        <v>212</v>
       </c>
       <c r="T14" s="3" t="n">
         <v>1</v>
@@ -1845,26 +1852,27 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>florinpop17/app-ideas</t>
+          <t>op7418/guizang-yingzao-skill</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>97431</v>
+        <v>396</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>247.7</v>
+        <v>396</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>收集应用想法以提升编码技能
-【原文】A Collection of application ideas which can be used to improve your coding skills.</t>
+          <t>将中国古建筑和文化照片转换为艺术海报
+【原文】🏯 Claude Code / Codex skill — transform Chinese architecture, cultural places &amp; travel photos into art-directed editorial posters with GPT Image. 中国古建筑与在地文化照片 → 艺术指导海报
+【依据】agent-skill, ai-agent, image-generation</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -1874,12 +1882,12 @@
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1889,7 +1897,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/florinpop17/app-ideas</t>
+          <t>https://github.com/op7418/guizang-yingzao-skill</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1898,14 +1906,18 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>35.39</v>
+        <v>56.57</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M15" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1918,21 +1930,21 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>applications, coding, codingchallenges, css, hacktoberfest, html, ideas, javascript, practice</t>
+          <t>agent-skill, ai-agent, anthropic, chinese-architecture, chinese-culture, claude-code, claude-skill, codex, cultural-heritage, editorial-design, gpt-image, image-generation</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2019-02-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2025-10-11</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>2753</v>
+        <v>7</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
@@ -1944,40 +1956,42 @@
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>skill in:name,description stars:&gt;50000</t>
+          <t>topic:xiaohongshu stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>LancelotRar/best-cf-ips</t>
+          <t>HKUDS/LightRAG</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1159</v>
+        <v>39517</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>165.5</v>
+        <v>391.2</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供自动更新的 Cloudflare 优选 IP API</t>
+          <t>提供简单快速的检索增强生成模型
+【原文】[EMNLP2025] LightRAG: Simple and Fast Retrieval-Augmented Generation
+【依据】topics: retrieval-augmented-generation</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1987,7 +2001,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LancelotRar/best-cf-ips</t>
+          <t>https://github.com/HKUDS/LightRAG</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -1996,14 +2010,18 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>23.65</v>
+        <v>55.89</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M16" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2014,10 +2032,14 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P16" s="6" t="inlineStr"/>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>docling, genai, gpt, graphrag, knowledge-graph, large-language-models, llm, mineru, rag, ragas, retrieval-augmented-generation</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
@@ -2026,48 +2048,49 @@
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>49</v>
+        <v>707</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>HKUDS/ViMax</t>
+          <t>ossu/computer-science</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>12313</v>
+        <v>208873</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>163.2</v>
+        <v>324.1</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>全功能视频生成系统，包括导演、编剧、制片人和视频生成
-【原文】"ViMax: Agentic Video Generation (Director, Screenwriter, Producer, and Video Generator All-in-One)"</t>
+          <t>计算机科学学习路径
+【原文】🎓 Path to a free self-taught education in Computer Science!
+【依据】computer-science, courses, curriculum</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2082,7 +2105,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HKUDS/ViMax</t>
+          <t>https://github.com/ossu/computer-science</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2091,7 +2114,7 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>23.32</v>
+        <v>46.3</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2100,7 +2123,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2115,21 +2138,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>agentic-aigc, video-generation</t>
+          <t>awesome-list, computer-science, courses, curriculum</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2025-03-30</t>
+          <t>2014-05-04</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>528</v>
+        <v>4511</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2141,37 +2164,37 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Anil-matcha/Open-Generative-AI</t>
+          <t>vuejs/vue</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>28193</v>
+        <v>212027</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>161.9</v>
+        <v>309.8</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>开源AI视频平台替代品，提供图像和视频生成
-【原文】Unrestricted Open-source alternative to AI video platforms — Free AI image &amp; video generation studio with 600+ models (Flux, Midjourney, Kling, Sora, Veo). No content filters. Self-hosted, MIT licensed.
-【依据】topics: ai-art-generator, ai-image-generation, ai-video-generation, creative-tools, image-to-video</t>
+          <t>Vue.js 框架仓库
+【原文】This is the repo for Vue 2. For Vue 3, go to https://github.com/vuejs/core
+【依据】framework, frontend, javascript</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2186,7 +2209,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Anil-matcha/Open-Generative-AI</t>
+          <t>https://github.com/vuejs/vue</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2195,7 +2218,7 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>23.13</v>
+        <v>44.26</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2204,7 +2227,7 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2219,24 +2242,24 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>ai-art-generator, ai-image-generation, ai-video-generation, creative-tools, fal-ai-alternative, generative-ai, image-to-video, invideo-alternative, javascript, kling-ai, lipsync, midjourney-alternative</t>
+          <t>framework, frontend, javascript, vue</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2023-05-09</t>
+          <t>2013-07-29</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-10-10</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>1219</v>
+        <v>4790</v>
       </c>
       <c r="T18" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
@@ -2245,36 +2268,36 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>3b1b/manim</t>
+          <t>google/adk-python</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>93637</v>
+        <v>21470</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>156.5</v>
+        <v>285.7</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>用于制作解释性数学视频的动画引擎
-【原文】Animation engine for explanatory math videos</t>
+          <t>构建、评估和部署复杂AI代理的Python工具包
+【原文】An open-source, code-first Python toolkit for building, evaluating, and deploying sophisticated AI agents with flexibility and control.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2289,7 +2312,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/3b1b/manim</t>
+          <t>https://github.com/google/adk-python</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2298,11 +2321,11 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>22.35</v>
+        <v>40.82</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2322,12 +2345,12 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>3b1b-videos, animation, explanatory-math-videos, python</t>
+          <t>agent, agentic, agentic-ai, agents, agents-sdk, ai, ai-agents, aiagentframework, genai, genai-chatbot, llm, llms</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2015-03-22</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
@@ -2336,7 +2359,7 @@
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>4189</v>
+        <v>526</v>
       </c>
       <c r="T19" s="3" t="n">
         <v>1</v>
@@ -2348,36 +2371,36 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>huggingface/diffusers</t>
+          <t>alvinunreal/oh-my-opencode-slim</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>34475</v>
+        <v>8751</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>154.4</v>
+        <v>258.4</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>提供 PyTorch 中的图像、视频和音频生成模型
-【原文】🤗 Diffusers: State-of-the-art diffusion models for image, video, and audio generation in PyTorch.</t>
+          <t>精调的Opencode多代理套件，混合任何模型
+【原文】Lean, fine tuned Opencode multi agent suite · Mix any models · Auto delegate tasks</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>视频产线/图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2392,7 +2415,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huggingface/diffusers</t>
+          <t>https://github.com/alvinunreal/oh-my-opencode-slim</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2401,16 +2424,16 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>22.06</v>
+        <v>36.92</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
@@ -2425,12 +2448,12 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>deep-learning, diffusion, flux, image-generation, image2image, image2video, latent-diffusion-models, pytorch, qwen-image, score-based-generative-modeling, stable-diffusion, stable-diffusion-diffusers</t>
+          <t>agentic-ai, antigravity, cerebras, herdr-plugin, oh-my-opencode, opencode, orchestration</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2022-05-30</t>
+          <t>2026-01-15</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
@@ -2439,10 +2462,10 @@
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>1563</v>
+        <v>237</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
@@ -2451,26 +2474,26 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>khoj-ai/khoj</t>
+          <t>Asabeneh/30-Days-Of-Python</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>37229</v>
+        <v>73264</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>140.8</v>
+        <v>206.3</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供个人 AI 助手，可自托管。
-【原文】Your AI second brain. Self-hostable. Get answers from the web or your docs. Build custom agents, schedule automations, do deep research. Turn any online or local LLM into your personal, autonomous AI (gpt, claude, gemini, llama, qwen, mistral). Get started - free.</t>
+          <t>提供Python编程挑战的指南和视频
+【原文】The 30 Days of Python programming challenge is a step-by-step guide to learn the Python programming language in 30 days. This challenge may take more than 100 days. Follow your own pace. These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2480,12 +2503,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G21" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2495,7 +2518,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/khoj-ai/khoj</t>
+          <t>https://github.com/Asabeneh/30-Days-Of-Python</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2504,11 +2527,11 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>20.12</v>
+        <v>29.47</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
@@ -2528,21 +2551,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, assistant, chat, chatgpt, emacs, image-generation, llama3, llamacpp, llm, obsidian, obsidian-md</t>
+          <t>30-days-of-python, data, data-science, database, flask, fullstack, github, heroku, matplotlib, ml, mongodb, numpy</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2021-08-16</t>
+          <t>2019-11-19</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>1850</v>
+        <v>2486</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2554,26 +2577,26 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Robbyant/lingbot-world</t>
+          <t>ChenShuo2004/cs-board</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>4423</v>
+        <v>541</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>138.2</v>
+        <v>199.3</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>推进开源世界模型的发展
-【原文】Advancing Open-source World Models</t>
+          <t>生成白板动画视频的AI工具
+【原文】将参考声音和中文文案自动生成白板动画视频的本地 AI 工具。</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2598,7 +2621,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Robbyant/lingbot-world</t>
+          <t>https://github.com/ChenShuo2004/cs-board</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2607,11 +2630,11 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>19.75</v>
+        <v>28.47</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2631,67 +2654,68 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>aigc, image-to-video, lingbot-world, video-generation, world-models</t>
+          <t>ai-video, chinese, fastapi, index-tts, react, tts, whiteboard-animation</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>224</v>
+        <v>19</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Tencent-Hunyuan/HunyuanVideo</t>
+          <t>topoteretes/cognee</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>12508</v>
+        <v>30607</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>134.7</v>
+        <v>191.3</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>大型视频生成模型系统框架
-【原文】HunyuanVideo: A Systematic Framework For Large Video Generation Model</t>
+          <t>为AI代理提供持久长期记忆的知识图谱引擎
+【原文】Cognee is the open-source AI memory platform for agents. Give your AI agents persistent long-term memory across sessions with a self-hosted knowledge graph engine.
+【依据】topics: cognitive-architecture, cognitive-memory</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H23" s="7" t="inlineStr">
@@ -2701,7 +2725,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent-Hunyuan/HunyuanVideo</t>
+          <t>https://github.com/topoteretes/cognee</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2710,11 +2734,11 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>19.24</v>
+        <v>27.33</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
@@ -2734,21 +2758,21 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>diffusion-models, diffusion-transformer, video-generation</t>
+          <t>agent-memory, agent-skills, ai, ai-agents, ai-memory, cognitive-architecture, cognitive-memory, context-engineering, contributions-welcome, good-first-issue, good-first-pr, graph-database</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2023-08-16</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>650</v>
+        <v>1120</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2760,36 +2784,36 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>invoke-ai/InvokeAI</t>
+          <t>microsoft/agent-framework</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>28173</v>
+        <v>13436</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>132.9</v>
+        <v>188.5</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>提供 Stable Diffusion 模型的创意引擎
-【原文】Invoke is a leading creative engine for Stable Diffusion models, empowering professionals, artists, and enthusiasts to generate and create visual media using the latest AI-driven technologies. The solution offers an industry leading WebUI, and serves as the foundation for multiple commercial products.</t>
+          <t>构建、编排和部署AI代理和多代理工作流的框架
+【原文】A framework for building, orchestrating and deploying AI agents and multi-agent workflows with support for Python and .NET.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库/技能包</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2804,7 +2828,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/invoke-ai/InvokeAI</t>
+          <t>https://github.com/microsoft/agent-framework</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2813,11 +2837,11 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>18.98</v>
+        <v>26.93</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
@@ -2837,21 +2861,21 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>ai-art, artificial-intelligence, generative-art, image-generation, img2img, inpainting, latent-diffusion, linux, macos, outpainting, stable-diffusion, txt2img</t>
+          <t>agent-framework, agentic-ai, agents, ai, dotnet, multi-agent, orchestration, python, sdk, workflows</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2022-08-17</t>
+          <t>2025-04-28</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>1484</v>
+        <v>499</v>
       </c>
       <c r="T24" s="3" t="n">
         <v>1</v>
@@ -2863,41 +2887,41 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>oritera/Cairn</t>
+          <t>remotion-dev/remotion</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>2709</v>
+        <v>58732</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>132.6</v>
+        <v>181.2</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 辅助的渗透测试工具。
-【原文】A AI general-purpose state-space search engine, validated first on autonomous penetration testing.</t>
+          <t>使用React编程方式制作视频
+【原文】🎥      Make videos programmatically with React</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
-        </is>
-      </c>
-      <c r="G25" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2907,7 +2931,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/oritera/Cairn</t>
+          <t>https://github.com/remotion-dev/remotion</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2916,16 +2940,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>18.94</v>
+        <v>25.88</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2940,53 +2964,52 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agent, ai-cybersecurity, ai-hacker, ai-hacking, blackbox-testing, ctf, ctf-tools, llm, penetration-testing, pentesting, red-teaming</t>
+          <t>javascript, react, video</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19</t>
+          <t>2020-06-23</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>143</v>
+        <v>2269</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>ciembor/agent-rules-books</t>
+          <t>Developer-Y/cs-video-courses</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>2732</v>
+        <v>83456</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>131</v>
+        <v>161.8</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>AI编码代理的规则/技能
-【原文】AGENTS.md rules / skills for AI coding agents: Codex, Cursor &amp; Claude Code. Inspired by Clean Code, Refactoring, DDD, Clean Architecture and DDIA programming books.
-【依据】topics: agent-rules, agent-skills, claude-code, claude-code-skills</t>
+          <t>提供计算机科学课程视频讲座列表
+【原文】List of Computer Science courses with video lectures.</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
@@ -2996,12 +3019,12 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3011,7 +3034,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ciembor/agent-rules-books</t>
+          <t>https://github.com/Developer-Y/cs-video-courses</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3020,11 +3043,11 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>18.71</v>
+        <v>23.12</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr"/>
@@ -3040,62 +3063,62 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>agent-rules, agent-skills, agent-skills-manager, agents-md, agents-rules, agents-skills, agentsmd, ai-agent, ai-skills, claude-code, claude-code-skills, code-quality</t>
+          <t>algorithms, bioinformatics, computational-biology, computational-physics, computer-architecture, computer-science, computer-vision, database-systems, databases, deep-learning, embedded-systems, machine-learning</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2016-10-21</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>146</v>
+        <v>3610</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>vllm-project/vllm-omni</t>
+          <t>OpenPipe/ART</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>6739</v>
+        <v>10707</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>129.9</v>
+        <v>136.8</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>高效模型推理框架，支持多种模态模型
-【原文】A framework for efficient model inference with omni-modality models</t>
+          <t>训练多步骤代理用于现实任务，支持多种LLM
+【原文】Agent Reinforcement Trainer: train multi-step agents for real-world tasks using GRPO. Give your agents on-the-job training. Reinforcement learning for Qwen3.6, GPT-OSS, Llama, and more!</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3110,7 +3133,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vllm-project/vllm-omni</t>
+          <t>https://github.com/OpenPipe/ART</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3119,7 +3142,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>18.56</v>
+        <v>19.54</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3143,12 +3166,12 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>audio-generation, diffusion, image-generation, inference, model-serving, multimodal, pytorch, transformer, video-generation, world-model</t>
+          <t>agent, agentic-ai, grpo, llms, lora, qwen, qwen3, reinforcement-learning, rl</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2025-09-11</t>
+          <t>2025-03-10</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
@@ -3157,10 +3180,10 @@
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>363</v>
+        <v>548</v>
       </c>
       <c r="T27" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
@@ -3169,27 +3192,26 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>FailproofAI/failproofai</t>
+          <t>Asabeneh/30-Days-Of-JavaScript</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>2526</v>
+        <v>46776</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>113.3</v>
+        <v>133.6</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>AI代理可观察性和执行策略
-【原文】Observability and enforcement for AI agent harnesses. Capture every run and runtime reliability with policy enforcement.  40 built-in policies, a local dashboard, no account required with a generous free cloud plan
-【依据】topics: agent-failure, agent-harness, agent-observability, agent-reliability</t>
+          <t>提供JavaScript编程挑战的指南和视频
+【原文】30 days of JavaScript programming challenge is a step-by-step guide to learn JavaScript programming language in 30 days. This challenge may take more than 100 days,  please just follow your own pace. These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -3199,12 +3221,12 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -3214,7 +3236,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FailproofAI/failproofai</t>
+          <t>https://github.com/Asabeneh/30-Days-Of-JavaScript</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3223,16 +3245,16 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>16.19</v>
+        <v>19.08</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>MDX</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3247,52 +3269,53 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>agent-failure, agent-harness, agent-observability, agent-reliability, agent-tracing, ai-agent, claude-code, codex, enforcement, evals, guardrails, hermes</t>
+          <t>30daysofjavascript, angular, challenge, css, d3, d3js, html, javascript, javascript-for-everyone, js, json, node</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2019-12-23</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>156</v>
+        <v>2452</v>
       </c>
       <c r="T28" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>peter123023/awesome-free-llm-api</t>
+          <t>agentpit-io/hunter-community</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>110</v>
+        <v>497</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>96.2</v>
+        <v>116</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>导航免费大模型 API
-【原文】免费大模型 API 导航 · 只收录能通过 API Key 和 endpoint 调用的永久免费 / 限时免费接口｜A curated list of free LLM APIs — permanently free tiers and limited-time free models, all callable via API key and endpoint. Channel-first, with a model index for DeepSeek, GLM, Qwen and more</t>
+          <t>私人金融AI团队，提供AI智能体和AI量化服务
+【原文】Hunter Community Edition · 私人金融 AI 团队 · AI 智能体 + AI 量化 · 开源自托管 · powered by opencode + Claude Code + MCP + multi-agent · your private financial AI team · open-source self-hosted · 15 min docker start
+【依据】AI智能体 + AI量化 · 开源自托管 · 15 min docker start</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
@@ -3317,7 +3340,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/peter123023/awesome-free-llm-api</t>
+          <t>https://github.com/agentpit-io/hunter-community</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3326,14 +3349,18 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>13.75</v>
+        <v>16.57</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M29" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3344,19 +3371,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P29" s="6" t="inlineStr"/>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>ai-agents, ai-hedge-fund, ai-quant, anthropic, apache-2, claude-agent-sdk, claude-code, codex, docker-compose, financial-ai, fintech, llm-agent</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
@@ -3368,27 +3399,26 @@
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVlabs/Sana</t>
+          <t>yifanfeng97/Hyper-Extract</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>9018</v>
+        <v>3925</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>90.40000000000001</v>
+        <v>112.1</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>基于线性扩散变换器的图像合成系统
-【原文】SANA: Efficient High-Resolution Image Synthesis with Linear Diffusion Transformer
-【依据】topics: diffusion, dit, linear-transformer, pytorch, text-to-image-generation</t>
+          <t>将文本转换为结构化知识的工具
+【原文】Hypergraph is more powerful. Transform unstructured text into structured knowledge with LLMs. Graphs, hypergraphs, and spatio-temporal extractions — with one command.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
@@ -3398,12 +3428,12 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -3413,7 +3443,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NVlabs/Sana</t>
+          <t>https://github.com/yifanfeng97/Hyper-Extract</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3422,11 +3452,11 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>12.92</v>
+        <v>16.02</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3446,12 +3476,12 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>diffusion, dit, linear-transformer, nvfp4, pytorch, reinforcement-learning, sana, streaming-video, system-algorithm-deisgn, text-to-image-generation, text-to-video, transformers</t>
+          <t>ai, ai-agents, cli, hypergraph, information-extraction, knowledge, knowledge-graph, llm, python, rag</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
@@ -3460,10 +3490,10 @@
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>698</v>
+        <v>245</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
@@ -3472,36 +3502,36 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GVCLab/PersonaLive</t>
+          <t>thu-ml/TurboDiffusion</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>3690</v>
+        <v>3639</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>89.7</v>
+        <v>92</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>生成直播中的表情丰富的肖像图像动画
-【原文】[CVPR 2026] PersonaLive! : Expressive Portrait Image Animation for Live Streaming</t>
+          <t>加速视频扩散模型
+【原文】TurboDiffusion: 100–200× Acceleration for Video Diffusion Models</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3516,7 +3546,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GVCLab/PersonaLive</t>
+          <t>https://github.com/thu-ml/TurboDiffusion</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3525,7 +3555,7 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>12.81</v>
+        <v>13.14</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -3549,21 +3579,21 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>cvpr, cvpr2026, talking-head, video-generation</t>
+          <t>ai-infra, consistency-model, diffusion-models, distillation, inference-acceleration, mlsystem, rcm, sageattention, sparse-linear-attention, video-generation</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-12-06</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3582,34 +3612,34 @@
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>jujumilk3/leaked-system-prompts</t>
+          <t>iina/iina</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>14924</v>
+        <v>46280</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>86.2</v>
+        <v>91.2</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>收集泄露的系统提示词
-【原文】Collection of leaked system prompts</t>
+          <t>为macOS提供现代视频播放器
+【原文】The modern video player for macOS.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G32" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -3619,7 +3649,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jujumilk3/leaked-system-prompts</t>
+          <t>https://github.com/iina/iina</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3628,14 +3658,18 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>12.31</v>
+        <v>13.03</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr"/>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3648,21 +3682,21 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>ai, document, llm, prompt</t>
+          <t>hacktoberfest, macos, mpv, swift, video, video-player</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>2016-12-19</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>1212</v>
+        <v>3551</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3674,41 +3708,42 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>prompts in:name stars:&gt;300 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>PKU-YuanGroup/Helios</t>
+          <t>TriliumNext/Trilium</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>2143</v>
+        <v>37775</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>78.5</v>
+        <v>77.8</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>提供实时长视频生成模型。
-【原文】Helios: Real Real-Time Long Video Generation Model</t>
+          <t>构建个人知识库
+【原文】Build your personal knowledge base with Trilium Notes
+【依据】knowledge-base, knowledge-graph, knowledge-management</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G33" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3718,7 +3753,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/PKU-YuanGroup/Helios</t>
+          <t>https://github.com/TriliumNext/Trilium</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3727,16 +3762,16 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>11.22</v>
+        <v>11.12</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3751,21 +3786,21 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>acceleration, diffusion, diffusion-model, diffusion-models, efficient-tuning, high-quality, image-to-video, image2video, interactive, long-context, long-video-generation, real-time</t>
+          <t>electron, electron-app, knowledge-base, knowledge-graph, knowledge-management, knowledge-management-graph, local-first, note-managment, note-taker, note-taking, notebook, notes</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2017-05-23</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>191</v>
+        <v>3396</v>
       </c>
       <c r="T33" s="3" t="n">
         <v>1</v>
@@ -3777,41 +3812,41 @@
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>zjp1997720/zhijian-ai-bluebook-workbuddy-harness</t>
+          <t>2FastLabs/agent-squad</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>204</v>
+        <v>7757</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>59.5</v>
+        <v>69.8</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>拆解 WorkBuddy 的提示词、记忆、插件等
-【原文】智见 AI 蓝皮书：拆解 WorkBuddy 的提示词、记忆、插件、专家、Skill 与安全边界。</t>
+          <t>管理多个AI代理和复杂对话的灵活框架
+【原文】Flexible and powerful framework for managing multiple AI agents and handling complex conversations</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H34" s="7" t="inlineStr">
@@ -3821,7 +3856,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zjp1997720/zhijian-ai-bluebook-workbuddy-harness</t>
+          <t>https://github.com/2FastLabs/agent-squad</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3830,14 +3865,18 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>8.5</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>Swift</t>
+        </is>
+      </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3850,62 +3889,63 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, bluebook, harness, workbuddy, zhijian-ai</t>
+          <t>agentic-ai, agents, ai-agents, ai-agents-framework, anthropic, anthropic-claude, aws, aws-bedrock, aws-cdk, aws-lambda, chatbot, framework</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2024-07-23</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>24</v>
+        <v>778</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>vercel/satori</t>
+          <t>mex-memory/mex</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>13927</v>
+        <v>1572</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>57.8</v>
+        <v>64</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>将 HTML 和 CSS 转换为 SVG
-【原文】Enlightened library to convert HTML and CSS to SVG</t>
+          <t>为工程师和他们的AI代理提供团队记忆
+【原文】Team memory for engineers and their AI agents. Lives in your repo. Shared through Git.
+【依据】topics: knowledge-graph</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3920,7 +3960,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vercel/satori</t>
+          <t>https://github.com/mex-memory/mex</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3929,11 +3969,11 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>8.26</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>MPL-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
@@ -3953,21 +3993,21 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>css, image, image-generation, image-generator, jsx, opengraph-images, satori, svg, vercel</t>
+          <t>claude-code, claude-code-skills, cli-tool, code-graph, codex, context-management, cursor, developer-tools, documentation, knowledge-graph, llm, mcp-server</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2022-01-27</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>1686</v>
+        <v>172</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
@@ -3979,42 +4019,42 @@
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>digitalsamba/claude-code-video-toolkit</t>
+          <t>axoviq-ai/synthadoc</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>2061</v>
+        <v>1175</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>52.6</v>
+        <v>54.5</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>AI原生视频生产工具包，支持Claude Code
-【原文】AI-native video production toolkit for Claude Code
-【依据】topics: ai-video-generator, claude-code, programmatic-video, text-to-speech, video-editing</t>
+          <t>将原始文档转换为结构化、本地优先的维基百科
+【原文】Synthadoc: An open-source LLM knowledge compilation engine that turns raw documents into structured, local-first wikis. A transparent, human-readable alternative to traditional RAG, which can be self-managed and self-improved without the use of any tools.
+【依据】topics: knowledge-graph</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -4024,7 +4064,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/digitalsamba/claude-code-video-toolkit</t>
+          <t>https://github.com/axoviq-ai/synthadoc</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4033,11 +4073,11 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>7.52</v>
+        <v>7.78</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
@@ -4057,21 +4097,21 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>ai-video-generator, claude-code, developer-tools, elevenlabs, open-source, openclaw, playwright, programmatic-video, qwen-tts, remotion, text-to-speech, video-editing</t>
+          <t>agent-skills, agentic-ai, cli-tool, domain-adaptation, enterprise, enterprise-solutions, knowledge-graph, local-llm, obsidian-md, obsidian-plugin, personal-knowledge-management, pkm</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>274</v>
+        <v>151</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
@@ -4083,31 +4123,32 @@
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>topic:ai-video-generator stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>SandAI-org/MAGI-1</t>
+          <t>ModernRelay/omnigraph</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>3782</v>
+        <v>1102</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>52.3</v>
+        <v>50.8</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>实现大规模自回归视频生成
-【原文】MAGI-1: Autoregressive Video Generation at Scale</t>
+          <t>提供湖屋原生图引擎，支持git-style workflows
+【原文】Lakehouse native graph engine with git-style workflows
+【依据】topics: knowledge-graph, lakehouse</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -4127,7 +4168,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/SandAI-org/MAGI-1</t>
+          <t>https://github.com/ModernRelay/omnigraph</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4136,16 +4177,16 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>7.47</v>
+        <v>7.25</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -4160,21 +4201,21 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>autoregressive, diffusion-models, video-generation</t>
+          <t>apache-arrow, context-graph, datafusion, graph-database, knowledge-graph, lakehouse, lance, mcp, rust, s3, versioning</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>506</v>
+        <v>152</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -4186,42 +4227,42 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Feelingeouncouple/Canva-Professional</t>
+          <t>videojs/video.js</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>598</v>
+        <v>39880</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>48.1</v>
+        <v>46.8</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Canva Pro云端工具包与自动化工作室
-【原文】Canva Pro Cloud Toolkit &amp; Automation Studio. Advanced graphic design assets, team collaboration workflows, premium template management, and visual content creation tools.
-【依据】topics: canva-app, canva-editor-tools, canva-export-tools, canva-free, canva-pro</t>
+          <t>提供HTML5视频播放功能
+【原文】Video.js - open source HTML5 video player
+【依据】topics: video-player</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -4231,7 +4272,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Feelingeouncouple/Canva-Professional</t>
+          <t>https://github.com/videojs/video.js</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4240,14 +4281,18 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>6.87</v>
+        <v>6.69</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M38" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4260,21 +4305,21 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>canva-app, canva-bulk-create, canva-editor-tools, canva-export-tools, canva-free, canva-full, canva-hack, canva-pro, canva-pro-team-2026, followers-ig, social-media-app, social-media-design</t>
+          <t>dash, hls, html, html5, html5-audio, html5-video, javascript, player, video, video-player, videojs</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2010-05-14</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>87</v>
+        <v>5962</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
@@ -4286,26 +4331,27 @@
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>content automation in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>hao-ai-lab/FastVideo</t>
+          <t>jitsi/jitsi-meet</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>4363</v>
+        <v>29895</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>44.6</v>
+        <v>45</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>加速视频生成的统一推理和后训练框架
-【原文】A unified inference and post-training framework for accelerated video generation.</t>
+          <t>提供安全、简单且可扩展的视频会议服务
+【原文】Jitsi Meet - Secure, Simple and Scalable Video Conferences that you use as a standalone app or embed in your web application.
+【依据】topics: video-conferencing</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4315,7 +4361,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4330,7 +4376,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/hao-ai-lab/FastVideo</t>
+          <t>https://github.com/jitsi/jitsi-meet</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4339,7 +4385,7 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>6.37</v>
+        <v>6.43</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
@@ -4348,7 +4394,7 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4363,21 +4409,21 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>diffusers, diffusion-models, distillation, inference, post-training, video-generation</t>
+          <t>debian, deep-video, jitsi, jitsi-meet, scalable-video-conferences, sfu, video, video-communication, video-conferencing, webrtc</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2024-10-24</t>
+          <t>2013-12-16</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>685</v>
+        <v>4650</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4389,41 +4435,41 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>leejet/stable-diffusion.cpp</t>
+          <t>beclab/Olares</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>6948</v>
+        <v>5262</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>43.3</v>
+        <v>42.7</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>提供纯 C/C++ 的扩散模型推理
-【原文】Diffusion model(SD,Flux,Wan,Qwen Image,Z-Image,...) inference in pure C/C++</t>
+          <t>为始终在线代理的开源个人云操作系统
+【原文】Open-Source Personal Cloud OS for Always-On Agents</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>技能包/可部署服务</t>
+        </is>
+      </c>
+      <c r="G40" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -4433,7 +4479,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/leejet/stable-diffusion.cpp</t>
+          <t>https://github.com/beclab/Olares</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4442,16 +4488,16 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>6.19</v>
+        <v>6.1</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4466,21 +4512,21 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>ai, cplusplus, diffusion, flux, flux-dev, ggml, image-generation, image2image, img2img, latent-diffusion, ltx-video, qwen-image</t>
+          <t>agentic-ai, ai-agents, cloud-native, data-privacy, edge-ai, homelab, kubernetes, local-ai, model-serving, operating-system, personal-cloud, self-hosted</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2023-08-13</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>1123</v>
+        <v>863</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
@@ -4492,26 +4538,27 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>topic:image-generation stars:&gt;5000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>strawberrynine/ZiWeiDouShu-Master</t>
+          <t>huiliyi37/Tianshu-harness</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>47</v>
+        <v>522</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>41.2</v>
+        <v>39.7</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>提供紫微斗数大师级分析
-【原文】紫微斗数大师级分析，基于古籍 希夷先生《紫微斗数》，融合倪海厦《天纪》体系，含完整排盘算法、四化系统、格局知识库，可以算任意一年/月/日的感情/健康/财运/事业运/学业运/移民运。需要提供具体到小时的出生时间，和具体到市的出生地点。</t>
+          <t>终端编程智能体运行时，针对DeepSeek V4优化
+【原文】天枢 (Tianshu) 是一个基于harness工程的终端编程智能体运行时（Tui X Gui），针对DeepSeek V4 做了前缀缓存工程优化（长会话实测稳态命中率 97–99%）和深度适配。它跳出了传统 AI 编程助手把大模型仅当成“工具”的局限，基于认知虚拟机 (CVM)、自感知层和信息素（Stigmergy）自衰减记忆构建，让 AI 成为有独立判断与认知防护的“开发伙伴”。
+【依据】基于harness工程的终端编程智能体运行时，针对DeepSeek V4做了前缀缓存工程优化</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
@@ -4526,7 +4573,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -4536,7 +4583,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/strawberrynine/ZiWeiDouShu-Master</t>
+          <t>https://github.com/huiliyi37/Tianshu-harness</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4545,14 +4592,18 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>5.88</v>
+        <v>5.67</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M41" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4563,19 +4614,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P41" s="6" t="inlineStr"/>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>ai-agent, coding-agent, context-management, deepseek, dsh, gui, harness, harness-engineering, prefix-cache, tui</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>1</v>
@@ -4587,41 +4642,42 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>古籍 in:name,description stars:&gt;20</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ModelEngine-Group/app-platform</t>
+          <t>FalkorDB/FalkorDB</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>1454</v>
+        <v>5983</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>19.3</v>
+        <v>36.5</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>提供大模型应用开发的集成声明式编程和低代码配置工具
-【原文】AppPlatform 是一个前沿的大模型应用工程，旨在通过集成的声明式编程和低代码配置工具，简化和优化大模型的训练与推理应用的开发过程。本工程为软件工程师和产品经理提供一个强大的、可扩展的环境，以支持从概念到部署的全流程 AI 应用开发。</t>
+          <t>提供高速图数据库，用于知识图谱
+【原文】A super fast Graph Database uses GraphBLAS under the hood for its sparse adjacency matrix graph representation. Our goal is to provide the best Knowledge Graph for LLM (GraphRAG).
+【依据】topics: knowledge-graph</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>视频产线/AI免费池</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考/可部署服务</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -4631,7 +4687,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ModelEngine-Group/app-platform</t>
+          <t>https://github.com/FalkorDB/FalkorDB</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -4640,16 +4696,16 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>2.76</v>
+        <v>5.22</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4664,66 +4720,67 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, agentic-workflow, ai, java, low-code</t>
+          <t>cloud-database, database, database-as-a-service, developer-tools, devtools, graph-database, graphrag, knowledge-graph, realtime-database</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>2025-03-31</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>527</v>
+        <v>1147</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>the-wayee/OpenTV</t>
+          <t>LLMQuant/quant-mind</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>201</v>
+        <v>2825</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>18.1</v>
+        <v>36.3</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>短视频内容的策划与生产工具</t>
+          <t>量化金融领域的知识提取和检索框架
+【原文】QuantMind is an agent-native knowledge extraction and retrieval framework for quantitative finance.</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -4733,7 +4790,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/the-wayee/OpenTV</t>
+          <t>https://github.com/LLMQuant/quant-mind</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4742,16 +4799,16 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>2.58</v>
+        <v>5.19</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4764,56 +4821,60 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="6" t="inlineStr"/>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>agent, context-engineering, data, harness-engineering, knowledge, llm, pipeline, quantitative-finance, quantitative-research, workflow</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2025-03-14</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>78</v>
+        <v>544</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>18534516725/llm-api-setup-guides</t>
+          <t>LadybugDB/ladybug</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>138</v>
+        <v>1724</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>16.9</v>
+        <v>35.8</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>中文AI API中转站与工具配置教程
-【原文】88篇中文 AI API中转站与工具配置教程：Codex API、Claude Code API、OpenAI-compatible API、Base URL、Cursor、Cherry Studio、计费验证与错误排查。
-【依据】topics: ai-api, api-proxy, api-relay, api-testing, cherry-studio, claude-api</t>
+          <t>提供图数据库服务
+【原文】LadybugDB a graph database
+【依据】topics: graph-database</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
@@ -4833,7 +4894,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/18534516725/llm-api-setup-guides</t>
+          <t>https://github.com/LadybugDB/ladybug</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4842,7 +4903,7 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>2.42</v>
+        <v>5.12</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
@@ -4851,7 +4912,7 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4866,68 +4927,67 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>ai-api, api-proxy, api-relay, api-testing, cherry-studio, chinese-tutorial, claude-api, claude-code, cline, codex-api, codex-cli, cursor</t>
+          <t>code-knowledge-base, code-knowledge-graph, cypher, cypher-query-language, database, graph, knowledge-graph</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>57</v>
+        <v>337</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>API 中转 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
         </is>
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>rfhdw0102/YouDaoNoteLM</t>
+          <t>urchade/GLiNER</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>201</v>
+        <v>3624</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>16.2</v>
+        <v>24.6</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>有道云笔记等内容的自动知识库沉淀与智能问答
-【原文】接入有道云笔记、本地文件、网页与音视频等内容，自动沉淀为可检索知识库；基于 RAG 精准引用你的资料，提供可靠的智能问答与内容生成。兼容主流大模型和向量模型，让知识真正为你所用。
-【依据】topics: YouDaoNoteLM, RAG, 智能问答</t>
+          <t>轻量级命名实体识别模型
+【原文】Generalist and Lightweight Model for Named Entity Recognition (Extract any entity types from texts)</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4937,7 +4997,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/rfhdw0102/YouDaoNoteLM</t>
+          <t>https://github.com/urchade/GLiNER</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -4946,16 +5006,16 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>2.31</v>
+        <v>3.52</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -4968,65 +5028,69 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P45" s="6" t="inlineStr"/>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>information-extraction, large-language-models, named-entity-recognition, natural-language-processing, prompt-tuning</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2023-11-14</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>87</v>
+        <v>1030</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>RAG 知识库 in:name,description stars:&gt;200</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>FurkanGozukara/Stable-Diffusion</t>
+          <t>trustgraph-ai/trustgraph</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2765</v>
+        <v>2697</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>15.8</v>
+        <v>23.9</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 艺术生成和深度伪造工具。
-【原文】FLUX, Stable Diffusion, SDXL, SD3, LoRA, Fine Tuning, DreamBooth, Training, Automatic1111, Forge WebUI, SwarmUI, DeepFake, TTS, Animation, Text To Video, Tutorials, Guides, Lectures, Courses, ComfyUI, Google Colab, RunPod, Kaggle, NoteBooks, ControlNet, TTS, Voice Cloning, AI, AI News, ML, ML News, News, Tech, Tech News, Kohya, Midjourney, RunPod</t>
+          <t>基于超图的上下文编排层，构建统一语义上下文层
+【原文】The context orchestration layer powered by hypergraphs. Build a unified semantic context layer where agentic outcomes are deterministic and agent behavior is not just traceable, but cryptographically verifiable.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>图文产线/AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/代码库</t>
-        </is>
-      </c>
-      <c r="G46" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -5036,7 +5100,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FurkanGozukara/Stable-Diffusion</t>
+          <t>https://github.com/trustgraph-ai/trustgraph</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5045,16 +5109,16 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>2.25</v>
+        <v>3.41</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5069,24 +5133,24 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>ai-art, coding, deepfake-generation, dreambooth, education, flux-dev, flux-lora, generative-ai, guides, how-to, image-to-video-generation, kohya-webui</t>
+          <t>agent, agent-harness, context, context-engineering, context-graph, context-harness, context-orchestration, determinism, explainable-ai, graph, graph-engineering, help-wanted</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2023-05-01</t>
+          <t>2024-07-10</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>1227</v>
+        <v>791</v>
       </c>
       <c r="T46" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
@@ -5095,26 +5159,26 @@
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>topic:text-to-video stars:&gt;2000 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>nndl/llm-beginner</t>
+          <t>BruceLanLan/augur</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>6730</v>
+        <v>526</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>13.7</v>
+        <v>23.7</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>提供大模型与智能体电子书和编程任务
-【原文】《大模型与智能体》电子书与 6 个编程任务：Transformer、mini-GPT、SFT/DPO、RAG、工具调用与编程智能体。</t>
+          <t>多智能体投资分析系统，提供投资大师分析及共识机制
+【原文】🦉 Augur — 多智能体投资分析系统。13位虚拟投资大师独立分析，加权共识机制，Bloomberg风格Web仪表盘。</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -5124,7 +5188,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -5139,7 +5203,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/nndl/llm-beginner</t>
+          <t>https://github.com/BruceLanLan/augur</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5148,7 +5212,7 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>1.95</v>
+        <v>3.39</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -5172,24 +5236,24 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>agent, fudannlp, llm, openmoss, step-by-step</t>
+          <t>ai-agents, investment-analysis, multi-agent, stock-analysis, value-investing</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2017-03-29</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="S47" s="3" t="n">
-        <v>3451</v>
+        <v>155</v>
       </c>
       <c r="T47" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
@@ -5198,26 +5262,26 @@
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>GalTransl/GalTransl</t>
+          <t>zjunlp/DeepKE</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>2263</v>
+        <v>4478</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>13.2</v>
+        <v>10.6</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>支持大语言模型的 Galgame 自动化翻译解决方案
-【原文】支持GPT-4/Claude/Deepseek/Sakura等大语言模型的Galgame自动化翻译解决方案  Automated translation solution for visual novels supporting GPT-4/Claude/Deepseek/Sakura</t>
+          <t>知识图谱提取与构建工具
+【原文】[EMNLP 2022] An Open Toolkit for Knowledge Graph Extraction and Construction</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
@@ -5227,12 +5291,12 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G48" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H48" s="7" t="inlineStr">
@@ -5242,7 +5306,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GalTransl/GalTransl</t>
+          <t>https://github.com/zjunlp/DeepKE</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5251,11 +5315,11 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1.89</v>
+        <v>1.51</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
@@ -5275,52 +5339,52 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>ai, galgame, translater</t>
+          <t>attribute-extraction, chinese, deep-learning, deepke, document-level, few-shot, information-extraction, instructie, kg, knowledge-graph, knowprompt, lightner</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>2023-05-31</t>
+          <t>2018-08-01</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>1197</v>
+        <v>2961</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>Pangu-Immortal/hunter-ai-content-factory</t>
+          <t>socai-io/socai</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>391</v>
+        <v>184</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>11.9</v>
+        <v>9.9</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>自动从多个平台采集热点，生成文章和插图。
-【原文】自动发布 24 小时情报系统：好文章的 80% 在于选题。Hunter AI 自动从 GitHub Trending、Twitter、HackerNews Reddit 等平台采集热点，用 AI 判断哪些值得写，自动生成文章和插图，自动发布。</t>
+          <t>为小红书优化的Web Use Agent
+【依据】topics: xhs, xiaohongshu</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -5330,7 +5394,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5345,7 +5409,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Pangu-Immortal/hunter-ai-content-factory</t>
+          <t>https://github.com/socai-io/socai</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5354,16 +5418,16 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>1.7</v>
+        <v>1.42</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -5376,50 +5440,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P49" s="6" t="inlineStr"/>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>agent, browser-use, claude, codex, compute-use, linkedin, tiktok, xhs, xiaohongshu</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
         </is>
       </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>sollyu/AndroidStudioChineseLanguagePack</t>
+          <t>LHRLAB/Graph-R1</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>2494</v>
+        <v>591</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>10.7</v>
+        <v>7.6</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>提供 AndroidStudio 中文插件
-【原文】AndroidStudio中文插件(官方修改版本）</t>
+          <t>基于强化学习的GraphRAG框架研究资源
+【原文】[ICML 2026] Official resources of "Graph-R1: Towards Agentic GraphRAG Framework via End-to-end Reinforcement Learning".</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5429,7 +5497,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5444,7 +5512,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/sollyu/AndroidStudioChineseLanguagePack</t>
+          <t>https://github.com/LHRLAB/Graph-R1</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5453,14 +5521,18 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>1.53</v>
+        <v>1.08</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M50" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N50" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5473,57 +5545,57 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>android-studio, chinese, plugins</t>
+          <t>chain-of-thought, graphrag, hypergraph, reinforcement-learning</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>2025-03-11</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>1633</v>
+        <v>547</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U50" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>wfcz10086/AI-automatically-generates-novels</t>
+          <t>KRLabsOrg/LettuceDetect</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>936</v>
+        <v>605</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>10.2</v>
+        <v>7.3</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>基于 AI 和提示词的 AIGC 创作生产力工具
-【原文】一个基于ai +提示词 的aigc创作生产力工具， 已经有数百家工作室和个人作者通过该工具实现了快速、批量生成小说、剧本、镜头。</t>
+          <t>RAG输出验证工具，用于代码和工具的验证
+【原文】Span-level grounding verification for RAG, code, and tool-grounded AI outputs.</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -5543,7 +5615,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wfcz10086/AI-automatically-generates-novels</t>
+          <t>https://github.com/KRLabsOrg/LettuceDetect</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5552,11 +5624,11 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>1.45</v>
+        <v>1.04</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -5574,50 +5646,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P51" s="6" t="inlineStr"/>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>bert, hallucination-detection, hallucination-evaluation, information-extraction, nlp, python, pytorch, token-classification</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>2024-12-04</t>
+          <t>2025-02-05</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>644</v>
+        <v>581</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U51" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>lornshrimp/Lorn.NovelWriteSkills</t>
+          <t>JabRef/jabref</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>205</v>
+        <v>4704</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>9.699999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>提供围绕小说创作工作流的AI写作资产库
-【原文】一个面向长篇网文 / 小说创作工作流的 AI 写作资产库。它不是“随手堆提示词”的仓库，而是一套围绕 题材设计 → 大纲搭建 → 章节创作 → 审阅润色 → 多平台改写 → 质量门禁 → 分发落盘 搭起来的可复用写作系统。</t>
+          <t>管理BibTeX和BibLaTeX (.bib)库的桌面应用程序
+【原文】Desktop app for managing BibTeX and BibLaTeX (.bib) libraries</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
@@ -5627,12 +5703,12 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -5642,7 +5718,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lornshrimp/Lorn.NovelWriteSkills</t>
+          <t>https://github.com/JabRef/jabref</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5651,16 +5727,16 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>1.39</v>
+        <v>1.03</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>PowerShell</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5675,52 +5751,52 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai, novel, skills, writing-assistant</t>
+          <t>academia, academic-publications, ai, biblatex, bibliography, bibtex, citation, citation-generator, citation-style-language, citation-styles, hacktoberfest, jabref</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2014-03-11</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>148</v>
+        <v>4565</v>
       </c>
       <c r="T52" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>metasequoiaime/MSIME-Windows</t>
+          <t>alaskasquirrel/Email-newsletter-RSS</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>1335</v>
+        <v>1647</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>8.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>提供水杉输入法 Windows 产品
-【原文】水杉输入法 Windows 产品：TSF、Server、GUI、设置页与安装器。内测：tg: https://t.me/msimegroup QQ Group: 829919142</t>
+          <t>邮箱、新闻简报和RSS聚合工具
+【原文】邮箱 📧 newsletter RSS 荟萃 News</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -5730,12 +5806,12 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G53" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -5745,7 +5821,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/metasequoiaime/MSIME-Windows</t>
+          <t>https://github.com/alaskasquirrel/Email-newsletter-RSS</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5754,18 +5830,14 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>1.26</v>
+        <v>0.91</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr">
-        <is>
-          <t>C++</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr"/>
       <c r="N53" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5778,21 +5850,21 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>chinese, ime, input-method, japanese, metasequoia, tsf, windows, windows-11</t>
+          <t>chinese, email, newsletter, rss</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>2023-10-14</t>
+          <t>2021-09-19</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-05</t>
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>1061</v>
+        <v>1816</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>1</v>
@@ -5811,29 +5883,29 @@
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>renmengwen/MuseDock</t>
+          <t>monarch-initiative/ontogpt</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>110</v>
+        <v>1006</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>8.1</v>
+        <v>5.2</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>AI短视频创作与编辑工作台，整理来源，生成视频
-【原文】MuseDock 是一个本地优先的 AI 短视频创作与编辑工作台。输入一个选题，粘贴文章、GitHub 或抖音链接，也可以直接上传图片；MuseDock 会整理来源、补充研究、规划脚本与镜头，生成配音和 HTML 动画帧，最后在本机渲染成视频。</t>
+          <t>基于LLM的实体抽取工具，包括SPIRES
+【原文】LLM-based ontological extraction tools, including SPIRES</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5848,7 +5920,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/renmengwen/MuseDock</t>
+          <t>https://github.com/monarch-initiative/ontogpt</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5857,16 +5929,16 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1.16</v>
+        <v>0.75</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5879,50 +5951,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P54" s="6" t="inlineStr"/>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>ai, chat-gpt, data-modeling, gpt-3, information-extraction, language-models, large-language-models, linkml, llm, monarchinitiative, named-entity-recognition, ner</t>
+        </is>
+      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>2026-06-06</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S54" s="3" t="n">
-        <v>95</v>
+        <v>1345</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U54" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>Java-Edge/Java-Interview-Tutorial</t>
+          <t>LHRLAB/HyperGraphRAG</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>2860</v>
+        <v>451</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>7.7</v>
+        <v>5</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>Java/数据库/DDD/设计模式/微服务/中间件/AI大模型应用/区块链开发最佳实践教程
-【原文】请star，勿fork，因为爱force push！涵盖国际大厂Java/数据库/DDD/设计模式/微服务/中间件/AI大模型应用/区块链开发最佳实践。关注公众号【JavaEdge】，一起交流学习！</t>
+          <t>提供基于超图结构的检索增强生成资源
+【原文】[NeurIPS 2025] Official resources of "HyperGraphRAG: Retrieval-Augmented Generation via Hypergraph-Structured Knowledge Representation".</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -5932,7 +6008,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -5947,7 +6023,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Java-Edge/Java-Interview-Tutorial</t>
+          <t>https://github.com/LHRLAB/HyperGraphRAG</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -5956,16 +6032,16 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>1.1</v>
+        <v>0.72</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -5980,52 +6056,52 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>architecture, blockchain, ddd, java</t>
+          <t>graphrag, hypergraph, knowledge-graph, large-language-models</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>2019-07-22</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="S55" s="3" t="n">
-        <v>2606</v>
+        <v>629</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>大模型 in:name,description stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>go-ego/gse</t>
+          <t>dromara/dante-cloud</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2841</v>
+        <v>959</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>提供多语言 NLP 和文本分割工具
-【原文】Go efficient multilingual NLP and text segmentation; support English, Chinese, Japanese and others.</t>
+          <t>微服务云原生基座和AI Agent开发平台
+【原文】🐉 Dante Cloud 是支持阻塞式与响应式服务并行的微服务云原生基座和面向AI Agent开发的智能基座，基于领域驱动模型（DDD）设计，以高质量代码与低安全漏洞为核心，高度模块化、组件化，覆盖IoT设备认证、国家等保三级、接口国密数字信封加密等多层次安全体系，并提供多租户解决方案。独创“一套代码实现微服务和单体架构灵活切换”，赋能企业级智能应用构建。🔝🔝点个star 持续关注更新！</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -6035,7 +6111,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -6050,7 +6126,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/go-ego/gse</t>
+          <t>https://github.com/dromara/dante-cloud</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6059,7 +6135,7 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.84</v>
+        <v>0.49</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
@@ -6068,7 +6144,7 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N56" s="3" t="inlineStr">
@@ -6083,12 +6159,12 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>chinese, english, go, gse, hmm, hmm-viterbi-algorithm, japanese, jieba, nlp, segment, trie</t>
+          <t>ai-agent, harness-engineering, iot, loki, microservices, monolith, monorepo, mqtt, nacos, rsocket, spring-ai, spring-ai-alibaba</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>2017-06-23</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
@@ -6097,7 +6173,7 @@
         </is>
       </c>
       <c r="S56" s="3" t="n">
-        <v>3365</v>
+        <v>1939</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>1</v>
@@ -6109,26 +6185,26 @@
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+          <t>智能体 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>AIPMAndy/FreeToken</t>
+          <t>ail-project/ail-framework</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>105</v>
+        <v>1013</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>5.7</v>
+        <v>3</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>收集免费 API Token 的获取方法和使用指南
-【原文】🎁 收集各种免费 API Token 的获取方法和使用指南</t>
+          <t>信息泄露分析框架
+【原文】AIL framework - Analysis Information Leak framework</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
@@ -6141,9 +6217,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G57" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -6153,7 +6229,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AIPMAndy/FreeToken</t>
+          <t>https://github.com/ail-project/ail-framework</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6162,14 +6238,18 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.82</v>
+        <v>0.43</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N57" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6180,61 +6260,64 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P57" s="6" t="inlineStr"/>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>ail-framework, darkweb, darkweb-scraping, data-mining, information-extraction, information-security, leak</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2020-04-20</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S57" s="3" t="n">
-        <v>128</v>
+        <v>2333</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
         </is>
       </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>lihanghang/NLP-Knowledge-Graph</t>
+          <t>iMoonLab/HGNN</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>1766</v>
+        <v>849</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>自然语言处理、知识图谱、对话系统技术研究与应用
-【原文】自然语言处理、知识图谱、对话系统，大模型等技术研究与应用。
-【依据】topics: bert, deep-learning, knowledge-graph, llm, nlp</t>
+          <t>超图神经网络研究，基于PyTorch
+【原文】Hypergraph Neural Networks (AAAI 2019)</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>代码库/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6249,7 +6332,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/lihanghang/NLP-Knowledge-Graph</t>
+          <t>https://github.com/iMoonLab/HGNN</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6258,7 +6341,7 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.64</v>
+        <v>0.3</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
@@ -6282,67 +6365,67 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, bert, deep-learning, ernie, event-driven, kbqa, knowledge-graph, llm, machine-learning, ner, nlp</t>
+          <t>complex-data, deep-learning, hypergraph, hypergraph-neural-networks, pytorch</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>2019-01-29</t>
+          <t>2018-12-06</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2022-08-31</t>
         </is>
       </c>
       <c r="S58" s="3" t="n">
-        <v>2780</v>
+        <v>2834</v>
       </c>
       <c r="T58" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U58" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>知识图谱 in:name,description stars:&gt;200 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>neopen/story-shot-agent</t>
+          <t>pnnl/HyperNetX</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>183</v>
+        <v>711</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>4</v>
+        <v>1.8</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>自动解析剧本，生成视频提示词，支持角色和剧情一致性保持
-【原文】剧本分镜智能体（PenShot）：电影/动漫/短剧/小说→分镜→提示词→视频。| 基于LLM 通过 LangGraph+LlamaIndex实现任意格式剧本的自动解析，生成 Sora/Veo/Runway 等模型可用的连贯text-to-video提示词。保持角色/剧情跨片段一致，支持 MCP/REST API/Function Calls/A2A 多方式集成。（LLM-powered text-to-video-prompt agent. Break scripts into Sora/Veo-ready shots with character consistency）</t>
+          <t>超图分析可视化Python包
+【原文】Python package for hypergraph analysis and visualization.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -6352,7 +6435,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/neopen/story-shot-agent</t>
+          <t>https://github.com/pnnl/HyperNetX</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6361,11 +6444,11 @@
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.57</v>
+        <v>0.25</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M59" s="3" t="inlineStr">
@@ -6385,53 +6468,52 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>agent-to-agent, ai-filmmaking, ai-video-generation, character-consistency, function-calling, kling-ai, langgraph-agent, llm-agent, pika-labs, prompt-engineering, rag, screenplay</t>
+          <t>hypergraph, hypergraphs, knowledge-graph, property-hypergraphs, python, s-linegraph, simplicial-complexes, simplicial-homology</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>2025-10-23</t>
+          <t>2018-10-22</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="S59" s="3" t="n">
-        <v>321</v>
+        <v>2879</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U59" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>MoFox-Studio/Neo-MoFox</t>
+          <t>easy-graph/Easy-Graph</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>101</v>
+        <v>479</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>提供 AI 聊天机器人框架，旨在创造数字生命体。
-【原文】一个全新重构的 AI 聊天机器人框架，它的目标不仅仅是回答问题，而是创造一个真正的数字生命体。
-【依据】旨在创造一个真正的数字生命体。</t>
+          <t>提供高级网络分析方法，包括结构洞检测和网络嵌入等
+【原文】EasyGraph is an open-source network analysis library designed to cover advanced network processing methods. It includes functionalities for detecting structural hole spanners, network embedding, and various classic network analysis techniques.</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -6441,12 +6523,12 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G60" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -6456,7 +6538,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/MoFox-Studio/Neo-MoFox</t>
+          <t>https://github.com/easy-graph/Easy-Graph</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6465,11 +6547,11 @@
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.45</v>
+        <v>0.21</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>BSD-3-Clause</t>
         </is>
       </c>
       <c r="M60" s="3" t="inlineStr">
@@ -6489,52 +6571,52 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>agent, ai, bot, chatbot</t>
+          <t>hypergraph, multiprocessing-optimization, network-analysis, python, structural-hole-theory</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2020-06-21</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S60" s="3" t="n">
-        <v>224</v>
+        <v>2271</v>
       </c>
       <c r="T60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>数字人 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>unraous/uxuescript</t>
+          <t>kahypar/kahypar</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>170</v>
+        <v>534</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>提供学习通自动刷课脚本。
-【原文】学习通一键全自动刷课脚本，支持后台刷课、倍速播放、自动回答互动题目，截止 2026/09/09 可用。（免安装打包版已发布至Release）</t>
+          <t>多级超图划分框架，提供高质量解决方案
+【原文】KaHyPar (Karlsruhe Hypergraph Partitioning) is a multilevel hypergraph partitioning framework providing direct k-way and recursive bisection based partitioning algorithms that compute solutions of very high quality.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
@@ -6544,7 +6626,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G61" s="8" t="inlineStr">
@@ -6559,7 +6641,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/unraous/uxuescript</t>
+          <t>https://github.com/kahypar/kahypar</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6568,7 +6650,7 @@
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.36</v>
+        <v>0.15</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
@@ -6577,7 +6659,7 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -6592,67 +6674,67 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>chaoxing, education, javascript, xuexitong</t>
+          <t>algorithm-engineering, cpp, evolutionary-algorithms, graph, graph-algorithms, graph-partitioning, graphs, hypergraph, hypergraph-partitioning, hypergraphs, papers-with-code, partitioning</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>2025-05-28</t>
+          <t>2016-09-23</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-03-07</t>
         </is>
       </c>
       <c r="S61" s="3" t="n">
-        <v>469</v>
+        <v>3638</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>自动 发布 in:name,description stars:&gt;100 pushed:&gt;2026-06-11</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>mofahuizhang/Gn</t>
+          <t>yamafaktory/hypergraph</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>0</v>
+        <v>352</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>提供中医病机分析框架。
-【原文】Gn 通用病机分析框架——中医理论现代化、结构化与AI大模型结构复用</t>
+          <t>创建有向超图的数据结构库
+【原文】Hypergraph is a data structure library to create a directed hypergraph in which a hyperedge can join any number of vertices.</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
         <is>
-          <t>方剂知识线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -6662,7 +6744,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mofahuizhang/Gn</t>
+          <t>https://github.com/yamafaktory/hypergraph</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6671,14 +6753,18 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Rust</t>
+        </is>
+      </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6689,31 +6775,35 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P62" s="6" t="inlineStr"/>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>data, data-science, data-structure, data-structures, hypergraph, hypergraphs, rust, rust-lang, rustlang</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2020-10-07</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="S62" s="3" t="n">
-        <v>3</v>
+        <v>2163</v>
       </c>
       <c r="T62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>中医 大模型 in:name,description</t>
+          <t>topic:hypergraph stars:&gt;300</t>
         </is>
       </c>
     </row>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-09 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-10 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ruvnet/RuView</t>
+          <t>shanraisshan/claude-code-best-practice</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>92914</v>
+        <v>65804</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1417</v>
+        <v>1467</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>将WiFi信号转换为实时空间智能、生命体征监测和存在检测
-【原文】π RuView turns commodity WiFi signals into real-time spatial intelligence, vital sign monitoring, and presence detection — all without a single pixel of video.</t>
+          <t>Claude 代码最佳实践，从 vibe coding 到 agentic engineering
+【原文】from vibe coding to agentic engineering - practice makes claude perfect</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ruvnet/RuView</t>
+          <t>https://github.com/shanraisshan/claude-code-best-practice</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>202.43</v>
+        <v>209.57</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,21 +703,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>awesome, claude, densepose, esp32, firmware, home-assistant, home-automation, iot, monitoring, networking, npm, pose-estimation</t>
+          <t>agentic-ai, agentic-coding, agentic-engineering, agentic-workflow, ai, ai-agents, anthropic, best-practices, boris, claude, claude-ai, claude-code</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2025-06-07</t>
+          <t>2025-10-31</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>459</v>
+        <v>314</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,41 +729,41 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>tinyhumansai/openhuman</t>
+          <t>deeplethe/utopia</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>39576</v>
+        <v>6435</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1364.7</v>
+        <v>1324.8</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>开源个人AI，支持本地存储和代理编排
-【原文】OpenHuman is an open source personal AI for Mac, Windows and Linux — local-first memory, agent orchestration, and deep research.</t>
+          <t>构建企业级世界模型
+【原文】World's first open-source enterprise world model.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H4" s="7" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/tinyhumansai/openhuman</t>
+          <t>https://github.com/deeplethe/utopia</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,11 +782,11 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>194.96</v>
+        <v>189.26</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
@@ -806,68 +806,67 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent-orchestration, ai-agents, ai-assistant, desktop, llm, local-first, mcp, personal-ai, privacy, rust, second-brain, tauri</t>
+          <t>agent-memory, bitemporal, graphrag, knowledge-base, knowledge-graph, llm, ontology, pgvector, postgresql, rag, rust, self-hosted</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>203</v>
+        <v>34</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-10</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>codecrafters-io/build-your-own-x</t>
+          <t>browser-use/video-use</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>546232</v>
+        <v>24542</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1255.7</v>
+        <v>1137.7</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>编程技术教程
-【原文】Master programming by recreating your favorite technologies from scratch.
-【依据】programming, tutorial-code, tutorials</t>
+          <t>使用编码代理编辑视频
+【原文】Edit videos with coding agents</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H5" s="7" t="inlineStr">
@@ -877,7 +876,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/codecrafters-io/build-your-own-x</t>
+          <t>https://github.com/browser-use/video-use</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -886,16 +885,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>179.39</v>
+        <v>162.53</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Markdown</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -908,23 +907,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>awesome-list, free, programming, tutorial-code, tutorial-exercises, tutorials</t>
-        </is>
-      </c>
+      <c r="P5" s="6" t="inlineStr"/>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>3045</v>
+        <v>151</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -936,41 +931,41 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>truefoundry/trueforge</t>
+          <t>LaoFeng-mouse/flyingmouse-format</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5349</v>
+        <v>5674</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>780.1</v>
+        <v>1134.8</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>将LLM转换为工作代理的开源代理 harness
-【原文】The open-source agent harness - the runtime layer that turns an LLM into a working agent.</t>
+          <t>提供 Windows 文件格式转换工具，支持 OCR 和批量转换
+【原文】飞鼠格式 FlyingMouse Format - Windows 免费文件格式转换工具（离线可用，内置 FFmpeg/LibreOffice/Poppler/Tesseract）。图片/文档/表格/PPT/PDF/音视频/WPS 格式互转 + OCR + 批量转换；音频仅支持普通格式。作者：牢蜂（LaoFeng）｜仅供个人免费使用，禁止商业售卖/转卖/套壳</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>图文产线/古籍OCR线</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -980,7 +975,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/truefoundry/trueforge</t>
+          <t>https://github.com/LaoFeng-mouse/flyingmouse-format</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -989,16 +984,16 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>111.44</v>
+        <v>162.11</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
@@ -1013,21 +1008,21 @@
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, agents, harness, harness-engineering</t>
+          <t>desktop-app, electron, ffmpeg, file-converter, format-converter, libreoffice, ocr, pdf, windows, wps</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1039,37 +1034,36 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>donnemartin/system-design-primer</t>
+          <t>webadderallorg/Recordly</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>369020</v>
+        <v>26521</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>741.9</v>
+        <v>1020</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>系统设计学习资源
-【原文】Learn how to design large-scale systems. Prep for the system design interview.  Includes Anki flashcards.
-【依据】design, system, web-application</t>
+          <t>创建无需编辑技能的演示视频
+【原文】Create polished demo videos without editing skills. Mac/Windows/Linux</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1084,7 +1078,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/donnemartin/system-design-primer</t>
+          <t>https://github.com/webadderallorg/Recordly</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1093,7 +1087,7 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>105.98</v>
+        <v>145.72</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
@@ -1102,7 +1096,7 @@
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1117,21 +1111,21 @@
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
-          <t>design, design-patterns, design-system, development, interview, interview-practice, interview-questions, programming, python, system, web, web-application</t>
+          <t>electron, free, linux, macos, open-source, screen-recorder, screen-studio, windows</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2017-02-26</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>3482</v>
+        <v>182</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1143,42 +1137,41 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>996icu/996.ICU</t>
+          <t>debpalash/VoiceStudio</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>276933</v>
+        <v>21930</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>711.6</v>
+        <v>996.8</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>统计贡献者仓库
-【原文】Repo for counting stars and contributing. Press F to pay respect to glorious developers.
-【依据】-</t>
+          <t>提供语音克隆、配音、视频配音等功能
+【原文】VoiceStudio is the open-source, fully-local ElevenLabs alternative — voice cloning, voice design, video dubbing, dictation, transcription &amp; audiobook creation in 646 languages.</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1188,7 +1181,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/996icu/996.ICU</t>
+          <t>https://github.com/debpalash/VoiceStudio</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1197,14 +1190,18 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>101.66</v>
+        <v>142.4</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1215,19 +1212,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P8" s="6" t="inlineStr"/>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>ai, audiobook, cuda, dubbing, elevenlabs-alternative, huggingface, local-first, mlx, omnivoice-studio, speech-to-text, tauri, text-to-speech</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2019-03-26</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2025-08-22</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>2724</v>
+        <v>154</v>
       </c>
       <c r="T8" s="3" t="n">
         <v>1</v>
@@ -1239,27 +1240,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>jwasham/coding-interview-university</t>
+          <t>kajisho5/ffmpeg-skill</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>360645</v>
+        <v>896</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>673.8</v>
+        <v>896</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>软件工程师学习计划
-【原文】A complete computer science study plan to become a software engineer.
-【依据】algorithm, coding-interview, software-engineering</t>
+          <t>使用ffmpeg进行视频处理的技能
+【依据】ffmpeg-skill</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jwasham/coding-interview-university</t>
+          <t>https://github.com/kajisho5/ffmpeg-skill</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1293,14 +1293,18 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>96.25</v>
+        <v>128</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>CC-BY-SA-4.0</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1311,23 +1315,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>algorithm, algorithms, coding-interview, coding-interviews, computer-science, data-structures, interview, interview-prep, interview-preparation, programming-interviews, software-engineering, study-plan</t>
-        </is>
-      </c>
+      <c r="P9" s="6" t="inlineStr"/>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2016-06-06</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>3747</v>
+        <v>7</v>
       </c>
       <c r="T9" s="3" t="n">
         <v>1</v>
@@ -1339,27 +1339,26 @@
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>trimstray/the-book-of-secret-knowledge</t>
+          <t>microsoft/ai-agents-for-beginners</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>242884</v>
+        <v>74307</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>566.7</v>
+        <v>799</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>收集技术资源列表
-【原文】A collection of inspiring lists, manuals, cheatsheets, blogs, hacks, one-liners, cli/web tools and more.
-【依据】awesome, cheatsheets, devops</t>
+          <t>提供构建 AI 代理的 Jupyter Notebook 教程和框架
+【原文】18 Lessons to Get Started Building AI Agents</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1369,7 +1368,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1384,7 +1383,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/trimstray/the-book-of-secret-knowledge</t>
+          <t>https://github.com/microsoft/ai-agents-for-beginners</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1393,14 +1392,18 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>80.95999999999999</v>
+        <v>114.14</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
           <t>MIT</t>
         </is>
       </c>
-      <c r="M10" s="3" t="inlineStr"/>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>Jupyter Notebook</t>
+        </is>
+      </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1413,21 +1416,21 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-list, bsd, cheatsheets, devops, guidelines, hacking, hacks, howtos, linux, lists, manuals</t>
+          <t>agentic-ai, agentic-framework, agentic-rag, ai-agents, ai-agents-framework, autogen, foundry, foundry-local, generative-ai, microsoft-foundry, semantic-kernel</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2018-06-23</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2024-11-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>3000</v>
+        <v>651</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1439,37 +1442,36 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>massgravel/Microsoft-Activation-Scripts</t>
+          <t>AUTOMATIC1111/stable-diffusion-webui</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>189923</v>
+        <v>164882</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>546.6</v>
+        <v>779.9</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Windows 和 Office 激活脚本
-【原文】Open-source Windows and Office activator featuring HWID, Ohook, TSforge, and Online KMS activation methods, along with advanced troubleshooting.
-【依据】activator, hwid, kms</t>
+          <t>Stable Diffusion 的网页用户界面，用于图像生成和文本到图像
+【原文】Stable Diffusion web UI</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1484,7 +1486,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/massgravel/Microsoft-Activation-Scripts</t>
+          <t>https://github.com/AUTOMATIC1111/stable-diffusion-webui</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1493,16 +1495,16 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>78.09</v>
+        <v>111.41</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>Batchfile</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
@@ -1517,21 +1519,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>activator, hwid, kms, kms38, massgrave, massgravel, microsoft, microsoft365, office, office365, ohook, powershell</t>
+          <t>ai, ai-art, deep-learning, diffusion, gradio, image-generation, image2image, img2img, pytorch, stable-diffusion, text2image, torch</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2020-01-12</t>
+          <t>2022-08-22</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>2432</v>
+        <v>1480</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1550,24 +1552,24 @@
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>charmbracelet/crush</t>
+          <t>vectorize-io/hindsight</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>27978</v>
+        <v>23350</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>411.5</v>
+        <v>518.9</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>用于所有AI代理的华丽编码工具
-【原文】Glamourous agentic coding for all 💘</t>
+          <t>代理记忆服务，用于学习代理记忆
+【原文】Hindsight: Agent Memory That Learns</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
@@ -1577,7 +1579,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1587,7 +1589,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/charmbracelet/crush</t>
+          <t>https://github.com/vectorize-io/hindsight</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1596,16 +1598,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>58.78</v>
+        <v>74.13</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1620,21 +1622,21 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai, llms, ravishing</t>
+          <t>agentic-ai, agents, ai-memory, memory</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-10-30</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>476</v>
+        <v>315</v>
       </c>
       <c r="T12" s="3" t="n">
         <v>1</v>
@@ -1646,41 +1648,41 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ZJU-REAL/Easel</t>
+          <t>CyC2018/CS-Notes</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>700</v>
+        <v>185972</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>408.3</v>
+        <v>415.8</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>社交媒体AI智能体，用于内容创作和发布
-【原文】An open-source AI agent for social media — discover trends, create content, publish everywhere, and learn what works across Xiaohongshu, Douyin, Zhihu, Bilibili, and more.🎨一个开源的 AI 社交媒体智能体——发现热点趋势、创作内容、一键发布至各大平台，并学习分析哪些内容真正有效，覆盖小红书、抖音、知乎、哔哩哔哩等平台。</t>
+          <t>提供技术面试必备基础知识、Leetcode 和计算机科学相关资料
+【原文】:books: 技术面试必备基础知识、Leetcode、计算机操作系统、计算机网络、系统设计</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>视频产线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1690,7 +1692,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ZJU-REAL/Easel</t>
+          <t>https://github.com/CyC2018/CS-Notes</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1699,18 +1701,14 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>58.33</v>
+        <v>59.4</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr"/>
       <c r="N13" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -1723,62 +1721,62 @@
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>agent, agent-skill, content-automation, content-creation, content-generation, mcp, openclaw, social-media, social-media-management</t>
+          <t>algorithm, computer-science, cpp, interview, java, leetcode, python, system-design</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2018-02-13</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2024-08-21</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>12</v>
+        <v>3131</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>run-llama/liteparse</t>
+          <t>Mintplex-Labs/anything-llm</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>12278</v>
+        <v>65856</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>405.4</v>
+        <v>386.1</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>快速、有用的开源文档解析器
-【原文】A fast, helpful, and open-source document parser</t>
+          <t>提供本地 AI 代理体验的 JavaScript 库
+【原文】Stop renting your intelligence. Own it with AnythingLLM. Everything you need for a powerful local-first agent experience</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1793,7 +1791,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/run-llama/liteparse</t>
+          <t>https://github.com/Mintplex-Labs/anything-llm</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1802,16 +1800,16 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>57.92</v>
+        <v>55.16</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1826,24 +1824,24 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>document-ocr, document-processing, ocr, ocr-recognition, pdf, pdf-parser, text-extraction</t>
+          <t>agent-computer, agent-harness, agent-orchestration, agentic-ai, ai-agents, computer-use, hermes-agent, llm, local-ai, localai, multimodal, no-code</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2023-06-04</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>212</v>
+        <v>1194</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
@@ -1852,42 +1850,41 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>op7418/guizang-yingzao-skill</t>
+          <t>zvec-ai/zvec-grep</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>396</v>
+        <v>3324</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>396</v>
+        <v>375.3</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>将中国古建筑和文化照片转换为艺术海报
-【原文】🏯 Claude Code / Codex skill — transform Chinese architecture, cultural places &amp; travel photos into art-directed editorial posters with GPT Image. 中国古建筑与在地文化照片 → 艺术指导海报
-【依据】agent-skill, ai-agent, image-generation</t>
+          <t>提供本地优先的搜索工具，适用于人类和AI代理
+【原文】Local-first search across your workspace, built for humans and AI agents.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>MCP服务/技能包/可部署服务</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H15" s="7" t="inlineStr">
@@ -1897,7 +1894,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/op7418/guizang-yingzao-skill</t>
+          <t>https://github.com/zvec-ai/zvec-grep</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1906,16 +1903,16 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>56.57</v>
+        <v>53.61</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1930,68 +1927,67 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>agent-skill, ai-agent, anthropic, chinese-architecture, chinese-culture, claude-code, claude-skill, codex, cultural-heritage, editorial-design, gpt-image, image-generation</t>
+          <t>ai-agents, bm25, cli, code-search, full-text-search, local-first, mcp, ripgrep, semantic-search, vector-search</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>7</v>
+        <v>62</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:xiaohongshu stars:&gt;100</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>HKUDS/LightRAG</t>
+          <t>Tencent/WeKnora</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>39517</v>
+        <v>21969</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>391.2</v>
+        <v>370.6</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>提供简单快速的检索增强生成模型
-【原文】[EMNLP2025] LightRAG: Simple and Fast Retrieval-Augmented Generation
-【依据】topics: retrieval-augmented-generation</t>
+          <t>开源的LLM知识平台，将原始文档转换为可查询的RAG、自主推理代理和自维护Wiki
+【原文】Open-source LLM knowledge platform: turn raw documents into a queryable RAG, an autonomous reasoning agent, and a self-maintaining Wiki.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -2001,7 +1997,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/HKUDS/LightRAG</t>
+          <t>https://github.com/Tencent/WeKnora</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2010,16 +2006,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>55.89</v>
+        <v>52.94</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2034,24 +2030,24 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>docling, genai, gpt, graphrag, knowledge-graph, large-language-models, llm, mineru, rag, ragas, retrieval-augmented-generation</t>
+          <t>agent, agentic, ai, chatbot, dsh-plugin, embeddings, evaluation, generative-ai, golang, knowledge-base, llm, multi-tenant</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2025-07-22</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>707</v>
+        <v>415</v>
       </c>
       <c r="T16" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
@@ -2060,27 +2056,26 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>ossu/computer-science</t>
+          <t>simstudioai/sim</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>208873</v>
+        <v>29590</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>324.1</v>
+        <v>337.9</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>计算机科学学习路径
-【原文】🎓 Path to a free self-taught education in Computer Science!
-【依据】computer-science, courses, curriculum</t>
+          <t>构建、部署和监控AI代理和流程的工作空间
+【原文】Sim is the collaborative workspace to build, deploy, and monitor AI agents and workflows. Used by 100,000+ builders.</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
@@ -2090,7 +2085,7 @@
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2105,7 +2100,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ossu/computer-science</t>
+          <t>https://github.com/simstudioai/sim</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2114,16 +2109,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>46.3</v>
+        <v>48.27</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2138,21 +2133,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>awesome-list, computer-science, courses, curriculum</t>
+          <t>agent-workflow, agentic-workflow, agents, ai, aiagents, anthropic, artificial-intelligence, automation, chatbot, deepseek, gemini, low-code</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2014-05-04</t>
+          <t>2025-01-05</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>4511</v>
+        <v>613</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2164,27 +2159,26 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>vuejs/vue</t>
+          <t>redhat-et/ripwire</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>212027</v>
+        <v>1841</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>309.8</v>
+        <v>299.7</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Vue.js 框架仓库
-【原文】This is the repo for Vue 2. For Vue 3, go to https://github.com/vuejs/core
-【依据】framework, frontend, javascript</t>
+          <t>AI代理的ripgrep工具，提供代码导航和MCP服务器
+【原文】The ripgrep of AI context: a zero-dependency C++23 CLI + MCP server for coding agents. Find what you want without reading the repo, then check you built what you meant — blast radius, tests-to-run, quality deltas. Signatures at 74.7% fewer bytes than bodies; every guess labelled, every loss published. Paddle out with a map.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
@@ -2194,7 +2188,7 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
@@ -2209,7 +2203,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vuejs/vue</t>
+          <t>https://github.com/redhat-et/ripwire</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2218,16 +2212,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>44.26</v>
+        <v>42.81</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2242,21 +2236,21 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>framework, frontend, javascript, vue</t>
+          <t>ai-agents, call-graph, claude, claude-code, cli, code-navigation, codex, coding-agents, context-engineering, cpp, developer-tools, llm</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2013-07-29</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2024-10-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>4790</v>
+        <v>43</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2268,26 +2262,26 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>google/adk-python</t>
+          <t>feder-cr/AIHawk</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>21470</v>
+        <v>30334</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>285.7</v>
+        <v>276.8</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>构建、评估和部署复杂AI代理的Python工具包
-【原文】An open-source, code-first Python toolkit for building, evaluating, and deploying sophisticated AI agents with flexibility and control.</t>
+          <t>开源 AI 浏览器代理，用于网页自动化和计算机使用
+【原文】Open-source AI browser agent for web automation: a web browsing agent and computer-use agent in plain English. Browser MCP for Claude Code and Gemini CLI.</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -2297,7 +2291,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2312,7 +2306,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/google/adk-python</t>
+          <t>https://github.com/feder-cr/AIHawk</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2321,11 +2315,11 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>40.82</v>
+        <v>39.55</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
@@ -2345,24 +2339,24 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic, agentic-ai, agents, agents-sdk, ai, ai-agents, aiagentframework, genai, genai-chatbot, llm, llms</t>
+          <t>agentic-ai, ai-agent, ai-automation, autonomous-agent, autonomous-agents, browser, browser-agent, computer-use, job-hunting, job-search, lead-generation, llm-agent</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2024-08-04</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>526</v>
+        <v>767</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
@@ -2371,41 +2365,41 @@
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>alvinunreal/oh-my-opencode-slim</t>
+          <t>getify/You-Dont-Know-JS</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>8751</v>
+        <v>184849</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>258.4</v>
+        <v>276.4</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>精调的Opencode多代理套件，混合任何模型
-【原文】Lean, fine tuned Opencode multi agent suite · Mix any models · Auto delegate tasks</t>
+          <t>JavaScript 语言书籍系列，包括异步、闭包、原型等主题
+【原文】A book series (2 published editions) on the JS language.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2415,7 +2409,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/alvinunreal/oh-my-opencode-slim</t>
+          <t>https://github.com/getify/You-Dont-Know-JS</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2424,18 +2418,14 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>36.92</v>
+        <v>39.49</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr"/>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2448,21 +2438,21 @@
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, antigravity, cerebras, herdr-plugin, oh-my-opencode, opencode, orchestration</t>
+          <t>async, book, book-series, closures, education, es2015, es6, javascript, learn-to-code, programming, prototypes, training-materials</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2026-01-15</t>
+          <t>2013-11-16</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-02-15</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>237</v>
+        <v>4681</v>
       </c>
       <c r="T20" s="3" t="n">
         <v>1</v>
@@ -2474,26 +2464,26 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Asabeneh/30-Days-Of-Python</t>
+          <t>jlevy/the-art-of-command-line</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>73264</v>
+        <v>162328</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>206.3</v>
+        <v>275.1</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供Python编程挑战的指南和视频
-【原文】The 30 Days of Python programming challenge is a step-by-step guide to learn the Python programming language in 30 days. This challenge may take more than 100 days. Follow your own pace. These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
+          <t>提供命令行操作的指南和技巧
+【原文】Master the command line, in one page</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2503,7 +2493,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2518,7 +2508,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Asabeneh/30-Days-Of-Python</t>
+          <t>https://github.com/jlevy/the-art-of-command-line</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2527,18 +2517,14 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>29.47</v>
+        <v>39.3</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
           <t>NONE</t>
         </is>
       </c>
-      <c r="M21" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+      <c r="M21" s="3" t="inlineStr"/>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2551,21 +2537,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>30-days-of-python, data, data-science, database, flask, fullstack, github, heroku, matplotlib, ml, mongodb, numpy</t>
+          <t>bash, documentation, linux, macos, unix, windows</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2019-11-19</t>
+          <t>2015-05-20</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2024-06-25</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>2486</v>
+        <v>4131</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2577,31 +2563,31 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>stars:&gt;150000</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ChenShuo2004/cs-board</t>
+          <t>run-llama/llama_index</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>541</v>
+        <v>52106</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>199.3</v>
+        <v>259.1</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>生成白板动画视频的AI工具
-【原文】将参考声音和中文文案自动生成白板动画视频的本地 AI 工具。</t>
+          <t>文档代理和OCR平台
+【原文】LlamaIndex is the leading document agent and OCR platform</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
@@ -2621,7 +2607,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ChenShuo2004/cs-board</t>
+          <t>https://github.com/run-llama/llama_index</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2630,7 +2616,7 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>28.47</v>
+        <v>37.01</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
@@ -2654,53 +2640,52 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>ai-video, chinese, fastapi, index-tts, react, tts, whiteboard-animation</t>
+          <t>agents, application, data, fine-tuning, framework, llamaindex, llm, multi-agents, rag, vector-database</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>19</v>
+        <v>1408</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>topoteretes/cognee</t>
+          <t>ValueCell-ai/ClawX</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>30607</v>
+        <v>7617</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>191.3</v>
+        <v>245.7</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>为AI代理提供持久长期记忆的知识图谱引擎
-【原文】Cognee is the open-source AI memory platform for agents. Give your AI agents persistent long-term memory across sessions with a self-hosted knowledge graph engine.
-【依据】topics: cognitive-architecture, cognitive-memory</t>
+          <t>提供桌面应用程序，用于管理 OpenClaw AI 代理
+【原文】ClawX is a desktop app that provides a graphical interface for OpenClaw AI agents. It turns CLI-based AI orchestration into a desktop experience without using the terminal. China website is https://clawx.com.cn.</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2710,7 +2695,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>MCP服务/技能包/架构参考</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2725,7 +2710,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/topoteretes/cognee</t>
+          <t>https://github.com/ValueCell-ai/ClawX</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2734,16 +2719,16 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>27.33</v>
+        <v>35.1</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2758,21 +2743,21 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>agent-memory, agent-skills, ai, ai-agents, ai-memory, cognitive-architecture, cognitive-memory, context-engineering, contributions-welcome, good-first-issue, good-first-pr, graph-database</t>
+          <t>agent, agentic-ai, agents, ai, clawdbot, moltbot, openclaw, skill</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2023-08-16</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>1120</v>
+        <v>217</v>
       </c>
       <c r="T23" s="3" t="n">
         <v>1</v>
@@ -2784,26 +2769,26 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>microsoft/agent-framework</t>
+          <t>Gentleman-Programming/gentle-ai</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>13436</v>
+        <v>6571</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>188.5</v>
+        <v>235.9</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>构建、编排和部署AI代理和多代理工作流的框架
-【原文】A framework for building, orchestrating and deploying AI agents and multi-agent workflows with support for Python and .NET.</t>
+          <t>配置和集成多种AI编码代理
+【原文】Gentle-AI configures the AI coding agents you already use: Claude Code, Cursor, OpenCode, Codex, Pi, and more. Choose persistent memory, Spec-Driven Development, curated skills, MCP servers, personas, and optional bounded review. Open source, no agent lock-in.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -2813,7 +2798,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2828,7 +2813,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/agent-framework</t>
+          <t>https://github.com/Gentleman-Programming/gentle-ai</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2837,7 +2822,7 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>26.93</v>
+        <v>33.7</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -2846,7 +2831,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2861,24 +2846,24 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>agent-framework, agentic-ai, agents, ai, dotnet, multi-agent, orchestration, python, sdk, workflows</t>
+          <t>agent-skills, ai-agents, ai-coding, claude-code, code-review, codex, coding-agents, copilot, cursor, developer-tools, golang, llm</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2025-04-28</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>499</v>
+        <v>195</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
@@ -2887,41 +2872,42 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>remotion-dev/remotion</t>
+          <t>Osmantic/ODS</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>58732</v>
+        <v>6347</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>181.2</v>
+        <v>208.6</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>使用React编程方式制作视频
-【原文】🎥      Make videos programmatically with React</t>
+          <t>将个人电脑转变为AI服务器，提供LLM推理和聊天UI
+【原文】Turn your PC, Mac, or Linux box into an AI server.  LLM inference, chat UI, voice, agents, workflows, RAG, and image generation.
+【依据】Turn your PC, Mac, or Linux box into an AI server. LLM inference, chat UI, voice, agents, workflows, RAG, and image gene</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>AI免费池/未归类</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/可部署服务</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H25" s="7" t="inlineStr">
@@ -2931,7 +2917,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/remotion-dev/remotion</t>
+          <t>https://github.com/Osmantic/ODS</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2940,16 +2926,16 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>25.88</v>
+        <v>29.8</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2964,21 +2950,21 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>javascript, react, video</t>
+          <t>ai-agents, amd, comfyui, docker, llama-cpp, llm, local-ai, n8n, nvidia, open-webui, rag, self-hosted</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2020-06-23</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>2269</v>
+        <v>213</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2990,31 +2976,31 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Developer-Y/cs-video-courses</t>
+          <t>semantica-agi/semantica</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>83456</v>
+        <v>12538</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>161.8</v>
+        <v>198.6</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>提供计算机科学课程视频讲座列表
-【原文】List of Computer Science courses with video lectures.</t>
+          <t>提供图原生基础设施以构建可解释的AI系统
+【原文】Graph-Native Infrastructure for Context and Accountable AI Systems</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -3024,7 +3010,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3034,7 +3020,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Developer-Y/cs-video-courses</t>
+          <t>https://github.com/semantica-agi/semantica</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3043,14 +3029,18 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>23.12</v>
+        <v>28.37</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3063,21 +3053,21 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>algorithms, bioinformatics, computational-biology, computational-physics, computer-architecture, computer-science, computer-vision, database-systems, databases, deep-learning, embedded-systems, machine-learning</t>
+          <t>agent-memory, ai, ai-governance, ai-infrastructure, artificial-intelligence, context-engineering, context-graphs, data-engineering, decision-intelligence, developer-tools, explainable-ai, generative-ai</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2016-10-21</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>3610</v>
+        <v>442</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -3089,26 +3079,26 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>OpenPipe/ART</t>
+          <t>OpenBMB/MiniCPM-V</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>10707</v>
+        <v>26333</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>136.8</v>
+        <v>193</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>训练多步骤代理用于现实任务，支持多种LLM
-【原文】Agent Reinforcement Trainer: train multi-step agents for real-world tasks using GRPO. Give your agents on-the-job training. Reinforcement learning for Qwen3.6, GPT-OSS, Llama, and more!</t>
+          <t>在手机上实现高效的图像和视频理解
+【原文】A Pocket-Sized MLLM for Ultra-Efficient Image and Video Understanding on Your Phone</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -3118,7 +3108,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3133,7 +3123,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/OpenPipe/ART</t>
+          <t>https://github.com/OpenBMB/MiniCPM-V</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3142,7 +3132,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>19.54</v>
+        <v>27.57</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3166,21 +3156,21 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, grpo, llms, lora, qwen, qwen3, reinforcement-learning, rl</t>
+          <t>minicpm, minicpm-o, minicpm-v, multi-modal</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2025-03-10</t>
+          <t>2024-01-29</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>548</v>
+        <v>955</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3192,41 +3182,42 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Asabeneh/30-Days-Of-JavaScript</t>
+          <t>GLips/Figma-Context-MCP</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>46776</v>
+        <v>15817</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>133.6</v>
+        <v>192.9</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>提供JavaScript编程挑战的指南和视频
-【原文】30 days of JavaScript programming challenge is a step-by-step guide to learn JavaScript programming language in 30 days. This challenge may take more than 100 days,  please just follow your own pace. These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
+          <t>为Figma布局信息提供MCP服务器
+【原文】MCP server to provide Figma layout information to AI coding agents like Cursor
+【依据】MCP server to provide Figma layout information to AI coding agents like Cursor.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/架构参考</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H28" s="7" t="inlineStr">
@@ -3236,7 +3227,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Asabeneh/30-Days-Of-JavaScript</t>
+          <t>https://github.com/GLips/Figma-Context-MCP</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3245,16 +3236,16 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>19.08</v>
+        <v>27.56</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3269,24 +3260,24 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>30daysofjavascript, angular, challenge, css, d3, d3js, html, javascript, javascript-for-everyone, js, json, node</t>
+          <t>ai, cursor, figma, mcp, typescript</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2019-12-23</t>
+          <t>2025-02-13</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>2452</v>
+        <v>574</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
@@ -3295,42 +3286,41 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>agentpit-io/hunter-community</t>
+          <t>paperless-ngx/paperless-ngx</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>497</v>
+        <v>44970</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>116</v>
+        <v>188.4</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>私人金融AI团队，提供AI智能体和AI量化服务
-【原文】Hunter Community Edition · 私人金融 AI 团队 · AI 智能体 + AI 量化 · 开源自托管 · powered by opencode + Claude Code + MCP + multi-agent · your private financial AI team · open-source self-hosted · 15 min docker start
-【依据】AI智能体 + AI量化 · 开源自托管 · 15 min docker start</t>
+          <t>提供文档管理系统，支持扫描、索引和存档文档
+【原文】A community-supported supercharged document management system: scan, index and archive all your documents</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G29" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3340,7 +3330,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/agentpit-io/hunter-community</t>
+          <t>https://github.com/paperless-ngx/paperless-ngx</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3349,11 +3339,11 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>16.57</v>
+        <v>26.91</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -3373,62 +3363,63 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, ai-hedge-fund, ai-quant, anthropic, apache-2, claude-agent-sdk, claude-code, codex, docker-compose, financial-ai, fintech, llm-agent</t>
+          <t>ai, angular, archiving, django, dms, document-management, document-management-system, llm, machine-learning, ocr, optical-character-recognition, pdf</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2022-02-12</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>30</v>
+        <v>1671</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>yifanfeng97/Hyper-Extract</t>
+          <t>onyx-dot-app/onyx</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>3925</v>
+        <v>32006</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>112.1</v>
+        <v>181.9</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>将文本转换为结构化知识的工具
-【原文】Hypergraph is more powerful. Transform unstructured text into structured knowledge with LLMs. Graphs, hypergraphs, and spatio-temporal extractions — with one command.</t>
+          <t>提供具有高级功能的AI聊天平台
+【原文】Open Source AI Platform - AI Chat with advanced features that works with every LLM
+【依据】Open Source AI Platform - AI Chat with advanced features that works with every LLM.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线/未归类</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/可部署服务</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3443,7 +3434,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yifanfeng97/Hyper-Extract</t>
+          <t>https://github.com/onyx-dot-app/onyx</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3452,7 +3443,7 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>16.02</v>
+        <v>25.98</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
@@ -3476,24 +3467,24 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-agents, cli, hypergraph, information-extraction, knowledge, knowledge-graph, llm, python, rag</t>
+          <t>ai, ai-chat, chatgpt, chatui, enterprise-search, gen-ai, information-retrieval, llm, llm-ui, nextjs, python, rag</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2023-04-27</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>245</v>
+        <v>1232</v>
       </c>
       <c r="T30" s="3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
@@ -3502,31 +3493,31 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>thu-ml/TurboDiffusion</t>
+          <t>elizaOS/eliza</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>3639</v>
+        <v>19312</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>92</v>
+        <v>170.5</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>加速视频扩散模型
-【原文】TurboDiffusion: 100–200× Acceleration for Video Diffusion Models</t>
+          <t>开源的自主操作系统框架
+【原文】Open source agentic operating system</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -3546,7 +3537,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/thu-ml/TurboDiffusion</t>
+          <t>https://github.com/elizaOS/eliza</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3555,16 +3546,16 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>13.14</v>
+        <v>24.35</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
@@ -3579,21 +3570,21 @@
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
-          <t>ai-infra, consistency-model, diffusion-models, distillation, inference-acceleration, mlsystem, rcm, sageattention, sparse-linear-attention, video-generation</t>
+          <t>agent, agentic, ai, autonomous, chatbot, crypto, discord, eliza, elizaos, framework, plugins, rag</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2025-12-06</t>
+          <t>2024-07-09</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>277</v>
+        <v>793</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3605,41 +3596,41 @@
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>topic:video-generation stars:&gt;3000 pushed:&gt;2026-06-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>iina/iina</t>
+          <t>ningzimu/image-to-editable-ppt-skill</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>46280</v>
+        <v>2429</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>91.2</v>
+        <v>151.8</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>为macOS提供现代视频播放器
-【原文】The modern video player for macOS.</t>
+          <t>将图像、PDF转换为可编辑的PPT演示文稿
+【原文】Codex skill for converting slide images, PDFs, and image-based PPTX files into editable PowerPoint decks.</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>图文产线/视频产线</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H32" s="7" t="inlineStr">
@@ -3649,7 +3640,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iina/iina</t>
+          <t>https://github.com/ningzimu/image-to-editable-ppt-skill</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3658,16 +3649,16 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>13.03</v>
+        <v>21.69</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3682,21 +3673,21 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>hacktoberfest, macos, mpv, swift, video, video-player</t>
+          <t>codex, codex-skill, editable-ppt, image-to-ppt, imagegen, multi-agent, pdf-to-pptx, powerpoint, pptx, presentation</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2016-12-19</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>3551</v>
+        <v>112</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3708,42 +3699,41 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>TriliumNext/Trilium</t>
+          <t>cocoindex-io/cocoindex</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>37775</v>
+        <v>11517</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>77.8</v>
+        <v>145</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>构建个人知识库
-【原文】Build your personal knowledge base with Trilium Notes
-【依据】knowledge-base, knowledge-graph, knowledge-management</t>
+          <t>为长期代理提供增量引擎
+【原文】Incremental engine for long horizon agents 🌟 Star if you like it!</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H33" s="7" t="inlineStr">
@@ -3753,7 +3743,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/TriliumNext/Trilium</t>
+          <t>https://github.com/cocoindex-io/cocoindex</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3762,16 +3752,16 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>11.12</v>
+        <v>20.71</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3786,24 +3776,24 @@
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>electron, electron-app, knowledge-base, knowledge-graph, knowledge-management, knowledge-management-graph, local-first, note-managment, note-taker, note-taking, notebook, notes</t>
+          <t>agentic-data-framework, ai, ai-agents, change-data-capture, codebase-intelligence, context-engineering, data-engineering, data-indexing, data-processing, etl, help-wanted, indexing</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2017-05-23</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>3396</v>
+        <v>556</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
@@ -3812,36 +3802,36 @@
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>2FastLabs/agent-squad</t>
+          <t>promptfoo/promptfoo</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>7757</v>
+        <v>24982</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>69.8</v>
+        <v>142</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>管理多个AI代理和复杂对话的灵活框架
-【原文】Flexible and powerful framework for managing multiple AI agents and handling complex conversations</t>
+          <t>测试和评估AI的提示词、代理和RAG
+【原文】Test your prompts, agents, and RAGs. Red teaming/pentesting/vulnerability scanning for AI. Compare performance of GPT, Claude, Gemini, DeepSeek, and more. Simple declarative configs with command line and CI/CD integration.  Used by OpenAI and Anthropic.</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>技能包/代码库</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3856,7 +3846,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/2FastLabs/agent-squad</t>
+          <t>https://github.com/promptfoo/promptfoo</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3865,16 +3855,16 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>9.970000000000001</v>
+        <v>20.29</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>Swift</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3889,21 +3879,21 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, ai-agents, ai-agents-framework, anthropic, anthropic-claude, aws, aws-bedrock, aws-cdk, aws-lambda, chatbot, framework</t>
+          <t>ci, ci-cd, cicd, evaluation, evaluation-framework, llm, llm-eval, llm-evaluation, llm-evaluation-framework, llmops, pentesting, prompt-engineering</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2024-07-23</t>
+          <t>2023-04-28</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>778</v>
+        <v>1231</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
@@ -3915,42 +3905,41 @@
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>mex-memory/mex</t>
+          <t>JunkFood02/Seal</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>1572</v>
+        <v>28855</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>64</v>
+        <v>125.5</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>为工程师和他们的AI代理提供团队记忆
-【原文】Team memory for engineers and their AI agents. Lives in your repo. Shared through Git.
-【依据】topics: knowledge-graph</t>
+          <t>提供Android视频/音频下载器，基于yt-dlp
+【原文】🦭 Video/Audio Downloader for Android, based on yt-dlp</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>可部署服务</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -3960,7 +3949,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mex-memory/mex</t>
+          <t>https://github.com/JunkFood02/Seal</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3969,16 +3958,16 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>9.140000000000001</v>
+        <v>17.93</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Kotlin</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3993,21 +3982,21 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>claude-code, claude-code-skills, cli-tool, code-graph, codex, context-management, cursor, developer-tools, documentation, knowledge-graph, llm, mcp-server</t>
+          <t>android, f-droid, jetpack-compose, kotlin, material-design, youtube-dl, youtube-downloader, yt-dlp</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2026-03-21</t>
+          <t>2022-04-15</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>172</v>
+        <v>1609</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
@@ -4019,42 +4008,41 @@
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>axoviq-ai/synthadoc</t>
+          <t>cometcanaryview7/canva-pro</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>1175</v>
+        <v>619</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>54.5</v>
+        <v>117.1</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>将原始文档转换为结构化、本地优先的维基百科
-【原文】Synthadoc: An open-source LLM knowledge compilation engine that turns raw documents into structured, local-first wikis. A transparent, human-readable alternative to traditional RAG, which can be self-managed and self-improved without the use of any tools.
-【依据】topics: knowledge-graph</t>
+          <t>提供Canva Pro的高级图形设计工具和团队协作工作流程
+【原文】Canva Pro Cloud Toolkit &amp; Automation Studio. Advanced graphic design assets, team collaboration workflows, premium template management, and visual content creation tools.</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -4064,7 +4052,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/axoviq-ai/synthadoc</t>
+          <t>https://github.com/cometcanaryview7/canva-pro</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4073,18 +4061,14 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>7.78</v>
+        <v>16.73</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr"/>
       <c r="N36" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -4097,12 +4081,12 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, agentic-ai, cli-tool, domain-adaptation, enterprise, enterprise-solutions, knowledge-graph, local-llm, obsidian-md, obsidian-plugin, personal-knowledge-management, pkm</t>
+          <t>canva, canva-bulk-create, canva-editor-tools, canva-export-tools, canva-free, canva-full, canva-hack, canva-pro, canva-pro-for-life-time, canva-pro-team-2026, figma-alternative, figma-design</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
@@ -4111,7 +4095,7 @@
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
@@ -4123,37 +4107,36 @@
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>content automation in:name,description stars:&gt;500 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>ModernRelay/omnigraph</t>
+          <t>agentscope-ai/agentscope-java</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>1102</v>
+        <v>5530</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>50.8</v>
+        <v>110</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>提供湖屋原生图引擎，支持git-style workflows
-【原文】Lakehouse native graph engine with git-style workflows
-【依据】topics: knowledge-graph, lakehouse</t>
+          <t>构建分布式、生产级、长期运行的代理
+【原文】Build distributed, production-grade, long-running agents.</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -4168,7 +4151,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ModernRelay/omnigraph</t>
+          <t>https://github.com/agentscope-ai/agentscope-java</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4177,16 +4160,16 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>7.25</v>
+        <v>15.71</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -4201,21 +4184,21 @@
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
-          <t>apache-arrow, context-graph, datafusion, graph-database, knowledge-graph, lakehouse, lance, mcp, rust, s3, versioning</t>
+          <t>adk, agent, agent-framework, agentic, agentic-ai, agentscope, ai, harness, llm</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>152</v>
+        <v>352</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -4227,42 +4210,41 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>videojs/video.js</t>
+          <t>ruvnet/RuVector</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>39880</v>
+        <v>4487</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>46.8</v>
+        <v>106.5</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>提供HTML5视频播放功能
-【原文】Video.js - open source HTML5 video player
-【依据】topics: video-player</t>
+          <t>高性能实时自学习AI，向量GNN，内存数据库
+【原文】RuVector is a High Performance, Real-Time, Self-Learning Ai, Vector GNN, Memory DB built in Rust.</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -4272,7 +4254,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/videojs/video.js</t>
+          <t>https://github.com/ruvnet/RuVector</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4281,16 +4263,16 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>6.69</v>
+        <v>15.21</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4305,21 +4287,21 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>dash, hls, html, html5, html5-audio, html5-video, javascript, player, video, video-player, videojs</t>
+          <t>ai, ai-ocr, attention-mechanism, gnn, gnn-model, gnns, graph, graph-neural-networks, llm-inference, low-latency, mincut, neo4j</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2010-05-14</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>5962</v>
+        <v>295</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
@@ -4331,42 +4313,41 @@
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>jitsi/jitsi-meet</t>
+          <t>Asabeneh/30-Days-Of-React</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>29895</v>
+        <v>27490</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>45</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>提供安全、简单且可扩展的视频会议服务
-【原文】Jitsi Meet - Secure, Simple and Scalable Video Conferences that you use as a standalone app or embed in your web application.
-【依据】topics: video-conferencing</t>
+          <t>提供30天React挑战，逐步指导学习React
+【原文】30 Days of  React challenge is a step by step guide to learn React in 30 days.  These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -4376,7 +4357,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jitsi/jitsi-meet</t>
+          <t>https://github.com/Asabeneh/30-Days-Of-React</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4385,16 +4366,16 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>6.43</v>
+        <v>12.66</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4409,21 +4390,21 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>debian, deep-video, jitsi, jitsi-meet, scalable-video-conferences, sfu, video, video-communication, video-conferencing, webrtc</t>
+          <t>30dayofjavascript, challenge, css, html, html5, javascript, js, programming, react, react-router-dom, reactjs, redux</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2013-12-16</t>
+          <t>2020-09-29</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>4650</v>
+        <v>2172</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4435,41 +4416,41 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>beclab/Olares</t>
+          <t>Unstructured-IO/unstructured</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>5262</v>
+        <v>15412</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>42.7</v>
+        <v>74.7</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>为始终在线代理的开源个人云操作系统
-【原文】Open-Source Personal Cloud OS for Always-On Agents</t>
+          <t>将文档转换为结构化数据的 HTML 库
+【原文】Convert documents to structured data effortlessly. Unstructured is open-source ETL solution for transforming complex documents into clean, structured formats for language models.  Visit our website to learn more about our enterprise grade Platform product for production grade workflows, partitioning, enrichments, chunking and embedding.</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
-        </is>
-      </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>数据集/代码库</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H40" s="7" t="inlineStr">
@@ -4479,7 +4460,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/beclab/Olares</t>
+          <t>https://github.com/Unstructured-IO/unstructured</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4488,16 +4469,16 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>6.1</v>
+        <v>10.67</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4512,21 +4493,21 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-agents, cloud-native, data-privacy, edge-ai, homelab, kubernetes, local-ai, model-serving, operating-system, personal-cloud, self-hosted</t>
+          <t>data-pipelines, deep-learning, document-image-analysis, document-image-processing, document-parser, document-parsing, docx, donut, information-retrieval, langchain, llm, machine-learning</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2022-09-26</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>863</v>
+        <v>1445</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
@@ -4538,42 +4519,41 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-10</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>huiliyi37/Tianshu-harness</t>
+          <t>mg-chao/snow-apps</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>522</v>
+        <v>4982</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>39.7</v>
+        <v>62.2</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>终端编程智能体运行时，针对DeepSeek V4优化
-【原文】天枢 (Tianshu) 是一个基于harness工程的终端编程智能体运行时（Tui X Gui），针对DeepSeek V4 做了前缀缓存工程优化（长会话实测稳态命中率 97–99%）和深度适配。它跳出了传统 AI 编程助手把大模型仅当成“工具”的局限，基于认知虚拟机 (CVM)、自感知层和信息素（Stigmergy）自衰减记忆构建，让 AI 成为有独立判断与认知防护的“开发伙伴”。
-【依据】基于harness工程的终端编程智能体运行时，针对DeepSeek V4做了前缀缓存工程优化</t>
+          <t>提供图像查看器、OCR 和屏幕录制工具的 C++ 代码库
+【原文】Snow Apps repository, providing source code for Snow Shot and Snow Image Viewer.</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>图文产线/古籍OCR线</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -4583,7 +4563,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/huiliyi37/Tianshu-harness</t>
+          <t>https://github.com/mg-chao/snow-apps</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4592,16 +4572,16 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>5.67</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -4616,68 +4596,67 @@
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, coding-agent, context-management, deepseek, dsh, gui, harness, harness-engineering, prefix-cache, tui</t>
+          <t>image-viewer, ocr, screen-recorder, screenshot, tools</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>92</v>
+        <v>561</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>FalkorDB/FalkorDB</t>
+          <t>ShareX/ShareX</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>5983</v>
+        <v>39508</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>36.5</v>
+        <v>58.6</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>提供高速图数据库，用于知识图谱
-【原文】A super fast Graph Database uses GraphBLAS under the hood for its sparse adjacency matrix graph representation. Our goal is to provide the best Knowledge Graph for LLM (GraphRAG).
-【依据】topics: knowledge-graph</t>
+          <t>屏幕区域捕获和文件上传工具
+【原文】ShareX is a free and open-source application that enables users to capture or record any area of their screen with a single keystroke. It also supports uploading images, text, and various file types to a wide range of destinations.</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G42" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G42" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -4687,7 +4666,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/FalkorDB/FalkorDB</t>
+          <t>https://github.com/ShareX/ShareX</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -4696,16 +4675,16 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>5.22</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4720,21 +4699,21 @@
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
-          <t>cloud-database, database, database-as-a-service, developer-tools, devtools, graph-database, graphrag, knowledge-graph, realtime-database</t>
+          <t>avalonia, capture, color-picker, csharp, dropbox, file-sharing, file-upload, ftp, gif, gif-recorder, image-annotation, ocr</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2013-10-08</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>1147</v>
+        <v>4720</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>1</v>
@@ -4746,26 +4725,26 @@
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>LLMQuant/quant-mind</t>
+          <t>raphaelmansuy/edgequake</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2825</v>
+        <v>2092</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>36.3</v>
+        <v>55.6</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>量化金融领域的知识提取和检索框架
-【原文】QuantMind is an agent-native knowledge extraction and retrieval framework for quantitative finance.</t>
+          <t>将文档转换为智能知识图谱
+【原文】EdegQuake 🌋 High-performance GraphRAG inspired from LightRag written in Rust; Transform documents into intelligent knowledge graphs for superior retrieval and generation</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
@@ -4775,7 +4754,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4790,7 +4769,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LLMQuant/quant-mind</t>
+          <t>https://github.com/raphaelmansuy/edgequake</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4799,16 +4778,16 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>5.19</v>
+        <v>7.95</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4823,21 +4802,21 @@
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
-          <t>agent, context-engineering, data, harness-engineering, knowledge, llm, pipeline, quantitative-finance, quantitative-research, workflow</t>
+          <t>graphrag, knowledge-graph, lightrag, rag</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2025-03-14</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>544</v>
+        <v>263</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>1</v>
@@ -4849,42 +4828,42 @@
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>LadybugDB/ladybug</t>
+          <t>najmuzzaman-mohammad/gawkbot</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>1724</v>
+        <v>1287</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>35.8</v>
+        <v>53.3</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>提供图数据库服务
-【原文】LadybugDB a graph database
-【依据】topics: graph-database</t>
+          <t>开源的 grok bot，通过 AI 模型自动化工作并构建微应用
+【原文】open source grok bot. gawk bots automate your menial work via AI models and build you microapps to manage the outcome, so that you have a false sense of control.
+【依据】open source grok bot. gawk bots automate your menial work via AI models and build you microapps to manage the outcome.</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -4894,7 +4873,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LadybugDB/ladybug</t>
+          <t>https://github.com/najmuzzaman-mohammad/gawkbot</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4903,16 +4882,16 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>5.12</v>
+        <v>7.62</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4927,12 +4906,12 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>code-knowledge-base, code-knowledge-graph, cypher, cypher-query-language, database, graph, knowledge-graph</t>
+          <t>agents, ai-agents, ai-teammates, autonomous-agents, claude-code, codex, grok-bot, grok-bot-alternative, grokbot, knowledge-graph, local-llm, microapps</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
@@ -4941,7 +4920,7 @@
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>337</v>
+        <v>169</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>1</v>
@@ -4953,41 +4932,41 @@
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-10</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>urchade/GLiNER</t>
+          <t>NickeManarin/ScreenToGif</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>3624</v>
+        <v>27613</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>24.6</v>
+        <v>52.4</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>轻量级命名实体识别模型
-【原文】Generalist and Lightweight Model for Named Entity Recognition (Extract any entity types from texts)</t>
+          <t>提供屏幕录制和编辑工具，支持保存为gif或视频
+【原文】🎬 ScreenToGif allows you to record a selected area of your screen, edit and save it as a gif or video.</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4997,7 +4976,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/urchade/GLiNER</t>
+          <t>https://github.com/NickeManarin/ScreenToGif</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -5006,16 +4985,16 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>3.52</v>
+        <v>7.48</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MS-PL</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
@@ -5030,21 +5009,21 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>information-extraction, large-language-models, named-entity-recognition, natural-language-processing, prompt-tuning</t>
+          <t>editor, gif, recorder, sketchboard, video, webcam, wpf</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2023-11-14</t>
+          <t>2016-08-02</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>1030</v>
+        <v>3691</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>1</v>
@@ -5056,26 +5035,26 @@
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>trustgraph-ai/trustgraph</t>
+          <t>pipeshub-ai/pipeshub-ai</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>2697</v>
+        <v>3735</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>23.9</v>
+        <v>47.2</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>基于超图的上下文编排层，构建统一语义上下文层
-【原文】The context orchestration layer powered by hypergraphs. Build a unified semantic context layer where agentic outcomes are deterministic and agent behavior is not just traceable, but cryptographically verifiable.</t>
+          <t>连接企业知识到 AI 的开源平台，提供权限感知搜索和知识图谱
+【原文】PipesHub is an open-source platform for securely connecting enterprise knowledge to AI. Give AI agents trusted context and your team permission-aware search with verified citations across your business systems.</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
@@ -5085,7 +5064,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -5100,7 +5079,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/trustgraph-ai/trustgraph</t>
+          <t>https://github.com/pipeshub-ai/pipeshub-ai</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5109,7 +5088,7 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>3.41</v>
+        <v>6.75</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -5133,21 +5112,21 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>agent, agent-harness, context, context-engineering, context-graph, context-harness, context-orchestration, determinism, explainable-ai, graph, graph-engineering, help-wanted</t>
+          <t>agent, agents, ai, drive, glean, gmail, knowledge-graph, langchain, langgraph, llamaparse, notion, ollama</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2024-07-10</t>
+          <t>2025-03-06</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>791</v>
+        <v>553</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>2</v>
@@ -5159,26 +5138,26 @@
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>BruceLanLan/augur</t>
+          <t>zhitongblog/solomd</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>526</v>
+        <v>1024</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>23.7</v>
+        <v>46.3</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>多智能体投资分析系统，提供投资大师分析及共识机制
-【原文】🦉 Augur — 多智能体投资分析系统。13位虚拟投资大师独立分析，加权共识机制，Bloomberg风格Web仪表盘。</t>
+          <t>Markdown编辑器，连接LLM的桥梁，包含MCP服务器
+【原文】A markdown editor — and the bridge to your LLM. Local-first, MIT, ~15 MB. Bundled MCP server lets Claude Code / Codex / Cursor drive your vault directly. 14 AI providers BYOK.</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -5203,7 +5182,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/BruceLanLan/augur</t>
+          <t>https://github.com/zhitongblog/solomd</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5212,7 +5191,7 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>3.39</v>
+        <v>6.61</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -5221,7 +5200,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -5236,17 +5215,17 @@
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, investment-analysis, multi-agent, stock-analysis, value-investing</t>
+          <t>ai, android, autogit, byok, cross-platform, ios, knowledge-base, local-first, markdown, markdown-editor, mcp, mcp-server</t>
         </is>
       </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S47" s="3" t="n">
@@ -5257,41 +5236,41 @@
       </c>
       <c r="U47" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>zjunlp/DeepKE</t>
+          <t>CarGuo/GSYVideoPlayer</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>4478</v>
+        <v>21490</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>10.6</v>
+        <v>41.9</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>知识图谱提取与构建工具
-【原文】[EMNLP 2022] An Open Toolkit for Knowledge Graph Extraction and Construction</t>
+          <t>提供视频播放器、支持16k页面大小、弹幕等
+【原文】Video players (IJKplayer, ExoPlayer, MediaPlayer), HTTPS, 16k page size, danmaku (bullet chat) support, external subtitles, support for filters, watermarks, and GIF screenshots, pre-roll and mid-roll ads, multiple simultaneous playback, basic seeking/dragging, volume and brightness adjustment, play-while-cache support</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>可部署服务</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5306,7 +5285,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zjunlp/DeepKE</t>
+          <t>https://github.com/CarGuo/GSYVideoPlayer</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5315,16 +5294,16 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>1.51</v>
+        <v>5.99</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -5339,24 +5318,24 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>attribute-extraction, chinese, deep-learning, deepke, document-level, few-shot, information-extraction, instructie, kg, knowledge-graph, knowprompt, lightner</t>
+          <t>16k, android, exoplayer, ffmpeg, gsy, ijkplayer, player, ssl, video, videocache</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>2018-08-01</t>
+          <t>2016-11-13</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>2961</v>
+        <v>3588</v>
       </c>
       <c r="T48" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U48" s="3" t="inlineStr">
         <is>
@@ -5365,26 +5344,26 @@
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>knowledge extraction in:name,description stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>socai-io/socai</t>
+          <t>kyegomez/swarms</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>184</v>
+        <v>7161</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>9.9</v>
+        <v>41.2</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>为小红书优化的Web Use Agent
-【依据】topics: xhs, xiaohongshu</t>
+          <t>提供企业级多代理编排框架的 Python 库
+【原文】The Enterprise-Grade Multi-Agent Orchestration Framework. Website: https://swarms.ai</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -5394,7 +5373,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5409,7 +5388,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/socai-io/socai</t>
+          <t>https://github.com/kyegomez/swarms</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5418,7 +5397,7 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>1.42</v>
+        <v>5.88</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -5427,7 +5406,7 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -5442,24 +5421,24 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>agent, browser-use, claude, codex, compute-use, linkedin, tiktok, xhs, xiaohongshu</t>
+          <t>agentic-ai, agentic-workflow, agents, ai, artificial-intelligence, chatgpt, claude-code, gpt4all, huggingface, langchain, langchain-python, machine-learning</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2023-05-11</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>130</v>
+        <v>1218</v>
       </c>
       <c r="T49" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U49" s="3" t="inlineStr">
         <is>
@@ -5468,26 +5447,26 @@
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>auto publish douyin xiaohongshu in:name,description,readme stars:&gt;100</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>LHRLAB/Graph-R1</t>
+          <t>modelscope/evalscope</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>591</v>
+        <v>3401</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>7.6</v>
+        <v>23.6</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>基于强化学习的GraphRAG框架研究资源
-【原文】[ICML 2026] Official resources of "Graph-R1: Towards Agentic GraphRAG Framework via End-to-end Reinforcement Learning".</t>
+          <t>用于高效评估大型模型（LLM、VLM、AIGC）的框架
+【原文】A streamlined and customizable framework for efficient large model (LLM, VLM, AIGC) evaluation and performance benchmarking.</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5497,7 +5476,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5512,7 +5491,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LHRLAB/Graph-R1</t>
+          <t>https://github.com/modelscope/evalscope</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5521,11 +5500,11 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>1.08</v>
+        <v>3.37</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
@@ -5545,21 +5524,21 @@
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>chain-of-thought, graphrag, hypergraph, reinforcement-learning</t>
+          <t>evaluation, llm, performance, rag, vlm</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>2025-03-11</t>
+          <t>2023-12-07</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>547</v>
+        <v>1008</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>1</v>
@@ -5571,26 +5550,26 @@
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>KRLabsOrg/LettuceDetect</t>
+          <t>doobidoo/mcp-memory-service</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>605</v>
+        <v>1933</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>7.3</v>
+        <v>21.7</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>RAG输出验证工具，用于代码和工具的验证
-【原文】Span-level grounding verification for RAG, code, and tool-grounded AI outputs.</t>
+          <t>为 AI 代理管道提供持久化内存服务，包括知识图谱和自主合并
+【原文】Open-source persistent memory for AI agent pipelines (LangGraph, CrewAI, AutoGen) and Claude. REST API + knowledge graph + autonomous consolidation.</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -5600,7 +5579,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>MCP服务/可部署服务/代码库</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -5615,7 +5594,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/KRLabsOrg/LettuceDetect</t>
+          <t>https://github.com/doobidoo/mcp-memory-service</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5624,11 +5603,11 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>1.04</v>
+        <v>3.1</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
@@ -5648,21 +5627,21 @@
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>bert, hallucination-detection, hallucination-evaluation, information-extraction, nlp, python, pytorch, token-classification</t>
+          <t>agent-memory, agentic-ai, ai-agents, autogen, claude, crewai, knowledge-graph, langgraph, long-term-memory, mcp, mcp-server, memory</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>2025-02-05</t>
+          <t>2024-12-26</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>581</v>
+        <v>623</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>1</v>
@@ -5674,41 +5653,41 @@
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>JabRef/jabref</t>
+          <t>CrossPaste/crosspaste-desktop</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>4704</v>
+        <v>2547</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>7.2</v>
+        <v>17.4</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>管理BibTeX和BibLaTeX (.bib)库的桌面应用程序
-【原文】Desktop app for managing BibTeX and BibLaTeX (.bib) libraries</t>
+          <t>提供跨设备剪贴板同步的 Kotlin 应用程序，内置 OCR 和 CLI 服务器
+【原文】Cross-device clipboard sync for macOS, Windows &amp; Linux — end-to-end encrypted, LAN-only, no cloud. OCR, CLI and MCP server built in.</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>可部署服务/技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G52" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -5718,7 +5697,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/JabRef/jabref</t>
+          <t>https://github.com/CrossPaste/crosspaste-desktop</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5727,16 +5706,16 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>1.03</v>
+        <v>2.48</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Kotlin</t>
         </is>
       </c>
       <c r="N52" s="3" t="inlineStr">
@@ -5751,24 +5730,24 @@
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>academia, academic-publications, ai, biblatex, bibliography, bibtex, citation, citation-generator, citation-style-language, citation-styles, hacktoberfest, jabref</t>
+          <t>cli, clipboard, clipboard-history, clipboard-manager, clips, compose-desktop, copy-paste, cross-platform, desktop-application, end-to-end-encryption, kotlin-multiplatform, local-first</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>2014-03-11</t>
+          <t>2023-11-16</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>4565</v>
+        <v>1029</v>
       </c>
       <c r="T52" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
@@ -5777,26 +5756,26 @@
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>alaskasquirrel/Email-newsletter-RSS</t>
+          <t>dickwu/apple-design-skill</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>1647</v>
+        <v>390</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>6.4</v>
+        <v>14</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>邮箱、新闻简报和RSS聚合工具
-【原文】邮箱 📧 newsletter RSS 荟萃 News</t>
+          <t>基于Apple HIG的跨平台UI/UX设计审查器
+【原文】Cross-platform UI/UX design reviewer based on Apple HIG. Works with Flutter, Tauri, Electron, React Native. Compatible with Claude Code, Cursor, Codex.</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -5806,12 +5785,12 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -5821,7 +5800,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/alaskasquirrel/Email-newsletter-RSS</t>
+          <t>https://github.com/dickwu/apple-design-skill</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5830,14 +5809,18 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>0.91</v>
+        <v>2</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M53" s="3" t="inlineStr"/>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>JavaScript</t>
+        </is>
+      </c>
       <c r="N53" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5850,52 +5833,52 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>chinese, email, newsletter, rss</t>
+          <t>apple-hig, claude-code, codex, cursor, design-system, electron, flutter, liquid-glass, tauri, ui-ux</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>2021-09-19</t>
+          <t>2026-02-27</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-05</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>1816</v>
+        <v>195</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V53" s="6" t="inlineStr">
         <is>
-          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-10</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>monarch-initiative/ontogpt</t>
+          <t>cyanfish/naps2</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>1006</v>
+        <v>4502</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>5.2</v>
+        <v>7.8</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>基于LLM的实体抽取工具，包括SPIRES
-【原文】LLM-based ontological extraction tools, including SPIRES</t>
+          <t>扫描文档到PDF等格式
+【原文】Scan documents to PDF and more, as simply as possible.</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5910,7 +5893,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -5920,7 +5903,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/monarch-initiative/ontogpt</t>
+          <t>https://github.com/cyanfish/naps2</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5929,16 +5912,16 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>0.75</v>
+        <v>1.11</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5953,12 +5936,12 @@
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>ai, chat-gpt, data-modeling, gpt-3, information-extraction, language-models, large-language-models, linkml, llm, monarchinitiative, named-entity-recognition, ner</t>
+          <t>csharp, dotnet, escl, linux, macos, ocr, pdf, sane, scanner, twain, wia, windows</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>2023-01-03</t>
+          <t>2015-07-19</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
@@ -5967,7 +5950,7 @@
         </is>
       </c>
       <c r="S54" s="3" t="n">
-        <v>1345</v>
+        <v>4071</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>1</v>
@@ -5979,26 +5962,26 @@
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>LHRLAB/HyperGraphRAG</t>
+          <t>aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>451</v>
+        <v>3355</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>提供基于超图结构的检索增强生成资源
-【原文】[NeurIPS 2025] Official resources of "HyperGraphRAG: Retrieval-Augmented Generation via Hypergraph-Structured Knowledge Representation".</t>
+          <t>无需登录的免费网络应用列表
+【原文】🚀 Awesome (free) web apps that work without login</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -6013,7 +5996,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H55" s="7" t="inlineStr">
@@ -6023,7 +6006,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LHRLAB/HyperGraphRAG</t>
+          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6032,16 +6015,16 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.72</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Shell</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -6056,21 +6039,21 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>graphrag, hypergraph, knowledge-graph, large-language-models</t>
+          <t>application, applications, awesome, awesome-list, awesomeness, list, no-login, no-login-web-apps, portableapps, web-app</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>2024-12-19</t>
+          <t>2016-12-06</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S55" s="3" t="n">
-        <v>629</v>
+        <v>3565</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>1</v>
@@ -6082,26 +6065,26 @@
       </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>dromara/dante-cloud</t>
+          <t>wenhwu/awesome-remote-sensing-change-detection</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>959</v>
+        <v>2325</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>3.4</v>
+        <v>5.7</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>微服务云原生基座和AI Agent开发平台
-【原文】🐉 Dante Cloud 是支持阻塞式与响应式服务并行的微服务云原生基座和面向AI Agent开发的智能基座，基于领域驱动模型（DDD）设计，以高质量代码与低安全漏洞为核心，高度模块化、组件化，覆盖IoT设备认证、国家等保三级、接口国密数字信封加密等多层次安全体系，并提供多租户解决方案。独创“一套代码实现微服务和单体架构灵活切换”，赋能企业级智能应用构建。🔝🔝点个star 持续关注更新！</t>
+          <t>收集远程传感变化检测的数据集和工具
+【原文】A comprehensive and up-to-date compilation of datasets, tools, methods, review papers, and competitions for remote sensing change detection.</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -6111,12 +6094,12 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -6126,7 +6109,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dromara/dante-cloud</t>
+          <t>https://github.com/wenhwu/awesome-remote-sensing-change-detection</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6135,18 +6118,14 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.49</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr">
-        <is>
-          <t>Java</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr"/>
       <c r="N56" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6159,12 +6138,12 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>ai-agent, harness-engineering, iot, loki, microservices, monolith, monorepo, mqtt, nacos, rsocket, spring-ai, spring-ai-alibaba</t>
+          <t>awesome, change-detection, dataset, deep-learning, remote-sensing</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>2021-05-19</t>
+          <t>2018-11-03</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
@@ -6173,53 +6152,53 @@
         </is>
       </c>
       <c r="S56" s="3" t="n">
-        <v>1939</v>
+        <v>2868</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U56" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>智能体 in:name,description stars:&gt;200</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>ail-project/ail-framework</t>
+          <t>zibo-chen/ocr-rs</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>1013</v>
+        <v>326</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>信息泄露分析框架
-【原文】AIL framework - Analysis Information Leak framework</t>
+          <t>提供高性能OCR识别库，支持多种语言和调用方式
+【原文】高性能OCR识别库，支持上百种语言，提供命令行、图形界面及C API多种调用方式，使用便捷高效。  High-performance OCR library powered by PaddleOCR v4/v5/v6 with MNN backend. Supports 10+ languages (Chinese, English, Japanese, Korean, Arabic, Cyrillic, Thai, etc). Provides Rust crate + C API + CLI tools. Fast, lightweight, easy-to-integrate.</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>古籍OCR线</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G57" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G57" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -6229,7 +6208,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ail-project/ail-framework</t>
+          <t>https://github.com/zibo-chen/ocr-rs</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6238,16 +6217,16 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.43</v>
+        <v>0.63</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -6262,12 +6241,12 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>ail-framework, darkweb, darkweb-scraping, data-mining, information-extraction, information-security, leak</t>
+          <t>ocr, ocr-rs, paddleocr, tesseract-ocr</t>
         </is>
       </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>2020-04-20</t>
+          <t>2025-04-12</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
@@ -6276,48 +6255,48 @@
         </is>
       </c>
       <c r="S57" s="3" t="n">
-        <v>2333</v>
+        <v>516</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U57" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>topic:information-extraction stars:&gt;500 pushed:&gt;2026-06-11</t>
+          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab/HGNN</t>
+          <t>iMoonLab/Hyper-RAG</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>849</v>
+        <v>319</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>超图神经网络研究，基于PyTorch
-【原文】Hypergraph Neural Networks (AAAI 2019)</t>
+          <t>提供使用超图驱动的检索增强生成来对抗LLM幻觉的Hyper-RAG工具
+【原文】"Hyper-RAG: Combating LLM Hallucinations using Hypergraph-Driven Retrieval-Augmented Generation" by Yifan Feng, Hao Hu, Shihui Ying, Xingliang Hou, Shiquan Liu, Mingyuan Yang, Junchang Li, Shaoyi Du, Nanning Zheng, Han Hu, and Yue Gao.</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6332,7 +6311,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iMoonLab/HGNN</t>
+          <t>https://github.com/iMoonLab/Hyper-RAG</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6341,11 +6320,11 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.3</v>
+        <v>0.61</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
@@ -6365,21 +6344,21 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>complex-data, deep-learning, hypergraph, hypergraph-neural-networks, pytorch</t>
+          <t>graph-rag, hypergraph, llms, rag</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>2018-12-06</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2022-08-31</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="S58" s="3" t="n">
-        <v>2834</v>
+        <v>525</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>1</v>
@@ -6398,19 +6377,19 @@
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>pnnl/HyperNetX</t>
+          <t>heathersherry/Knowledge-Graph-Tutorials-and-Papers</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>711</v>
+        <v>1071</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>超图分析可视化Python包
-【原文】Python package for hypergraph analysis and visualization.</t>
+          <t>提供关于知识图谱的教程和论文
+【原文】Insightful Tutorials and Papers about Knowledge Graphs</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -6420,12 +6399,12 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>数据集</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -6435,7 +6414,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pnnl/HyperNetX</t>
+          <t>https://github.com/heathersherry/Knowledge-Graph-Tutorials-and-Papers</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6444,18 +6423,14 @@
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6468,21 +6443,21 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>hypergraph, hypergraphs, knowledge-graph, property-hypergraphs, python, s-linegraph, simplicial-complexes, simplicial-homology</t>
+          <t>awesome, awesome-kg, awesome-list, data-integration, entity-linking, information-extration, kg, kgqa, knowledge-base, knowledge-graph, knowledge-graph-completion, knowledge-graph-construction</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>2018-10-22</t>
+          <t>2019-03-10</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="S59" s="3" t="n">
-        <v>2879</v>
+        <v>2741</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>1</v>
@@ -6494,26 +6469,26 @@
       </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
         </is>
       </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>easy-graph/Easy-Graph</t>
+          <t>CYBIRD-D/FREE-LLM-API-Provider</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>479</v>
+        <v>101</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>提供高级网络分析方法，包括结构洞检测和网络嵌入等
-【原文】EasyGraph is an open-source network analysis library designed to cover advanced network processing methods. It includes functionalities for detecting structural hole spanners, network embedding, and various classic network analysis techniques.</t>
+          <t>提供免费LLM API资源列表，包括cn平台
+【原文】This is a list of free LLM provider resources accessible via API. Including some cn platform  免费llm api平台（包括cn平台）</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -6523,12 +6498,12 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -6538,7 +6513,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/easy-graph/Easy-Graph</t>
+          <t>https://github.com/CYBIRD-D/FREE-LLM-API-Provider</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6547,18 +6522,14 @@
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>BSD-3-Clause</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr">
-        <is>
-          <t>Python</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr"/>
       <c r="N60" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6571,67 +6542,67 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>hypergraph, multiprocessing-optimization, network-analysis, python, structural-hole-theory</t>
+          <t>api, free, freetier, gemini-api, groq, llm, llm-interface, nvidia, ollama, openrouter</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>2020-06-21</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="S60" s="3" t="n">
-        <v>2271</v>
+        <v>311</v>
       </c>
       <c r="T60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-12</t>
         </is>
       </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>kahypar/kahypar</t>
+          <t>jw9730/tokengt</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>534</v>
+        <v>351</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>多级超图划分框架，提供高质量解决方案
-【原文】KaHyPar (Karlsruhe Hypergraph Partitioning) is a multilevel hypergraph partitioning framework providing direct k-way and recursive bisection based partitioning algorithms that compute solutions of very high quality.</t>
+          <t>提供基于PyTorch的Tokenized Graph Transformer模型
+【原文】[NeurIPS'22] Tokenized Graph Transformer (TokenGT), in PyTorch</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
-        </is>
-      </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>代码库</t>
+        </is>
+      </c>
+      <c r="G61" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -6641,7 +6612,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kahypar/kahypar</t>
+          <t>https://github.com/jw9730/tokengt</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6650,16 +6621,16 @@
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.15</v>
+        <v>0.23</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -6674,21 +6645,21 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>algorithm-engineering, cpp, evolutionary-algorithms, graph, graph-algorithms, graph-partitioning, graphs, hypergraph, hypergraph-partitioning, hypergraphs, papers-with-code, partitioning</t>
+          <t>equivariance, gnn, graph, hypergraph, pytorch, self-attention, transformer</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>2016-09-23</t>
+          <t>2022-06-29</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2023-04-11</t>
         </is>
       </c>
       <c r="S61" s="3" t="n">
-        <v>3638</v>
+        <v>1534</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1</v>
@@ -6707,19 +6678,19 @@
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>yamafaktory/hypergraph</t>
+          <t>gzcsudo/Awesome-Hypergraph-Network</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>创建有向超图的数据结构库
-【原文】Hypergraph is a data structure library to create a directed hypergraph in which a hyperedge can join any number of vertices.</t>
+          <t>提供超图学习、超图理论、超图数据集和超图工具的精选列表
+【原文】A curated list of Hypergraph Learning, Hypergraph Theory, Hypergraph Dataset and Hypergraph Tool.</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6729,12 +6700,12 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -6744,7 +6715,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/yamafaktory/hypergraph</t>
+          <t>https://github.com/gzcsudo/Awesome-Hypergraph-Network</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6753,18 +6724,14 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr">
-        <is>
-          <t>Rust</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr"/>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6777,21 +6744,21 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>data, data-science, data-structure, data-structures, hypergraph, hypergraphs, rust, rust-lang, rustlang</t>
+          <t>awesome-list, graph, graph-neural-network, higher-order-graph, hypergraph, hypergraph-neural-network, hypergraph-theory</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>2020-10-07</t>
+          <t>2022-01-12</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2025-02-03</t>
         </is>
       </c>
       <c r="S62" s="3" t="n">
-        <v>2163</v>
+        <v>1702</v>
       </c>
       <c r="T62" s="3" t="n">
         <v>1</v>

--- a/reports/arsenal/军火榜_最新.xlsx
+++ b/reports/arsenal/军火榜_最新.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>GitHub 军火榜 · 2026-09-10 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
+          <t>GitHub 军火榜 · 2026-09-13 · 共 60 个候选 · 按周涨星降序(总星数偏袒老仓,周涨星才看得出现在热不热)· 分类看「落哪条产线」列,点表头筛选器过滤 · 黄底=军火库还没有的新发现 · 红底=传染许可(只能读架构不能抄代码)</t>
         </is>
       </c>
     </row>
@@ -633,19 +633,19 @@
     <row r="3" ht="150" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>shanraisshan/claude-code-best-practice</t>
+          <t>Egonex-AI/Understand-Anything</t>
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>65804</v>
+        <v>82338</v>
       </c>
       <c r="C3" s="5" t="n">
-        <v>1467</v>
+        <v>3166.9</v>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Claude 代码最佳实践，从 vibe coding 到 agentic engineering
-【原文】from vibe coding to agentic engineering - practice makes claude perfect</t>
+          <t>将代码转换为可交互的知识图谱，支持多种代码和工具的集成。
+【原文】Graphs that teach &gt; graphs that impress. Turn any code into an interactive knowledge graph you can explore, search, and ask questions about. Works with Claude Code, Codex, Cursor, Copilot, Gemini CLI, and more.</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -655,7 +655,7 @@
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -670,7 +670,7 @@
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/shanraisshan/claude-code-best-practice</t>
+          <t>https://github.com/Egonex-AI/Understand-Anything</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="K3" s="5" t="n">
-        <v>209.57</v>
+        <v>452.41</v>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
@@ -688,7 +688,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -703,21 +703,21 @@
       </c>
       <c r="P3" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agentic-coding, agentic-engineering, agentic-workflow, ai, ai-agents, anthropic, best-practices, boris, claude, claude-ai, claude-code</t>
+          <t>antigravity-skills, business-knowledge, claude-code, claude-skills, codebase-analysis, codex, codex-skills, developer-tools-ai-agent, gemini-cli-skills, karpathy-llm-wiki, knowledge-base, knowledge-graph</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2026-03-15</t>
         </is>
       </c>
       <c r="R3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S3" s="3" t="n">
-        <v>314</v>
+        <v>182</v>
       </c>
       <c r="T3" s="3" t="n">
         <v>1</v>
@@ -729,36 +729,36 @@
       </c>
       <c r="V3" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="4" ht="150" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>deeplethe/utopia</t>
+          <t>XiaoDuoYa/codex-with-chatgpt</t>
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>6435</v>
+        <v>4134</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>1324.8</v>
+        <v>1808.7</v>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>构建企业级世界模型
-【原文】World's first open-source enterprise world model.</t>
+          <t>结合ChatGPT和Codex的MCP服务，用于文本处理和代码生成
+【原文】ChatGPT thinks. Codex works. Use ChatGPT as the planning brain while keeping the Codex harness.</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>MCP服务/技能包</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/deeplethe/utopia</t>
+          <t>https://github.com/XiaoDuoYa/codex-with-chatgpt</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -782,16 +782,16 @@
         </is>
       </c>
       <c r="K4" s="5" t="n">
-        <v>189.26</v>
+        <v>258.38</v>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -806,52 +806,53 @@
       </c>
       <c r="P4" s="6" t="inlineStr">
         <is>
-          <t>agent-memory, bitemporal, graphrag, knowledge-base, knowledge-graph, llm, ontology, pgvector, postgresql, rag, rust, self-hosted</t>
+          <t>ai-agents, chatgpt, codex, mcp, model-context-protocol, oauth</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S4" s="3" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="5" ht="150" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>browser-use/video-use</t>
+          <t>eternityspring/reelbench-skills</t>
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>24542</v>
+        <v>371</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>1137.7</v>
+        <v>1298.5</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>使用编码代理编辑视频
-【原文】Edit videos with coding agents</t>
+          <t>提供 AI 视频学习笔记和工具
+【原文】Learning notes and tooling skills for AI video - AI 视频相关的学习与工具 skill
+【依据】topics: ai-video, claude-code, claude-skills, ffmpeg, shot-analysis, video-analysis</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -861,7 +862,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -876,7 +877,7 @@
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/browser-use/video-use</t>
+          <t>https://github.com/eternityspring/reelbench-skills</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -885,16 +886,16 @@
         </is>
       </c>
       <c r="K5" s="5" t="n">
-        <v>162.53</v>
+        <v>185.5</v>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
@@ -907,19 +908,23 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P5" s="6" t="inlineStr"/>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>ai-video, claude-code, claude-skills, ffmpeg, shot-analysis, video-analysis</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S5" s="3" t="n">
-        <v>151</v>
+        <v>2</v>
       </c>
       <c r="T5" s="3" t="n">
         <v>1</v>
@@ -931,41 +936,40 @@
       </c>
       <c r="V5" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="6" ht="150" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>LaoFeng-mouse/flyingmouse-format</t>
+          <t>mizzlelover/gongwen-gbt9704-skill</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>5674</v>
+        <v>548</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1134.8</v>
+        <v>959</v>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>提供 Windows 文件格式转换工具，支持 OCR 和批量转换
-【原文】飞鼠格式 FlyingMouse Format - Windows 免费文件格式转换工具（离线可用，内置 FFmpeg/LibreOffice/Poppler/Tesseract）。图片/文档/表格/PPT/PDF/音视频/WPS 格式互转 + OCR + 批量转换；音频仅支持普通格式。作者：牢蜂（LaoFeng）｜仅供个人免费使用，禁止商业售卖/转卖/套壳</t>
+          <t>信息安全提醒：请勿上传企业禁止对外公开的文件；可在本地或企业内网部署大模型后使用。中文公文排版 Skill：按 GB/T 9704-2012 生成可编辑 DOCX。配套 CEB：https://github.com/mizzlelover/CEB</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>图文产线/古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H6" s="7" t="inlineStr">
@@ -975,7 +979,7 @@
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/LaoFeng-mouse/flyingmouse-format</t>
+          <t>https://github.com/mizzlelover/gongwen-gbt9704-skill</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -984,11 +988,11 @@
         </is>
       </c>
       <c r="K6" s="5" t="n">
-        <v>162.11</v>
+        <v>137</v>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
@@ -1003,26 +1007,26 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P6" s="6" t="inlineStr">
         <is>
-          <t>desktop-app, electron, ffmpeg, file-converter, format-converter, libreoffice, ocr, pdf, windows, wps</t>
+          <t>ai-skill, ceb, chinese-official-document, claude-code, cross-platform, document-formatting, docx, gbt-9704-2012, kimi, opencode, trae-code, traework</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S6" s="3" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="T6" s="3" t="n">
         <v>1</v>
@@ -1034,41 +1038,40 @@
       </c>
       <c r="V6" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="7" ht="150" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>webadderallorg/Recordly</t>
+          <t>jtydhr88/screenwriting-skills</t>
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>26521</v>
+        <v>915</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>1020</v>
+        <v>915</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>创建无需编辑技能的演示视频
-【原文】Create polished demo videos without editing skills. Mac/Windows/Linux</t>
+          <t>(无描述)</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H7" s="7" t="inlineStr">
@@ -1078,7 +1081,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/webadderallorg/Recordly</t>
+          <t>https://github.com/jtydhr88/screenwriting-skills</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -1087,16 +1090,16 @@
         </is>
       </c>
       <c r="K7" s="5" t="n">
-        <v>145.72</v>
+        <v>130.71</v>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
@@ -1106,26 +1109,22 @@
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>electron, free, linux, macos, open-source, screen-recorder, screen-studio, windows</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P7" s="6" t="inlineStr"/>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S7" s="3" t="n">
-        <v>182</v>
+        <v>7</v>
       </c>
       <c r="T7" s="3" t="n">
         <v>1</v>
@@ -1137,41 +1136,41 @@
       </c>
       <c r="V7" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="8" ht="150" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>debpalash/VoiceStudio</t>
+          <t>VectifyAI/PageIndex</t>
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>21930</v>
+        <v>35628</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>996.8</v>
+        <v>470.5</v>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>提供语音克隆、配音、视频配音等功能
-【原文】VoiceStudio is the open-source, fully-local ElevenLabs alternative — voice cloning, voice design, video dubbing, dictation, transcription &amp; audiobook creation in 646 languages.</t>
+          <t>提供基于向量的文档索引，用于推理增强生成。
+【原文】📑 PageIndex: Document Index for Vectorless, Reasoning-based RAG</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G8" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H8" s="7" t="inlineStr">
@@ -1181,7 +1180,7 @@
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/debpalash/VoiceStudio</t>
+          <t>https://github.com/VectifyAI/PageIndex</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -1190,11 +1189,11 @@
         </is>
       </c>
       <c r="K8" s="5" t="n">
-        <v>142.4</v>
+        <v>67.22</v>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
@@ -1214,24 +1213,24 @@
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
-          <t>ai, audiobook, cuda, dubbing, elevenlabs-alternative, huggingface, local-first, mlx, omnivoice-studio, speech-to-text, tauri, text-to-speech</t>
+          <t>agentic-ai, agents, ai, ai-agents, context-engineering, information-retrieval, llm, rag, reasoning, retrieval, retrieval-augmented-generation, vector-database</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>2026-04-09</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S8" s="3" t="n">
-        <v>154</v>
+        <v>530</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
@@ -1240,26 +1239,26 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="9" ht="150" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>kajisho5/ffmpeg-skill</t>
+          <t>tradecatlabs/vibe-coding-cn</t>
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>896</v>
+        <v>16183</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>896</v>
+        <v>385.3</v>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>使用ffmpeg进行视频处理的技能
-【依据】ffmpeg-skill</t>
+          <t>提供 AI 编程教程和结对编程工作流
+【原文】Vibe Coding 从入门到精通教程｜AI 结对编程工作流｜Prompt、Skill、Workflow、上下文管理、codex实战指南</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
@@ -1284,7 +1283,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kajisho5/ffmpeg-skill</t>
+          <t>https://github.com/tradecatlabs/vibe-coding-cn</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1293,7 +1292,7 @@
         </is>
       </c>
       <c r="K9" s="5" t="n">
-        <v>128</v>
+        <v>55.04</v>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
@@ -1315,50 +1314,54 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P9" s="6" t="inlineStr"/>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>ai, ai-agent, ai-agents, ai-coding, ai-programming, chinese, claude-code, codex, cursor, developer-tools, gemini-cli, glue-coding</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2025-11-23</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S9" s="3" t="n">
-        <v>7</v>
+        <v>294</v>
       </c>
       <c r="T9" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V9" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-11</t>
+          <t>topic:chinese stars:&gt;500 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="10" ht="150" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>microsoft/ai-agents-for-beginners</t>
+          <t>Fosowl/agenticSeek</t>
         </is>
       </c>
       <c r="B10" s="4" t="n">
-        <v>74307</v>
+        <v>27200</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>799</v>
+        <v>333.5</v>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>提供构建 AI 代理的 Jupyter Notebook 教程和框架
-【原文】18 Lessons to Get Started Building AI Agents</t>
+          <t>提供本地化的 AI 代理，无需 API 和月费。
+【原文】Fully Local Manus AI. No APIs, No $200 monthly bills. Enjoy an autonomous agent that thinks, browses the web, and code for the sole cost of electricity.</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
@@ -1368,12 +1371,12 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H10" s="7" t="inlineStr">
@@ -1383,7 +1386,7 @@
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/microsoft/ai-agents-for-beginners</t>
+          <t>https://github.com/Fosowl/agenticSeek</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1392,16 +1395,16 @@
         </is>
       </c>
       <c r="K10" s="5" t="n">
-        <v>114.14</v>
+        <v>47.64</v>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>Jupyter Notebook</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -1416,21 +1419,21 @@
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agentic-framework, agentic-rag, ai-agents, ai-agents-framework, autogen, foundry, foundry-local, generative-ai, microsoft-foundry, semantic-kernel</t>
+          <t>agentic-ai, agents, ai, autonomous-agents, deepseek-r1, llm, llm-agents, voice-assistant</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>2024-11-28</t>
+          <t>2025-02-19</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S10" s="3" t="n">
-        <v>651</v>
+        <v>571</v>
       </c>
       <c r="T10" s="3" t="n">
         <v>1</v>
@@ -1442,41 +1445,42 @@
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="11" ht="150" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>AUTOMATIC1111/stable-diffusion-webui</t>
+          <t>SenteLabsAI/OpenExecutive</t>
         </is>
       </c>
       <c r="B11" s="4" t="n">
-        <v>164882</v>
+        <v>4137</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>779.9</v>
+        <v>308.1</v>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>Stable Diffusion 的网页用户界面，用于图像生成和文本到图像
-【原文】Stable Diffusion web UI</t>
+          <t>提供 AI 虚拟执行团队
+【原文】AI-powered virtual executive team — a single coherent executive persona backed by 8 specialist agents (FastAPI + Next.js).
+【依据】topics: ai, anthropic, claude, fastapi, llm, multi-agent, nextjs, python, rag, typescript</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>图文产线</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>技能包/架构参考</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr">
@@ -1486,7 +1490,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/AUTOMATIC1111/stable-diffusion-webui</t>
+          <t>https://github.com/SenteLabsAI/OpenExecutive</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1495,11 +1499,11 @@
         </is>
       </c>
       <c r="K11" s="5" t="n">
-        <v>111.41</v>
+        <v>44.01</v>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1519,21 +1523,21 @@
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-art, deep-learning, diffusion, gradio, image-generation, image2image, img2img, pytorch, stable-diffusion, text2image, torch</t>
+          <t>ai, anthropic, claude, fastapi, llm, multi-agent, nextjs, python, rag, typescript</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2022-08-22</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S11" s="3" t="n">
-        <v>1480</v>
+        <v>94</v>
       </c>
       <c r="T11" s="3" t="n">
         <v>1</v>
@@ -1545,26 +1549,26 @@
       </c>
       <c r="V11" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="12" ht="150" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>vectorize-io/hindsight</t>
+          <t>corsairdev/corsair</t>
         </is>
       </c>
       <c r="B12" s="4" t="n">
-        <v>23350</v>
+        <v>11293</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>518.9</v>
+        <v>236.7</v>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>代理记忆服务，用于学习代理记忆
-【原文】Hindsight: Agent Memory That Learns</t>
+          <t>连接用户到他们的应用程序，支持 API 集成和功能调用。
+【原文】Connect your users to their apps</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -1574,12 +1578,12 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H12" s="7" t="inlineStr">
@@ -1589,7 +1593,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/vectorize-io/hindsight</t>
+          <t>https://github.com/corsairdev/corsair</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1598,16 +1602,16 @@
         </is>
       </c>
       <c r="K12" s="5" t="n">
-        <v>74.13</v>
+        <v>33.81</v>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -1622,24 +1626,24 @@
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agents, ai-memory, memory</t>
+          <t>agentic-ai, agents, ai, ai-agents, aiagents, api-integration, corsair, developer-tools, function-calling, integrations, javascript, llm</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-10-14</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S12" s="3" t="n">
-        <v>315</v>
+        <v>334</v>
       </c>
       <c r="T12" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
@@ -1648,26 +1652,25 @@
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="13" ht="150" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>CyC2018/CS-Notes</t>
+          <t>Adkid-Zephyr/anti-defensive-writing-Skill</t>
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>185972</v>
+        <v>932</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>415.8</v>
+        <v>197.7</v>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>提供技术面试必备基础知识、Leetcode 和计算机科学相关资料
-【原文】:books: 技术面试必备基础知识、Leetcode、计算机操作系统、计算机网络、系统设计</t>
+          <t>极致轻量｜阻止论文的防御性写作 | Anti-defensive writing for academic papers — 学术写作原则 Skill + prompt pack (CN/EN)</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
@@ -1677,12 +1680,12 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H13" s="7" t="inlineStr">
@@ -1692,7 +1695,7 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CyC2018/CS-Notes</t>
+          <t>https://github.com/Adkid-Zephyr/anti-defensive-writing-Skill</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1701,11 +1704,11 @@
         </is>
       </c>
       <c r="K13" s="5" t="n">
-        <v>59.4</v>
+        <v>28.24</v>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr"/>
@@ -1716,26 +1719,26 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
-          <t>algorithm, computer-science, cpp, interview, java, leetcode, python, system-design</t>
+          <t>academic-writing, ai-writing, claude-skill, paper-writing, prompt</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t>2018-02-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>2024-08-21</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S13" s="3" t="n">
-        <v>3131</v>
+        <v>33</v>
       </c>
       <c r="T13" s="3" t="n">
         <v>1</v>
@@ -1747,26 +1750,26 @@
       </c>
       <c r="V13" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="14" ht="150" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Mintplex-Labs/anything-llm</t>
+          <t>Ar9av/obsidian-wiki</t>
         </is>
       </c>
       <c r="B14" s="4" t="n">
-        <v>65856</v>
+        <v>3398</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>386.1</v>
+        <v>148.7</v>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>提供本地 AI 代理体验的 JavaScript 库
-【原文】Stop renting your intelligence. Own it with AnythingLLM. Everything you need for a powerful local-first agent experience</t>
+          <t>通过 Obsidian Wiki 构建和维护 AI 代理的数字大脑
+【原文】Framework for AI agents to build and maintain a digital brain through Obsidian wiki</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
@@ -1776,7 +1779,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -1791,7 +1794,7 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Mintplex-Labs/anything-llm</t>
+          <t>https://github.com/Ar9av/obsidian-wiki</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
@@ -1800,7 +1803,7 @@
         </is>
       </c>
       <c r="K14" s="5" t="n">
-        <v>55.16</v>
+        <v>21.24</v>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -1809,7 +1812,7 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -1824,24 +1827,24 @@
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
-          <t>agent-computer, agent-harness, agent-orchestration, agentic-ai, ai-agents, computer-use, hermes-agent, llm, local-ai, localai, multimodal, no-code</t>
+          <t>agent-skills, brain, knowledge-base, knowledge-graph, llm-tools, memory, obsidian, obsidian-brain, wiki</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t>2023-06-04</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S14" s="3" t="n">
-        <v>1194</v>
+        <v>160</v>
       </c>
       <c r="T14" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
@@ -1850,36 +1853,36 @@
       </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="15" ht="150" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>zvec-ai/zvec-grep</t>
+          <t>GetStream/Vision-Agents</t>
         </is>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3324</v>
+        <v>8119</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>375.3</v>
+        <v>142.8</v>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>提供本地优先的搜索工具，适用于人类和AI代理
-【原文】Local-first search across your workspace, built for humans and AI agents.</t>
+          <t>构建语音和视觉代理的快速工具，使用Stream的边缘网络实现超低延迟
+【原文】Open Vision Agents by Stream. Build voice and vision agents quickly with any model or video provider. Uses Stream's edge network for ultra-low latency.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
@@ -1894,7 +1897,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zvec-ai/zvec-grep</t>
+          <t>https://github.com/GetStream/Vision-Agents</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
@@ -1903,7 +1906,7 @@
         </is>
       </c>
       <c r="K15" s="5" t="n">
-        <v>53.61</v>
+        <v>20.4</v>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
@@ -1912,7 +1915,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
@@ -1927,52 +1930,52 @@
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, bm25, cli, code-search, full-text-search, local-first, mcp, ripgrep, semantic-search, vector-search</t>
+          <t>agentic-ai, agents, ai, ai-agents, realtime, stt, tts, video-agents, video-ai, vision-ai, voice-ai</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2025-08-11</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S15" s="3" t="n">
-        <v>62</v>
+        <v>398</v>
       </c>
       <c r="T15" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t>stock</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V15" s="6" t="inlineStr">
         <is>
-          <t>topic:mcp stars:&gt;2000 pushed:&gt;2026-08-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="16" ht="150" customHeight="1">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Tencent/WeKnora</t>
+          <t>MrLesk/Backlog.md</t>
         </is>
       </c>
       <c r="B16" s="4" t="n">
-        <v>21969</v>
+        <v>6717</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>370.6</v>
+        <v>100.9</v>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>开源的LLM知识平台，将原始文档转换为可查询的RAG、自主推理代理和自维护Wiki
-【原文】Open-source LLM knowledge platform: turn raw documents into a queryable RAG, an autonomous reasoning agent, and a self-maintaining Wiki.</t>
+          <t>用于在 git 生态系统中管理项目协作和任务管理的工具。
+【原文】Backlog.md - A tool for managing project collaboration between humans and AI Agents in a git ecosystem</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -1987,7 +1990,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H16" s="7" t="inlineStr">
@@ -1997,7 +2000,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Tencent/WeKnora</t>
+          <t>https://github.com/MrLesk/Backlog.md</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
@@ -2006,16 +2009,16 @@
         </is>
       </c>
       <c r="K16" s="5" t="n">
-        <v>52.94</v>
+        <v>14.41</v>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
@@ -2030,21 +2033,21 @@
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic, ai, chatbot, dsh-plugin, embeddings, evaluation, generative-ai, golang, knowledge-base, llm, multi-tenant</t>
+          <t>agent, agentic-ai, management, markdown, project, task-manager, tasks</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t>2025-07-22</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S16" s="3" t="n">
-        <v>415</v>
+        <v>466</v>
       </c>
       <c r="T16" s="3" t="n">
         <v>1</v>
@@ -2056,36 +2059,37 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="17" ht="150" customHeight="1">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>simstudioai/sim</t>
+          <t>arc53/DocsGPT</t>
         </is>
       </c>
       <c r="B17" s="4" t="n">
-        <v>29590</v>
+        <v>18260</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>337.9</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>构建、部署和监控AI代理和流程的工作空间
-【原文】Sim is the collaborative workspace to build, deploy, and monitor AI agents and workflows. Used by 100,000+ builders.</t>
+          <t>提供 AI 代理和搜索平台
+【原文】Private AI platform for agents, assistants and enterprise search. Built-in Agent Builder, Deep research, Document analysis, Multi-model support, and API connectivity for agents.
+【依据】topics: agent-builder, agents, ai, chatgpt, docsgpt, hacktoberfest, hacktoberfest2026, information-retrieval, language-m</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包/架构参考</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
@@ -2100,7 +2104,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/simstudioai/sim</t>
+          <t>https://github.com/arc53/DocsGPT</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
@@ -2109,16 +2113,16 @@
         </is>
       </c>
       <c r="K17" s="5" t="n">
-        <v>48.27</v>
+        <v>13.84</v>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
@@ -2133,21 +2137,21 @@
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
-          <t>agent-workflow, agentic-workflow, agents, ai, aiagents, anthropic, artificial-intelligence, automation, chatbot, deepseek, gemini, low-code</t>
+          <t>agent-builder, agents, ai, chatgpt, docsgpt, hacktoberfest, hacktoberfest2026, information-retrieval, language-model, llm, machine-learning, natural-language-processing</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2025-01-05</t>
+          <t>2023-02-02</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S17" s="3" t="n">
-        <v>613</v>
+        <v>1319</v>
       </c>
       <c r="T17" s="3" t="n">
         <v>1</v>
@@ -2159,31 +2163,31 @@
       </c>
       <c r="V17" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="18" ht="150" customHeight="1">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>redhat-et/ripwire</t>
+          <t>charmbracelet/vhs</t>
         </is>
       </c>
       <c r="B18" s="4" t="n">
-        <v>1841</v>
+        <v>20880</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>299.7</v>
+        <v>96.3</v>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>AI代理的ripgrep工具，提供代码导航和MCP服务器
-【原文】The ripgrep of AI context: a zero-dependency C++23 CLI + MCP server for coding agents. Find what you want without reading the repo, then check you built what you meant — blast radius, tests-to-run, quality deltas. Signatures at 74.7% fewer bytes than bodies; every guess labelled, every loss published. Paddle out with a map.</t>
+          <t>命令行视频录制工具，支持GIF和终端录制
+【原文】Your CLI home video recorder 📼</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
@@ -2203,7 +2207,7 @@
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/redhat-et/ripwire</t>
+          <t>https://github.com/charmbracelet/vhs</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
@@ -2212,16 +2216,16 @@
         </is>
       </c>
       <c r="K18" s="5" t="n">
-        <v>42.81</v>
+        <v>13.76</v>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
@@ -2236,21 +2240,21 @@
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, call-graph, claude, claude-code, cli, code-navigation, codex, coding-agents, context-engineering, cpp, developer-tools, llm</t>
+          <t>ascii, cli, command-line, gif, recording, terminal, vhs, video</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2022-07-19</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S18" s="3" t="n">
-        <v>43</v>
+        <v>1517</v>
       </c>
       <c r="T18" s="3" t="n">
         <v>1</v>
@@ -2262,36 +2266,36 @@
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="19" ht="150" customHeight="1">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>feder-cr/AIHawk</t>
+          <t>iFurySt/open-codex-computer-use</t>
         </is>
       </c>
       <c r="B19" s="4" t="n">
-        <v>30334</v>
+        <v>2043</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>276.8</v>
+        <v>96</v>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>开源 AI 浏览器代理，用于网页自动化和计算机使用
-【原文】Open-source AI browser agent for web automation: a web browsing agent and computer-use agent in plain English. Browser MCP for Claude Code and Gemini CLI.</t>
+          <t>提供 Codex 计算机使用的开源替代方案
+【原文】👾 Open Computer Use – Open-Source Alternative to Codex Computer Use</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2306,7 +2310,7 @@
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/feder-cr/AIHawk</t>
+          <t>https://github.com/iFurySt/open-codex-computer-use</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
@@ -2315,7 +2319,7 @@
         </is>
       </c>
       <c r="K19" s="5" t="n">
-        <v>39.55</v>
+        <v>13.71</v>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
@@ -2324,7 +2328,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Swift</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -2339,52 +2343,53 @@
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, ai-agent, ai-automation, autonomous-agent, autonomous-agents, browser, browser-agent, computer-use, job-hunting, job-search, lead-generation, llm-agent</t>
+          <t>accessibility, ai-agent, ai-agents, claude-code, codex, codex-computer-use, computer-use, computer-use-agent, cross-platform, cua, desktop-automation, gemini-cli</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t>2024-08-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="S19" s="3" t="n">
-        <v>767</v>
+        <v>149</v>
       </c>
       <c r="T19" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V19" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="20" ht="150" customHeight="1">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>getify/You-Dont-Know-JS</t>
+          <t>yaklang/hack-skills</t>
         </is>
       </c>
       <c r="B20" s="4" t="n">
-        <v>184849</v>
+        <v>2182</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>276.4</v>
+        <v>96</v>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>JavaScript 语言书籍系列，包括异步、闭包、原型等主题
-【原文】A book series (2 published editions) on the JS language.</t>
+          <t>帮助 AI 代理成为黑客
+【原文】Helping AI Agent become an awesome practical hacker!
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
@@ -2394,12 +2399,12 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H20" s="7" t="inlineStr">
@@ -2409,7 +2414,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/getify/You-Dont-Know-JS</t>
+          <t>https://github.com/yaklang/hack-skills</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
@@ -2418,14 +2423,18 @@
         </is>
       </c>
       <c r="K20" s="5" t="n">
-        <v>39.49</v>
+        <v>13.72</v>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
-        </is>
-      </c>
-      <c r="M20" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>CSS</t>
+        </is>
+      </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2436,26 +2445,22 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>async, book, book-series, closures, education, es2015, es6, javascript, learn-to-code, programming, prototypes, training-materials</t>
-        </is>
-      </c>
+      <c r="P20" s="6" t="inlineStr"/>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>2013-11-16</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S20" s="3" t="n">
-        <v>4681</v>
+        <v>159</v>
       </c>
       <c r="T20" s="3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
@@ -2464,26 +2469,26 @@
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="21" ht="150" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>jlevy/the-art-of-command-line</t>
+          <t>RLinf/RLinf</t>
         </is>
       </c>
       <c r="B21" s="4" t="n">
-        <v>162328</v>
+        <v>5180</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>275.1</v>
+        <v>91.8</v>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>提供命令行操作的指南和技巧
-【原文】Master the command line, in one page</t>
+          <t>提供强化学习基础设施，用于具身和代理式 AI。
+【原文】RLinf: Reinforcement Learning Infrastructure for Embodied and Agentic AI</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
@@ -2493,12 +2498,12 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H21" s="7" t="inlineStr">
@@ -2508,7 +2513,7 @@
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jlevy/the-art-of-command-line</t>
+          <t>https://github.com/RLinf/RLinf</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
@@ -2517,14 +2522,18 @@
         </is>
       </c>
       <c r="K21" s="5" t="n">
-        <v>39.3</v>
+        <v>13.11</v>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M21" s="3" t="inlineStr"/>
+          <t>Apache-2.0</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -2537,21 +2546,21 @@
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
-          <t>bash, documentation, linux, macos, unix, windows</t>
+          <t>agentic-ai, embodied-ai, reinforcement-learning, rl-infra, rlinf, vla-rl</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t>2015-05-20</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S21" s="3" t="n">
-        <v>4131</v>
+        <v>395</v>
       </c>
       <c r="T21" s="3" t="n">
         <v>1</v>
@@ -2563,26 +2572,27 @@
       </c>
       <c r="V21" s="6" t="inlineStr">
         <is>
-          <t>stars:&gt;150000</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="22" ht="150" customHeight="1">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>run-llama/llama_index</t>
+          <t>langbot-app/LangBot</t>
         </is>
       </c>
       <c r="B22" s="4" t="n">
-        <v>52106</v>
+        <v>17756</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>259.1</v>
+        <v>90.3</v>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>文档代理和OCR平台
-【原文】LlamaIndex is the leading document agent and OCR platform</t>
+          <t>提供生产级智能机器人开发平台
+【原文】Production-grade platform for building agentic IM bots - 生产级多平台智能机器人开发平台/ Agent、知识库编排、插件系统 / Bots for Discord / Slack / LINE / Telegram / WeChat(企业微信, 企微智能机器人, 公众号) / 飞书 / 钉钉 / QQ / Matrix e.g. Integrated with ChatGPT(GPT), DeepSeek, Dify, n8n, Langflow, Coze, Claude, Gemini, GLM, Ollama, SiliconFlow, Moonshot, openclaw / hermes agent, deerflow
+【依据】topics: agent, coze, deepseek, dify, dingtalk, discord, feishu, kook, langbot, lark, line, llm</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
@@ -2592,7 +2602,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2607,7 +2617,7 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/run-llama/llama_index</t>
+          <t>https://github.com/langbot-app/LangBot</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
@@ -2616,11 +2626,11 @@
         </is>
       </c>
       <c r="K22" s="5" t="n">
-        <v>37.01</v>
+        <v>12.9</v>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -2640,21 +2650,21 @@
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
-          <t>agents, application, data, fine-tuning, framework, llamaindex, llm, multi-agents, rag, vector-database</t>
+          <t>agent, coze, deepseek, dify, dingtalk, discord, feishu, kook, langbot, lark, line, llm</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
+          <t>2022-12-07</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S22" s="3" t="n">
-        <v>1408</v>
+        <v>1376</v>
       </c>
       <c r="T22" s="3" t="n">
         <v>1</v>
@@ -2666,26 +2676,26 @@
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="23" ht="150" customHeight="1">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>ValueCell-ai/ClawX</t>
+          <t>Evil0ctal/Douyin_TikTok_Download_API</t>
         </is>
       </c>
       <c r="B23" s="4" t="n">
-        <v>7617</v>
+        <v>20081</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>245.7</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>提供桌面应用程序，用于管理 OpenClaw AI 代理
-【原文】ClawX is a desktop app that provides a graphical interface for OpenClaw AI agents. It turns CLI-based AI orchestration into a desktop experience without using the terminal. China website is https://clawx.com.cn.</t>
+          <t>抖音和TikTok爬虫和视频下载API，支持MCP服务器和CLI
+【原文】🚀 Self-hosted TikTok &amp; Douyin scraper and no-watermark video downloader — async REST API, MCP server, CLI and web console for posts, profiles, comments and playlists. Self-healing identity pool, PostgreSQL archive, one docker compose up. 抖音、TikTok 数据采集与无水印视频下载 API，自托管，支持 MCP 调用与 Docker 一键部署。</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
@@ -2695,7 +2705,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/技能包/架构参考</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2710,7 +2720,7 @@
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ValueCell-ai/ClawX</t>
+          <t>https://github.com/Evil0ctal/Douyin_TikTok_Download_API</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
@@ -2719,16 +2729,16 @@
         </is>
       </c>
       <c r="K23" s="5" t="n">
-        <v>35.1</v>
+        <v>11.34</v>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
@@ -2743,24 +2753,24 @@
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
-          <t>agent, agentic-ai, agents, ai, clawdbot, moltbot, openclaw, skill</t>
+          <t>asyncio, crawler, data-collection, douyin, douyin-api, downloader, fastapi, mcp-server, model-context-protocol, openapi, rest-api, scraper</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2021-11-07</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S23" s="3" t="n">
-        <v>217</v>
+        <v>1771</v>
       </c>
       <c r="T23" s="3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
@@ -2769,36 +2779,36 @@
       </c>
       <c r="V23" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="24" ht="150" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Gentleman-Programming/gentle-ai</t>
+          <t>oomol-lab/pdf-craft</t>
         </is>
       </c>
       <c r="B24" s="4" t="n">
-        <v>6571</v>
+        <v>6293</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>235.9</v>
+        <v>76.2</v>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>配置和集成多种AI编码代理
-【原文】Gentle-AI configures the AI coding agents you already use: Claude Code, Cursor, OpenCode, Codex, Pi, and more. Choose persistent memory, Spec-Driven Development, curated skills, MCP servers, personas, and optional bounded review. Open source, no agent lock-in.</t>
+          <t>将PDF文件转换为其他格式，专注于处理扫描书籍的PDF文件
+【原文】PDF craft can convert PDF files into various other formats. This project will focus on processing PDF files of scanned books.</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2813,7 +2823,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Gentleman-Programming/gentle-ai</t>
+          <t>https://github.com/oomol-lab/pdf-craft</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
@@ -2822,7 +2832,7 @@
         </is>
       </c>
       <c r="K24" s="5" t="n">
-        <v>33.7</v>
+        <v>10.89</v>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -2831,7 +2841,7 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
@@ -2846,24 +2856,24 @@
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
-          <t>agent-skills, ai-agents, ai-coding, claude-code, code-review, codex, coding-agents, copilot, cursor, developer-tools, golang, llm</t>
+          <t>deepseek-ocr, document, ocr, pdf</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2025-02-12</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S24" s="3" t="n">
-        <v>195</v>
+        <v>578</v>
       </c>
       <c r="T24" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
@@ -2872,37 +2882,36 @@
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="25" ht="150" customHeight="1">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Osmantic/ODS</t>
+          <t>keploy/keploy</t>
         </is>
       </c>
       <c r="B25" s="4" t="n">
-        <v>6347</v>
+        <v>18451</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>208.6</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>将个人电脑转变为AI服务器，提供LLM推理和聊天UI
-【原文】Turn your PC, Mac, or Linux box into an AI server.  LLM inference, chat UI, voice, agents, workflows, RAG, and image generation.
-【依据】Turn your PC, Mac, or Linux box into an AI server. LLM inference, chat UI, voice, agents, workflows, RAG, and image gene</t>
+          <t>开源平台，用于创建安全的 API、集成和端到端测试沙盒。
+【原文】Open-source platform for creating safe, isolated production sandboxes for API, integration, and E2E testing.</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>AI免费池/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2917,7 +2926,7 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Osmantic/ODS</t>
+          <t>https://github.com/keploy/keploy</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
@@ -2926,7 +2935,7 @@
         </is>
       </c>
       <c r="K25" s="5" t="n">
-        <v>29.8</v>
+        <v>10.87</v>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
@@ -2935,7 +2944,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -2950,21 +2959,21 @@
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
-          <t>ai-agents, amd, comfyui, docker, llama-cpp, llm, local-ai, n8n, nvidia, open-webui, rag, self-hosted</t>
+          <t>agentic-ai, ai-testing-tool, api-testing, code-quality, mock, mock-data-generator, mock-framework, test-automation, test-automation-framework, test-generation, testing, testing-library</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2022-01-19</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S25" s="3" t="n">
-        <v>213</v>
+        <v>1698</v>
       </c>
       <c r="T25" s="3" t="n">
         <v>1</v>
@@ -2976,31 +2985,31 @@
       </c>
       <c r="V25" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="26" ht="150" customHeight="1">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>semantica-agi/semantica</t>
+          <t>HIllya51/LunaTranslator</t>
         </is>
       </c>
       <c r="B26" s="4" t="n">
-        <v>12538</v>
+        <v>13151</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>198.6</v>
+        <v>63.6</v>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>提供图原生基础设施以构建可解释的AI系统
-【原文】Graph-Native Infrastructure for Context and Accountable AI Systems</t>
+          <t>视觉小说翻译器，支持OCR和反向工程
+【原文】视觉小说翻译器 / Visual Novel Translator</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
@@ -3008,9 +3017,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H26" s="7" t="inlineStr">
@@ -3020,7 +3029,7 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/semantica-agi/semantica</t>
+          <t>https://github.com/HIllya51/LunaTranslator</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
@@ -3029,16 +3038,16 @@
         </is>
       </c>
       <c r="K26" s="5" t="n">
-        <v>28.37</v>
+        <v>9.09</v>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C++</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
@@ -3053,21 +3062,21 @@
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
-          <t>agent-memory, ai, ai-governance, ai-infrastructure, artificial-intelligence, context-engineering, context-graphs, data-engineering, decision-intelligence, developer-tools, explainable-ai, generative-ai</t>
+          <t>galgame, ocr, reverse-engineering, translator, visual-novel, win32</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
+          <t>2022-09-28</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S26" s="3" t="n">
-        <v>442</v>
+        <v>1446</v>
       </c>
       <c r="T26" s="3" t="n">
         <v>1</v>
@@ -3079,36 +3088,37 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="27" ht="150" customHeight="1">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>OpenBMB/MiniCPM-V</t>
+          <t>HelixDB/helix-db</t>
         </is>
       </c>
       <c r="B27" s="4" t="n">
-        <v>26333</v>
+        <v>5900</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>193</v>
+        <v>62.6</v>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>在手机上实现高效的图像和视频理解
-【原文】A Pocket-Sized MLLM for Ultra-Efficient Image and Video Understanding on Your Phone</t>
+          <t>提供 OLTP 图数据库
+【原文】HelixDB is an OLTP graph database with native vector and full-text search built in Rust on Object Storage.
+【依据】topics: ai, cli, database, databases, graph-database, helix, helixdb, rag, rust, rust-crate, rust-lang, vector</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>未定</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3123,7 +3133,7 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/OpenBMB/MiniCPM-V</t>
+          <t>https://github.com/HelixDB/helix-db</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
@@ -3132,7 +3142,7 @@
         </is>
       </c>
       <c r="K27" s="5" t="n">
-        <v>27.57</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
@@ -3141,7 +3151,7 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
@@ -3156,21 +3166,21 @@
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
-          <t>minicpm, minicpm-o, minicpm-v, multi-modal</t>
+          <t>ai, cli, database, databases, graph-database, helix, helixdb, rag, rust, rust-crate, rust-lang, vector</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t>2024-01-29</t>
+          <t>2024-11-23</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S27" s="3" t="n">
-        <v>955</v>
+        <v>659</v>
       </c>
       <c r="T27" s="3" t="n">
         <v>1</v>
@@ -3182,37 +3192,36 @@
       </c>
       <c r="V27" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="28" ht="150" customHeight="1">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>GLips/Figma-Context-MCP</t>
+          <t>bluenviron/mediamtx</t>
         </is>
       </c>
       <c r="B28" s="4" t="n">
-        <v>15817</v>
+        <v>20111</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>192.9</v>
+        <v>57.5</v>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>为Figma布局信息提供MCP服务器
-【原文】MCP server to provide Figma layout information to AI coding agents like Cursor
-【依据】MCP server to provide Figma layout information to AI coding agents like Cursor.</t>
+          <t>支持多种媒体协议的实时媒体服务器和代理
+【原文】Ready-to-use Media-over-QUIC / SRT / WebRTC / RTSP / RTMP / LL-HLS / MPEG-TS / RTP live media server and media proxy that allows to read, publish, proxy, record and playback real-time video and audio streams.</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3227,7 +3236,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/GLips/Figma-Context-MCP</t>
+          <t>https://github.com/bluenviron/mediamtx</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3236,7 +3245,7 @@
         </is>
       </c>
       <c r="K28" s="5" t="n">
-        <v>27.56</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
@@ -3245,7 +3254,7 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
@@ -3260,24 +3269,24 @@
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
-          <t>ai, cursor, figma, mcp, typescript</t>
+          <t>go, golang, hls, media-over-quic, media-server, moq, obs-studio, rtcp, rtmp, rtmp-proxy, rtmp-server, rtp</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t>2025-02-13</t>
+          <t>2019-12-28</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S28" s="3" t="n">
-        <v>574</v>
+        <v>2451</v>
       </c>
       <c r="T28" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
@@ -3286,41 +3295,41 @@
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="29" ht="150" customHeight="1">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>paperless-ngx/paperless-ngx</t>
+          <t>MemMachine/MemMachine</t>
         </is>
       </c>
       <c r="B29" s="4" t="n">
-        <v>44970</v>
+        <v>3219</v>
       </c>
       <c r="C29" s="5" t="n">
-        <v>188.4</v>
+        <v>57.2</v>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>提供文档管理系统，支持扫描、索引和存档文档
-【原文】A community-supported supercharged document management system: scan, index and archive all your documents</t>
+          <t>为 AI 代理提供通用内存层，用于状态管理和自主系统。
+【原文】Universal memory layer for AI Agents. It provides scalable, extensible, and interoperable memory storage and retrieval to streamline AI agent state management for next-generation autonomous systems.</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G29" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H29" s="7" t="inlineStr">
@@ -3330,7 +3339,7 @@
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/paperless-ngx/paperless-ngx</t>
+          <t>https://github.com/MemMachine/MemMachine</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
@@ -3339,11 +3348,11 @@
         </is>
       </c>
       <c r="K29" s="5" t="n">
-        <v>26.91</v>
+        <v>8.17</v>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -3363,21 +3372,21 @@
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
-          <t>ai, angular, archiving, django, dms, document-management, document-management-system, llm, machine-learning, ocr, optical-character-recognition, pdf</t>
+          <t>agent, agentic-ai, agents, agents-sdk, ai, ai-agents, chatbots, conversational-agents, conversational-ai, genai, knowledge-graph, llm</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t>2022-02-12</t>
+          <t>2025-08-15</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S29" s="3" t="n">
-        <v>1671</v>
+        <v>394</v>
       </c>
       <c r="T29" s="3" t="n">
         <v>1</v>
@@ -3389,42 +3398,41 @@
       </c>
       <c r="V29" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="30" ht="150" customHeight="1">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>onyx-dot-app/onyx</t>
+          <t>Zleap-AI/SAG</t>
         </is>
       </c>
       <c r="B30" s="4" t="n">
-        <v>32006</v>
+        <v>2482</v>
       </c>
       <c r="C30" s="5" t="n">
-        <v>181.9</v>
+        <v>56.1</v>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>提供具有高级功能的AI聊天平台
-【原文】Open Source AI Platform - AI Chat with advanced features that works with every LLM
-【依据】Open Source AI Platform - AI Chat with advanced features that works with every LLM.</t>
+          <t>提供 RAG 检索架构和开源知识库
+【原文】A new SOTA for RAG — an original retrieval architecture and an open-source knowledge base for humans and agents.</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线/未归类</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>技能包/可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H30" s="7" t="inlineStr">
@@ -3434,7 +3442,7 @@
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/onyx-dot-app/onyx</t>
+          <t>https://github.com/Zleap-AI/SAG</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
@@ -3443,11 +3451,11 @@
         </is>
       </c>
       <c r="K30" s="5" t="n">
-        <v>25.98</v>
+        <v>8.01</v>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -3467,21 +3475,21 @@
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-chat, chatgpt, chatui, enterprise-search, gen-ai, information-retrieval, llm, llm-ui, nextjs, python, rag</t>
+          <t>agent, ai, data-engineering, graphrag, knowledge-base, knowledge-graph, knowledge-graphs, llm, rag, sag, vector-search</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>2023-04-27</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S30" s="3" t="n">
-        <v>1232</v>
+        <v>310</v>
       </c>
       <c r="T30" s="3" t="n">
         <v>1</v>
@@ -3493,26 +3501,27 @@
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="31" ht="150" customHeight="1">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>elizaOS/eliza</t>
+          <t>rothgar/awesome-tuis</t>
         </is>
       </c>
       <c r="B31" s="4" t="n">
-        <v>19312</v>
+        <v>20575</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>170.5</v>
+        <v>52.9</v>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>开源的自主操作系统框架
-【原文】Open source agentic operating system</t>
+          <t>提供终端用户界面项目列表
+【原文】List of projects that provide terminal user interfaces
+【依据】topics: -</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
@@ -3527,7 +3536,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H31" s="7" t="inlineStr">
@@ -3537,7 +3546,7 @@
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/elizaOS/eliza</t>
+          <t>https://github.com/rothgar/awesome-tuis</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
@@ -3546,18 +3555,14 @@
         </is>
       </c>
       <c r="K31" s="5" t="n">
-        <v>24.35</v>
+        <v>7.56</v>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t>TypeScript</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr"/>
       <c r="N31" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -3568,23 +3573,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>agent, agentic, ai, autonomous, chatbot, crypto, discord, eliza, elizaos, framework, plugins, rag</t>
-        </is>
-      </c>
+      <c r="P31" s="6" t="inlineStr"/>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t>2024-07-09</t>
+          <t>2019-03-31</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S31" s="3" t="n">
-        <v>793</v>
+        <v>2723</v>
       </c>
       <c r="T31" s="3" t="n">
         <v>1</v>
@@ -3596,36 +3597,37 @@
       </c>
       <c r="V31" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="32" ht="150" customHeight="1">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>ningzimu/image-to-editable-ppt-skill</t>
+          <t>genkit-ai/genkit</t>
         </is>
       </c>
       <c r="B32" s="4" t="n">
-        <v>2429</v>
+        <v>6433</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>151.8</v>
+        <v>51.9</v>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>将图像、PDF转换为可编辑的PPT演示文稿
-【原文】Codex skill for converting slide images, PDFs, and image-based PPTX files into editable PowerPoint decks.</t>
+          <t>提供构建代理应用的框架
+【原文】Open-source framework for building agentic apps in JavaScript, Go, Dart, and Python, built and used in production by Google
+【依据】topics: agents, ai, embedders, genkit, llm, multimodal, rag, vector-database</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t>图文产线/视频产线</t>
+          <t>AI免费池/RAG检索线</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>技能包</t>
+          <t>代码库</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3640,7 +3642,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ningzimu/image-to-editable-ppt-skill</t>
+          <t>https://github.com/genkit-ai/genkit</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
@@ -3649,16 +3651,16 @@
         </is>
       </c>
       <c r="K32" s="5" t="n">
-        <v>21.69</v>
+        <v>7.42</v>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
@@ -3673,21 +3675,21 @@
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
-          <t>codex, codex-skill, editable-ppt, image-to-ppt, imagegen, multi-agent, pdf-to-pptx, powerpoint, pptx, presentation</t>
+          <t>agents, ai, embedders, genkit, llm, multimodal, rag, vector-database</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S32" s="3" t="n">
-        <v>112</v>
+        <v>867</v>
       </c>
       <c r="T32" s="3" t="n">
         <v>1</v>
@@ -3699,31 +3701,30 @@
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="33" ht="150" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>cocoindex-io/cocoindex</t>
+          <t>T8mars/minimax-h3-prompt-skill-T8</t>
         </is>
       </c>
       <c r="B33" s="4" t="n">
-        <v>11517</v>
+        <v>222</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>145</v>
+        <v>44.4</v>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>为长期代理提供增量引擎
-【原文】Incremental engine for long horizon agents 🌟 Star if you like it!</t>
+          <t>Creative DNA video prompt cases and installable Skills for MiniMax H3 and Seedance 2.0, with an Electron video viewer.</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -3743,7 +3744,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cocoindex-io/cocoindex</t>
+          <t>https://github.com/T8mars/minimax-h3-prompt-skill-T8</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
@@ -3752,16 +3753,16 @@
         </is>
       </c>
       <c r="K33" s="5" t="n">
-        <v>20.71</v>
+        <v>6.34</v>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
@@ -3771,29 +3772,29 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
-          <t>agentic-data-framework, ai, ai-agents, change-data-capture, codebase-intelligence, context-engineering, data-engineering, data-indexing, data-processing, etl, help-wanted, indexing</t>
+          <t>ai-video, codex-skills, creative-dna, electron, minimax-h3, prompt-engineering, seedance-2-0, video-generation</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S33" s="3" t="n">
-        <v>556</v>
+        <v>35</v>
       </c>
       <c r="T33" s="3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
@@ -3802,26 +3803,26 @@
       </c>
       <c r="V33" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="34" ht="150" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>promptfoo/promptfoo</t>
+          <t>robert-mcdermott/ai-knowledge-graph</t>
         </is>
       </c>
       <c r="B34" s="4" t="n">
-        <v>24982</v>
+        <v>3075</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>142</v>
+        <v>40</v>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>测试和评估AI的提示词、代理和RAG
-【原文】Test your prompts, agents, and RAGs. Red teaming/pentesting/vulnerability scanning for AI. Compare performance of GPT, Claude, Gemini, DeepSeek, and more. Simple declarative configs with command line and CI/CD integration.  Used by OpenAI and Anthropic.</t>
+          <t>生成 AI 驱动的知识图谱
+【原文】AI Powered Knowledge Graph Generator</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
@@ -3831,7 +3832,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>技能包/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3846,7 +3847,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/promptfoo/promptfoo</t>
+          <t>https://github.com/robert-mcdermott/ai-knowledge-graph</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -3855,16 +3856,16 @@
         </is>
       </c>
       <c r="K34" s="5" t="n">
-        <v>20.29</v>
+        <v>5.71</v>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
@@ -3879,21 +3880,21 @@
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
-          <t>ci, ci-cd, cicd, evaluation, evaluation-framework, llm, llm-eval, llm-evaluation, llm-evaluation-framework, llmops, pentesting, prompt-engineering</t>
+          <t>artificial-intelligence, knowledge-distillation, knowledge-graph, llm, networkx, pyvis, visualization</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>2023-04-28</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S34" s="3" t="n">
-        <v>1231</v>
+        <v>539</v>
       </c>
       <c r="T34" s="3" t="n">
         <v>1</v>
@@ -3905,41 +3906,41 @@
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="35" ht="150" customHeight="1">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>JunkFood02/Seal</t>
+          <t>dgraph-io/dgraph</t>
         </is>
       </c>
       <c r="B35" s="4" t="n">
-        <v>28855</v>
+        <v>21796</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>125.5</v>
+        <v>37.8</v>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>提供Android视频/音频下载器，基于yt-dlp
-【原文】🦭 Video/Audio Downloader for Android, based on yt-dlp</t>
+          <t>提供高性能的图数据库，适用于实时用例。
+【原文】high-performance graph database for real-time use cases</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H35" s="7" t="inlineStr">
@@ -3949,7 +3950,7 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/JunkFood02/Seal</t>
+          <t>https://github.com/dgraph-io/dgraph</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
@@ -3958,16 +3959,16 @@
         </is>
       </c>
       <c r="K35" s="5" t="n">
-        <v>17.93</v>
+        <v>5.4</v>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t>Kotlin</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
@@ -3982,21 +3983,21 @@
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
-          <t>android, f-droid, jetpack-compose, kotlin, material-design, youtube-dl, youtube-downloader, yt-dlp</t>
+          <t>database, distributed, go, knowledge-graph</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t>2022-04-15</t>
+          <t>2015-08-25</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S35" s="3" t="n">
-        <v>1609</v>
+        <v>4037</v>
       </c>
       <c r="T35" s="3" t="n">
         <v>1</v>
@@ -4008,26 +4009,26 @@
       </c>
       <c r="V35" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="36" ht="150" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>cometcanaryview7/canva-pro</t>
+          <t>kaomei/hand-drawn-video-prompts</t>
         </is>
       </c>
       <c r="B36" s="4" t="n">
-        <v>619</v>
+        <v>210</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>117.1</v>
+        <v>30.7</v>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>提供Canva Pro的高级图形设计工具和团队协作工作流程
-【原文】Canva Pro Cloud Toolkit &amp; Automation Studio. Advanced graphic design assets, team collaboration workflows, premium template management, and visual content creation tools.</t>
+          <t>将中文口播稿转换为手绘视频提示词
+【原文】将中文口播稿转换为 9:16 Q版手绘视频提示词，并把马斯克、黄仁勋、扎克伯格等科技人物转成非写实Q版角色｜Turn Chinese scripts into hand-drawn video prompts for Flow and Nano Banana.</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
@@ -4042,7 +4043,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H36" s="7" t="inlineStr">
@@ -4052,7 +4053,7 @@
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cometcanaryview7/canva-pro</t>
+          <t>https://github.com/kaomei/hand-drawn-video-prompts</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
@@ -4061,11 +4062,11 @@
         </is>
       </c>
       <c r="K36" s="5" t="n">
-        <v>16.73</v>
+        <v>4.38</v>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr"/>
@@ -4081,52 +4082,51 @@
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
-          <t>canva, canva-bulk-create, canva-editor-tools, canva-export-tools, canva-free, canva-full, canva-hack, canva-pro, canva-pro-for-life-time, canva-pro-team-2026, figma-alternative, figma-design</t>
+          <t>ai-video, b-roll, flow, nano-banana, prompt-engineering, storyboard</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="S36" s="3" t="n">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="T36" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V36" s="6" t="inlineStr">
         <is>
-          <t>content automation in:name,description stars:&gt;500 pushed:&gt;2026-06-12</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="37" ht="150" customHeight="1">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>agentscope-ai/agentscope-java</t>
+          <t>microsoft/work-iq</t>
         </is>
       </c>
       <c r="B37" s="4" t="n">
-        <v>5530</v>
+        <v>1002</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>110</v>
+        <v>29.8</v>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>构建分布式、生产级、长期运行的代理
-【原文】Build distributed, production-grade, long-running agents.</t>
+          <t>MCP Server and CLI for accessing Work IQ</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
@@ -4136,12 +4136,12 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H37" s="7" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/agentscope-ai/agentscope-java</t>
+          <t>https://github.com/microsoft/work-iq</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -4160,16 +4160,16 @@
         </is>
       </c>
       <c r="K37" s="5" t="n">
-        <v>15.71</v>
+        <v>4.25</v>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>PowerShell</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
@@ -4179,26 +4179,22 @@
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>adk, agent, agent-framework, agentic, agentic-ai, agentscope, ai, harness, llm</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P37" s="6" t="inlineStr"/>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S37" s="3" t="n">
-        <v>352</v>
+        <v>236</v>
       </c>
       <c r="T37" s="3" t="n">
         <v>1</v>
@@ -4210,26 +4206,27 @@
       </c>
       <c r="V37" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="38" ht="150" customHeight="1">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ruvnet/RuVector</t>
+          <t>xushengfeng/eSearch</t>
         </is>
       </c>
       <c r="B38" s="4" t="n">
-        <v>4487</v>
+        <v>7114</v>
       </c>
       <c r="C38" s="5" t="n">
-        <v>106.5</v>
+        <v>27.7</v>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>高性能实时自学习AI，向量GNN，内存数据库
-【原文】RuVector is a High Performance, Real-Time, Self-Learning Ai, Vector GNN, Memory DB built in Rust.</t>
+          <t>提供截图、OCR搜索、翻译、图像编辑等功能
+【原文】截屏 离线OCR 搜索翻译 以图搜图 贴图 录屏 万向滚动截屏 屏幕翻译   Screenshot  Offline OCR   Search   Translate   Search for picture   Paste the picture on the screen   Screen recorder   Omnidirectional scrolling screenshot   Screen translator  支持Windows Linux macOS
+【依据】Screenshot Offline OCR Search Translate Search for picture Paste the picture on the screen Screen recorder Omnidirection</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
@@ -4242,9 +4239,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H38" s="7" t="inlineStr">
@@ -4254,7 +4251,7 @@
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ruvnet/RuVector</t>
+          <t>https://github.com/xushengfeng/eSearch</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
@@ -4263,16 +4260,16 @@
         </is>
       </c>
       <c r="K38" s="5" t="n">
-        <v>15.21</v>
+        <v>3.95</v>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
@@ -4287,21 +4284,21 @@
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
-          <t>ai, ai-ocr, attention-mechanism, gnn, gnn-model, gnns, graph, graph-neural-networks, llm-inference, low-latency, mincut, neo4j</t>
+          <t>clipboard, color-picker, cross-platform, electron, image-editing, image-editor, linux, live-text, macos, ocr, paddleocr, recorder</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2021-10-06</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S38" s="3" t="n">
-        <v>295</v>
+        <v>1803</v>
       </c>
       <c r="T38" s="3" t="n">
         <v>1</v>
@@ -4313,26 +4310,26 @@
       </c>
       <c r="V38" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="39" ht="150" customHeight="1">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>Asabeneh/30-Days-Of-React</t>
+          <t>onestardao/WFGY</t>
         </is>
       </c>
       <c r="B39" s="4" t="n">
-        <v>27490</v>
+        <v>1789</v>
       </c>
       <c r="C39" s="5" t="n">
-        <v>88.59999999999999</v>
+        <v>26.9</v>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>提供30天React挑战，逐步指导学习React
-【原文】30 Days of  React challenge is a step by step guide to learn React in 30 days.  These videos may help too: https://www.youtube.com/channel/UC7PNRuno1rzYPb1xLa4yktw</t>
+          <t>提供 AI 推理、RAG 和代理的开放源代码库，包括问题地图、全局调试卡等工具。
+【原文】WFGY is heading toward WFGY 5.0 Polaris Protocol, a major open-source release for AI reasoning, RAG, agents, and real-world workflows. Includes Problem Map, Global Debug Card, WFGY 4.0, and the CFV Easter Egg.</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
@@ -4342,12 +4339,12 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H39" s="7" t="inlineStr">
@@ -4357,7 +4354,7 @@
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Asabeneh/30-Days-Of-React</t>
+          <t>https://github.com/onestardao/WFGY</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
@@ -4366,16 +4363,16 @@
         </is>
       </c>
       <c r="K39" s="5" t="n">
-        <v>12.66</v>
+        <v>3.84</v>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
@@ -4390,21 +4387,21 @@
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
-          <t>30dayofjavascript, challenge, css, html, html5, javascript, js, programming, react, react-router-dom, reactjs, redux</t>
+          <t>ai-agents, alignment, debugging, evaluation, graphrag, hallucination, information-retrieval, knowledge-graph, llm, rag, reasoning, retrieval-augmented-generation</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t>2020-09-29</t>
+          <t>2025-06-04</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S39" s="3" t="n">
-        <v>2172</v>
+        <v>466</v>
       </c>
       <c r="T39" s="3" t="n">
         <v>1</v>
@@ -4416,26 +4413,27 @@
       </c>
       <c r="V39" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="40" ht="150" customHeight="1">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Unstructured-IO/unstructured</t>
+          <t>gptme/gptme</t>
         </is>
       </c>
       <c r="B40" s="4" t="n">
-        <v>15412</v>
+        <v>4411</v>
       </c>
       <c r="C40" s="5" t="n">
-        <v>74.7</v>
+        <v>24.4</v>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>将文档转换为结构化数据的 HTML 库
-【原文】Convert documents to structured data effortlessly. Unstructured is open-source ETL solution for transforming complex documents into clean, structured formats for language models.  Visit our website to learn more about our enterprise grade Platform product for production grade workflows, partitioning, enrichments, chunking and embedding.</t>
+          <t>提供终端 AI 助手
+【原文】Your agent in your terminal, equipped with local tools: writes code, uses the terminal, browses the web. Make your own persistent autonomous agent on top!
+【依据】topics: agent, agents, ai-agents, ai-assistant, anthropic, chatbot, chatgpt, cli, code-generation, llamacpp, llm, llm-ag</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
@@ -4445,7 +4443,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>数据集/代码库</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4460,7 +4458,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/Unstructured-IO/unstructured</t>
+          <t>https://github.com/gptme/gptme</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -4469,16 +4467,16 @@
         </is>
       </c>
       <c r="K40" s="5" t="n">
-        <v>10.67</v>
+        <v>3.48</v>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
@@ -4493,21 +4491,21 @@
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
-          <t>data-pipelines, deep-learning, document-image-analysis, document-image-processing, document-parser, document-parsing, docx, donut, information-retrieval, langchain, llm, machine-learning</t>
+          <t>agent, agents, ai-agents, ai-assistant, anthropic, chatbot, chatgpt, cli, code-generation, llamacpp, llm, llm-agent</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t>2022-09-26</t>
+          <t>2023-03-24</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S40" s="3" t="n">
-        <v>1445</v>
+        <v>1269</v>
       </c>
       <c r="T40" s="3" t="n">
         <v>1</v>
@@ -4519,41 +4517,40 @@
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="41" ht="150" customHeight="1">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>mg-chao/snow-apps</t>
+          <t>langroid/langroid</t>
         </is>
       </c>
       <c r="B41" s="4" t="n">
-        <v>4982</v>
+        <v>4102</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>62.2</v>
+        <v>23</v>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>提供图像查看器、OCR 和屏幕录制工具的 C++ 代码库
-【原文】Snow Apps repository, providing source code for Snow Shot and Snow Image Viewer.</t>
+          <t>Harness LLMs with Multi-Agent Programming</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>图文产线/古籍OCR线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H41" s="7" t="inlineStr">
@@ -4563,7 +4560,7 @@
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/mg-chao/snow-apps</t>
+          <t>https://github.com/langroid/langroid</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
@@ -4572,16 +4569,16 @@
         </is>
       </c>
       <c r="K41" s="5" t="n">
-        <v>8.880000000000001</v>
+        <v>3.29</v>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>C++</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
@@ -4591,26 +4588,26 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
-          <t>image-viewer, ocr, screen-recorder, screenshot, tools</t>
+          <t>agents, ai, chatgpt, function-calling, gpt, gpt-4, gpt4, information-retrieval, language-model, llama, llm, llm-agent</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-04-16</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S41" s="3" t="n">
-        <v>561</v>
+        <v>1246</v>
       </c>
       <c r="T41" s="3" t="n">
         <v>1</v>
@@ -4622,31 +4619,31 @@
       </c>
       <c r="V41" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="42" ht="150" customHeight="1">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ShareX/ShareX</t>
+          <t>shunbao-p/OneCue</t>
         </is>
       </c>
       <c r="B42" s="4" t="n">
-        <v>39508</v>
+        <v>104</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>58.6</v>
+        <v>22.8</v>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>屏幕区域捕获和文件上传工具
-【原文】ShareX is a free and open-source application that enables users to capture or record any area of their screen with a single keystroke. It also supports uploading images, text, and various file types to a wide range of destinations.</t>
+          <t>生成高质量视频、图像和音频内容
+【原文】只需要一台能跑 codex 的电脑，一句话直接可以生成可用的高质量视频，图像音频等一站式搞定。目前使用 mac-codex 中，使用流程：调用短视频导演 技能，告诉 codex 要做什么主题内容可选提交相关素材，然后等待即可直接得到成品，允许审阅后微调。</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
@@ -4654,9 +4651,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H42" s="7" t="inlineStr">
@@ -4666,7 +4663,7 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/ShareX/ShareX</t>
+          <t>https://github.com/shunbao-p/OneCue</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
@@ -4675,16 +4672,16 @@
         </is>
       </c>
       <c r="K42" s="5" t="n">
-        <v>8.369999999999999</v>
+        <v>3.25</v>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t>GPL-3.0</t>
+          <t>Apache-2.0</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
@@ -4697,69 +4694,65 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>avalonia, capture, color-picker, csharp, dropbox, file-sharing, file-upload, ftp, gif, gif-recorder, image-annotation, ocr</t>
-        </is>
-      </c>
+      <c r="P42" s="6" t="inlineStr"/>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t>2013-10-08</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="S42" s="3" t="n">
-        <v>4720</v>
+        <v>32</v>
       </c>
       <c r="T42" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="43" ht="150" customHeight="1">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>raphaelmansuy/edgequake</t>
+          <t>MontageAI/niwo-render-everything</t>
         </is>
       </c>
       <c r="B43" s="4" t="n">
-        <v>2092</v>
+        <v>108</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>55.6</v>
+        <v>22.3</v>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>将文档转换为智能知识图谱
-【原文】EdegQuake 🌋 High-performance GraphRAG inspired from LightRag written in Rust; Transform documents into intelligent knowledge graphs for superior retrieval and generation</t>
+          <t>将任意内容转换为短视频的技能
+【原文】把任意内容做成短视频 · Niwo Agent Skill</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>视频产线</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>技能包</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H43" s="7" t="inlineStr">
@@ -4769,7 +4762,7 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/raphaelmansuy/edgequake</t>
+          <t>https://github.com/MontageAI/niwo-render-everything</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
@@ -4778,16 +4771,16 @@
         </is>
       </c>
       <c r="K43" s="5" t="n">
-        <v>7.95</v>
+        <v>3.18</v>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
@@ -4800,55 +4793,50 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>graphrag, knowledge-graph, lightrag, rag</t>
-        </is>
-      </c>
+      <c r="P43" s="6" t="inlineStr"/>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t>2025-12-21</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S43" s="3" t="n">
-        <v>263</v>
+        <v>34</v>
       </c>
       <c r="T43" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V43" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="44" ht="150" customHeight="1">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>najmuzzaman-mohammad/gawkbot</t>
+          <t>dmMaze/BallonsTranslator</t>
         </is>
       </c>
       <c r="B44" s="4" t="n">
-        <v>1287</v>
+        <v>5117</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>53.3</v>
+        <v>22.1</v>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>开源的 grok bot，通过 AI 模型自动化工作并构建微应用
-【原文】open source grok bot. gawk bots automate your menial work via AI models and build you microapps to manage the outcome, so that you have a false sense of control.
-【依据】open source grok bot. gawk bots automate your menial work via AI models and build you microapps to manage the outcome.</t>
+          <t>深度学习辅助漫画翻译工具，支持一键机翻和图像/文本编辑
+【原文】深度学习辅助漫画翻译工具, 支持一键机翻和简单的图像/文本编辑 | Yet another computer-aided comic/manga translation tool powered by deeplearning</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
@@ -4858,12 +4846,12 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H44" s="7" t="inlineStr">
@@ -4873,7 +4861,7 @@
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/najmuzzaman-mohammad/gawkbot</t>
+          <t>https://github.com/dmMaze/BallonsTranslator</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
@@ -4882,16 +4870,16 @@
         </is>
       </c>
       <c r="K44" s="5" t="n">
-        <v>7.62</v>
+        <v>3.16</v>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
@@ -4906,21 +4894,21 @@
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
-          <t>agents, ai-agents, ai-teammates, autonomous-agents, claude-code, codex, grok-bot, grok-bot-alternative, grokbot, knowledge-graph, local-llm, microapps</t>
+          <t>auto-translation, chinese-translation, comics, computer-aided-translation, computer-vision, deep-learning, inpainting, manga, ocr, pyqt, pyqt6, pytorch</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S44" s="3" t="n">
-        <v>169</v>
+        <v>1618</v>
       </c>
       <c r="T44" s="3" t="n">
         <v>1</v>
@@ -4932,41 +4920,42 @@
       </c>
       <c r="V44" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="45" ht="150" customHeight="1">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>NickeManarin/ScreenToGif</t>
+          <t>rothgar/awesome-tmux</t>
         </is>
       </c>
       <c r="B45" s="4" t="n">
-        <v>27613</v>
+        <v>10336</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>52.4</v>
+        <v>19</v>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>提供屏幕录制和编辑工具，支持保存为gif或视频
-【原文】🎬 ScreenToGif allows you to record a selected area of your screen, edit and save it as a gif or video.</t>
+          <t>提供 tmux 资源列表
+【原文】A list of awesome resources for tmux
+【依据】topics: awesome, awesome-list, tmux</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>未知·需人工确认</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H45" s="7" t="inlineStr">
@@ -4976,7 +4965,7 @@
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/NickeManarin/ScreenToGif</t>
+          <t>https://github.com/rothgar/awesome-tmux</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
@@ -4985,18 +4974,14 @@
         </is>
       </c>
       <c r="K45" s="5" t="n">
-        <v>7.48</v>
+        <v>2.71</v>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t>MS-PL</t>
-        </is>
-      </c>
-      <c r="M45" s="3" t="inlineStr">
-        <is>
-          <t>C#</t>
-        </is>
-      </c>
+          <t>NONE</t>
+        </is>
+      </c>
+      <c r="M45" s="3" t="inlineStr"/>
       <c r="N45" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5009,21 +4994,21 @@
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
-          <t>editor, gif, recorder, sketchboard, video, webcam, wpf</t>
+          <t>awesome, awesome-list, tmux</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t>2016-08-02</t>
+          <t>2016-04-04</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S45" s="3" t="n">
-        <v>3691</v>
+        <v>3814</v>
       </c>
       <c r="T45" s="3" t="n">
         <v>1</v>
@@ -5035,31 +5020,31 @@
       </c>
       <c r="V45" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="46" ht="150" customHeight="1">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>pipeshub-ai/pipeshub-ai</t>
+          <t>vastsa/PI-Desktop</t>
         </is>
       </c>
       <c r="B46" s="4" t="n">
-        <v>3735</v>
+        <v>3140</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>47.2</v>
+        <v>17.3</v>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>连接企业知识到 AI 的开源平台，提供权限感知搜索和知识图谱
-【原文】PipesHub is an open-source platform for securely connecting enterprise knowledge to AI. Give AI agents trusted context and your team permission-aware search with verified citations across your business systems.</t>
+          <t>本地优先的AI编码代理桌面应用，支持插件安装
+【原文】Local-first AI coding agent desktop: Electron + Rust host core + pi Agent Harness + user-installable plugins</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
@@ -5067,9 +5052,9 @@
           <t>技能包/架构参考</t>
         </is>
       </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H46" s="7" t="inlineStr">
@@ -5079,7 +5064,7 @@
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/pipeshub-ai/pipeshub-ai</t>
+          <t>https://github.com/vastsa/PI-Desktop</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
@@ -5088,16 +5073,16 @@
         </is>
       </c>
       <c r="K46" s="5" t="n">
-        <v>6.75</v>
+        <v>2.47</v>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>LGPL-3.0</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
@@ -5112,52 +5097,51 @@
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
-          <t>agent, agents, ai, drive, glean, gmail, knowledge-graph, langchain, langgraph, llamaparse, notion, ollama</t>
+          <t>ai-agent, coding-agent, desktop-app, electron, global, i18n, local-first, mcp, pi, pi-agent, pi-desktop, plugins</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2025-03-06</t>
+          <t>2023-03-22</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="S46" s="3" t="n">
-        <v>553</v>
+        <v>1271</v>
       </c>
       <c r="T46" s="3" t="n">
         <v>2</v>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V46" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>topic:ai-agent stars:&gt;2000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="47" ht="150" customHeight="1">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>zhitongblog/solomd</t>
+          <t>donghuixin/AI-Vibe-Writing-Skills</t>
         </is>
       </c>
       <c r="B47" s="4" t="n">
-        <v>1024</v>
+        <v>492</v>
       </c>
       <c r="C47" s="5" t="n">
-        <v>46.3</v>
+        <v>16.7</v>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>Markdown编辑器，连接LLM的桥梁，包含MCP服务器
-【原文】A markdown editor — and the bridge to your LLM. Local-first, MIT, ~15 MB. Bundled MCP server lets Claude Code / Codex / Cursor drive your vault directly. 14 AI providers BYOK.</t>
+          <t>Using AI for high quality writing</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
@@ -5182,7 +5166,7 @@
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zhitongblog/solomd</t>
+          <t>https://github.com/donghuixin/AI-Vibe-Writing-Skills</t>
         </is>
       </c>
       <c r="J47" s="3" t="inlineStr">
@@ -5191,7 +5175,7 @@
         </is>
       </c>
       <c r="K47" s="5" t="n">
-        <v>6.61</v>
+        <v>2.38</v>
       </c>
       <c r="L47" s="3" t="inlineStr">
         <is>
@@ -5200,7 +5184,7 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>TypeScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N47" s="3" t="inlineStr">
@@ -5210,26 +5194,22 @@
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>是</t>
-        </is>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>ai, android, autogit, byok, cross-platform, ios, knowledge-base, local-first, markdown, markdown-editor, mcp, mcp-server</t>
-        </is>
-      </c>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P47" s="6" t="inlineStr"/>
       <c r="Q47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="R47" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S47" s="3" t="n">
-        <v>155</v>
+        <v>207</v>
       </c>
       <c r="T47" s="3" t="n">
         <v>1</v>
@@ -5241,36 +5221,36 @@
       </c>
       <c r="V47" s="6" t="inlineStr">
         <is>
-          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="48" ht="150" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>CarGuo/GSYVideoPlayer</t>
+          <t>j3ssie/osmedeus</t>
         </is>
       </c>
       <c r="B48" s="4" t="n">
-        <v>21490</v>
+        <v>6561</v>
       </c>
       <c r="C48" s="5" t="n">
-        <v>41.9</v>
+        <v>16</v>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>提供视频播放器、支持16k页面大小、弹幕等
-【原文】Video players (IJKplayer, ExoPlayer, MediaPlayer), HTTPS, 16k page size, danmaku (bullet chat) support, external subtitles, support for filters, watermarks, and GIF screenshots, pre-roll and mid-roll ads, multiple simultaneous playback, basic seeking/dragging, volume and brightness adjustment, play-while-cache support</t>
+          <t>现代安全编排引擎，用于安全攻击面管理和渗透测试
+【原文】A Modern Orchestration Engine for Security</t>
         </is>
       </c>
       <c r="E48" s="3" t="inlineStr">
         <is>
-          <t>视频产线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>可部署服务</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5285,7 +5265,7 @@
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CarGuo/GSYVideoPlayer</t>
+          <t>https://github.com/j3ssie/osmedeus</t>
         </is>
       </c>
       <c r="J48" s="3" t="inlineStr">
@@ -5294,16 +5274,16 @@
         </is>
       </c>
       <c r="K48" s="5" t="n">
-        <v>5.99</v>
+        <v>2.29</v>
       </c>
       <c r="L48" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>Go</t>
         </is>
       </c>
       <c r="N48" s="3" t="inlineStr">
@@ -5318,21 +5298,21 @@
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
-          <t>16k, android, exoplayer, ffmpeg, gsy, ijkplayer, player, ssl, video, videocache</t>
+          <t>agentic-ai, attack-surface-management, bugbounty, go, hacking, hacking-tool, llm, osint, penetration-testing, pentesting, reconnaissance, security</t>
         </is>
       </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
-          <t>2016-11-13</t>
+          <t>2018-11-10</t>
         </is>
       </c>
       <c r="R48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S48" s="3" t="n">
-        <v>3588</v>
+        <v>2864</v>
       </c>
       <c r="T48" s="3" t="n">
         <v>1</v>
@@ -5344,26 +5324,26 @@
       </c>
       <c r="V48" s="6" t="inlineStr">
         <is>
-          <t>video in:name,description stars:&gt;20000 pushed:&gt;2026-06-12</t>
+          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="49" ht="150" customHeight="1">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>kyegomez/swarms</t>
+          <t>iwe-org/iwe</t>
         </is>
       </c>
       <c r="B49" s="4" t="n">
-        <v>7161</v>
+        <v>1639</v>
       </c>
       <c r="C49" s="5" t="n">
-        <v>41.2</v>
+        <v>15.9</v>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>提供企业级多代理编排框架的 Python 库
-【原文】The Enterprise-Grade Multi-Agent Orchestration Framework. Website: https://swarms.ai</t>
+          <t>提供 Markdown 知识图谱和 CLI + MCP 内存
+【原文】Markdown knowledge graph — LSP for your editor, CLI + MCP memory for your AI agents</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
@@ -5373,7 +5353,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5388,7 +5368,7 @@
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/kyegomez/swarms</t>
+          <t>https://github.com/iwe-org/iwe</t>
         </is>
       </c>
       <c r="J49" s="3" t="inlineStr">
@@ -5397,7 +5377,7 @@
         </is>
       </c>
       <c r="K49" s="5" t="n">
-        <v>5.88</v>
+        <v>2.27</v>
       </c>
       <c r="L49" s="3" t="inlineStr">
         <is>
@@ -5406,7 +5386,7 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Rust</t>
         </is>
       </c>
       <c r="N49" s="3" t="inlineStr">
@@ -5421,21 +5401,21 @@
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
-          <t>agentic-ai, agentic-workflow, agents, ai, artificial-intelligence, chatgpt, claude-code, gpt4all, huggingface, langchain, langchain-python, machine-learning</t>
+          <t>ai-agents, ai-memory, cli, helix, knowledge-graph, knowledge-management, language-server, local-first, lsp, markdown, mcp, neovim</t>
         </is>
       </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
-          <t>2023-05-11</t>
+          <t>2024-09-20</t>
         </is>
       </c>
       <c r="R49" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S49" s="3" t="n">
-        <v>1218</v>
+        <v>723</v>
       </c>
       <c r="T49" s="3" t="n">
         <v>1</v>
@@ -5447,26 +5427,25 @@
       </c>
       <c r="V49" s="6" t="inlineStr">
         <is>
-          <t>topic:agentic-ai stars:&gt;5000 pushed:&gt;2026-08-11</t>
+          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="50" ht="150" customHeight="1">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>modelscope/evalscope</t>
+          <t>hemansnation/AI-Engineer-Headquarters</t>
         </is>
       </c>
       <c r="B50" s="4" t="n">
-        <v>3401</v>
+        <v>3683</v>
       </c>
       <c r="C50" s="5" t="n">
-        <v>23.6</v>
+        <v>15.8</v>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>用于高效评估大型模型（LLM、VLM、AIGC）的框架
-【原文】A streamlined and customizable framework for efficient large model (LLM, VLM, AIGC) evaluation and performance benchmarking.</t>
+          <t>A collection of scientific methods, processes, algorithms, and systems to build stories &amp; models.</t>
         </is>
       </c>
       <c r="E50" s="3" t="inlineStr">
@@ -5476,12 +5455,12 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H50" s="7" t="inlineStr">
@@ -5491,7 +5470,7 @@
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/modelscope/evalscope</t>
+          <t>https://github.com/hemansnation/AI-Engineer-Headquarters</t>
         </is>
       </c>
       <c r="J50" s="3" t="inlineStr">
@@ -5500,16 +5479,16 @@
         </is>
       </c>
       <c r="K50" s="5" t="n">
-        <v>3.37</v>
+        <v>2.26</v>
       </c>
       <c r="L50" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Jupyter Notebook</t>
         </is>
       </c>
       <c r="N50" s="3" t="inlineStr">
@@ -5519,26 +5498,26 @@
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
-          <t>evaluation, llm, performance, rag, vlm</t>
+          <t>ai, ai-agents, aiengineering, data-structures-and-algorithms, deep-learning, langchain, langgraph, llm, llm-evaluation, llm-inference, llm-security, machine-learning</t>
         </is>
       </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
-          <t>2023-12-07</t>
+          <t>2022-03-29</t>
         </is>
       </c>
       <c r="R50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S50" s="3" t="n">
-        <v>1008</v>
+        <v>1629</v>
       </c>
       <c r="T50" s="3" t="n">
         <v>1</v>
@@ -5550,26 +5529,25 @@
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-11</t>
+          <t>topic:rag stars:&gt;3000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="51" ht="150" customHeight="1">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>doobidoo/mcp-memory-service</t>
+          <t>bostrot/wsl2-distro-manager</t>
         </is>
       </c>
       <c r="B51" s="4" t="n">
-        <v>1933</v>
+        <v>3998</v>
       </c>
       <c r="C51" s="5" t="n">
-        <v>21.7</v>
+        <v>15.3</v>
       </c>
       <c r="D51" s="6" t="inlineStr">
         <is>
-          <t>为 AI 代理管道提供持久化内存服务，包括知识图谱和自主合并
-【原文】Open-source persistent memory for AI agent pipelines (LangGraph, CrewAI, AutoGen) and Claude. REST API + knowledge graph + autonomous consolidation.</t>
+          <t>GUI for the Windows Subsystem for Linux — and native Linux/macOS VMs on Mac. Install, back up, move and configure distros without CLI flags; AI assistant with tools, MCP server for agents, remote WSL over SSH.</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
@@ -5579,12 +5557,12 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>MCP服务/可部署服务/代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H51" s="7" t="inlineStr">
@@ -5594,7 +5572,7 @@
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/doobidoo/mcp-memory-service</t>
+          <t>https://github.com/bostrot/wsl2-distro-manager</t>
         </is>
       </c>
       <c r="J51" s="3" t="inlineStr">
@@ -5603,16 +5581,16 @@
         </is>
       </c>
       <c r="K51" s="5" t="n">
-        <v>3.1</v>
+        <v>2.19</v>
       </c>
       <c r="L51" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NOASSERTION</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Dart</t>
         </is>
       </c>
       <c r="N51" s="3" t="inlineStr">
@@ -5622,26 +5600,26 @@
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
-          <t>agent-memory, agentic-ai, ai-agents, autogen, claude, crewai, knowledge-graph, langgraph, long-term-memory, mcp, mcp-server, memory</t>
+          <t>ai, developer-tools, docker, flutter, gui, llm, macos, mcp, model-context-protocol, rootfs, turnkey, virtual-machine</t>
         </is>
       </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2021-09-17</t>
         </is>
       </c>
       <c r="R51" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S51" s="3" t="n">
-        <v>623</v>
+        <v>1822</v>
       </c>
       <c r="T51" s="3" t="n">
         <v>1</v>
@@ -5653,41 +5631,40 @@
       </c>
       <c r="V51" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>mcp server in:name,description stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="52" ht="150" customHeight="1">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>CrossPaste/crosspaste-desktop</t>
+          <t>ratatui/awesome-ratatui</t>
         </is>
       </c>
       <c r="B52" s="4" t="n">
-        <v>2547</v>
+        <v>2001</v>
       </c>
       <c r="C52" s="5" t="n">
-        <v>17.4</v>
+        <v>13.9</v>
       </c>
       <c r="D52" s="6" t="inlineStr">
         <is>
-          <t>提供跨设备剪贴板同步的 Kotlin 应用程序，内置 OCR 和 CLI 服务器
-【原文】Cross-device clipboard sync for macOS, Windows &amp; Linux — end-to-end encrypted, LAN-only, no cloud. OCR, CLI and MCP server built in.</t>
+          <t>A curated list of TUI apps and libraries built with Ratatui</t>
         </is>
       </c>
       <c r="E52" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>可部署服务/技能包/架构参考</t>
-        </is>
-      </c>
-      <c r="G52" s="8" t="inlineStr">
-        <is>
-          <t>传染·只能读架构</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr">
+        <is>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H52" s="7" t="inlineStr">
@@ -5697,7 +5674,7 @@
       </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CrossPaste/crosspaste-desktop</t>
+          <t>https://github.com/ratatui/awesome-ratatui</t>
         </is>
       </c>
       <c r="J52" s="3" t="inlineStr">
@@ -5706,18 +5683,14 @@
         </is>
       </c>
       <c r="K52" s="5" t="n">
-        <v>2.48</v>
+        <v>1.98</v>
       </c>
       <c r="L52" s="3" t="inlineStr">
         <is>
-          <t>AGPL-3.0</t>
-        </is>
-      </c>
-      <c r="M52" s="3" t="inlineStr">
-        <is>
-          <t>Kotlin</t>
-        </is>
-      </c>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M52" s="3" t="inlineStr"/>
       <c r="N52" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -5725,29 +5698,29 @@
       </c>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
-          <t>cli, clipboard, clipboard-history, clipboard-manager, clips, compose-desktop, copy-paste, cross-platform, desktop-application, end-to-end-encryption, kotlin-multiplatform, local-first</t>
+          <t>awesome, awesome-list, ratatui, rust, tui</t>
         </is>
       </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
-          <t>2023-11-16</t>
+          <t>2023-12-06</t>
         </is>
       </c>
       <c r="R52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S52" s="3" t="n">
-        <v>1029</v>
+        <v>1012</v>
       </c>
       <c r="T52" s="3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U52" s="3" t="inlineStr">
         <is>
@@ -5756,41 +5729,41 @@
       </c>
       <c r="V52" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="53" ht="150" customHeight="1">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>dickwu/apple-design-skill</t>
+          <t>Dest1ny-Sec/Des-CTF-Knowledge</t>
         </is>
       </c>
       <c r="B53" s="4" t="n">
-        <v>390</v>
+        <v>202</v>
       </c>
       <c r="C53" s="5" t="n">
-        <v>14</v>
+        <v>13.4</v>
       </c>
       <c r="D53" s="6" t="inlineStr">
         <is>
-          <t>基于Apple HIG的跨平台UI/UX设计审查器
-【原文】Cross-platform UI/UX design reviewer based on Apple HIG. Works with Flutter, Tauri, Electron, React Native. Compatible with Claude Code, Cursor, Codex.</t>
+          <t>CTF知识库，包含漏洞文章、脚本和AI/RAG知识库
+【原文】2026最新CTF知识库：12大Web漏洞深度文章+1156篇历年大赛WP+50+脚本+Payload速查 +AI/RAG离线在线知识库</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>未归类</t>
+          <t>RAG检索线</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>技能包/架构参考</t>
+          <t>数据集/代码库</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H53" s="7" t="inlineStr">
@@ -5800,7 +5773,7 @@
       </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/dickwu/apple-design-skill</t>
+          <t>https://github.com/Dest1ny-Sec/Des-CTF-Knowledge</t>
         </is>
       </c>
       <c r="J53" s="3" t="inlineStr">
@@ -5809,16 +5782,16 @@
         </is>
       </c>
       <c r="K53" s="5" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="L53" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
+          <t>MIT</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="N53" s="3" t="inlineStr">
@@ -5833,52 +5806,52 @@
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
-          <t>apple-hig, claude-code, codex, cursor, design-system, electron, flutter, liquid-glass, tauri, ui-ux</t>
+          <t>ai, ctf, ctf-challenges, ctf-writeups, knowledge-base, networking-security, rag-chatbot</t>
         </is>
       </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-05-30</t>
         </is>
       </c>
       <c r="R53" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="S53" s="3" t="n">
-        <v>195</v>
+        <v>106</v>
       </c>
       <c r="T53" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U53" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V53" s="6" t="inlineStr">
         <is>
-          <t>skill in:name stars:&gt;200 pushed:&gt;2026-08-11</t>
+          <t>RAG 知识库 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="54" ht="150" customHeight="1">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>cyanfish/naps2</t>
+          <t>zclucas/RMT</t>
         </is>
       </c>
       <c r="B54" s="4" t="n">
-        <v>4502</v>
+        <v>1114</v>
       </c>
       <c r="C54" s="5" t="n">
-        <v>7.8</v>
+        <v>12.7</v>
       </c>
       <c r="D54" s="6" t="inlineStr">
         <is>
-          <t>扫描文档到PDF等格式
-【原文】Scan documents to PDF and more, as simply as possible.</t>
+          <t>基于AHKv2的免费开源宏工具，用于自动化和图像识别
+【原文】RMT (RuoMengTu) is a free, open-source macro tool built on AHKv2. Let the code handle the tedious work—you have more meaningful things to do.</t>
         </is>
       </c>
       <c r="E54" s="3" t="inlineStr">
@@ -5891,9 +5864,9 @@
           <t>未定</t>
         </is>
       </c>
-      <c r="G54" s="3" t="inlineStr">
-        <is>
-          <t>未知·需人工确认</t>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H54" s="7" t="inlineStr">
@@ -5903,7 +5876,7 @@
       </c>
       <c r="I54" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/cyanfish/naps2</t>
+          <t>https://github.com/zclucas/RMT</t>
         </is>
       </c>
       <c r="J54" s="3" t="inlineStr">
@@ -5912,16 +5885,16 @@
         </is>
       </c>
       <c r="K54" s="5" t="n">
-        <v>1.11</v>
+        <v>1.81</v>
       </c>
       <c r="L54" s="3" t="inlineStr">
         <is>
-          <t>NOASSERTION</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>C#</t>
+          <t>AutoHotkey</t>
         </is>
       </c>
       <c r="N54" s="3" t="inlineStr">
@@ -5936,21 +5909,21 @@
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
-          <t>csharp, dotnet, escl, linux, macos, ocr, pdf, sane, scanner, twain, wia, windows</t>
+          <t>ahk, autohotkey, automation, gamepad-macros, image-recognition, key-macros, menu-macros, ocr, timed-macros</t>
         </is>
       </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
-          <t>2015-07-19</t>
+          <t>2025-01-07</t>
         </is>
       </c>
       <c r="R54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S54" s="3" t="n">
-        <v>4071</v>
+        <v>614</v>
       </c>
       <c r="T54" s="3" t="n">
         <v>1</v>
@@ -5962,26 +5935,26 @@
       </c>
       <c r="V54" s="6" t="inlineStr">
         <is>
-          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-12</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="55" ht="150" customHeight="1">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>aviaryan/awesome-no-login-web-apps</t>
+          <t>xianyu110/awesome-gptimage2</t>
         </is>
       </c>
       <c r="B55" s="4" t="n">
-        <v>3355</v>
+        <v>267</v>
       </c>
       <c r="C55" s="5" t="n">
-        <v>6.6</v>
+        <v>12.5</v>
       </c>
       <c r="D55" s="6" t="inlineStr">
         <is>
-          <t>无需登录的免费网络应用列表
-【原文】🚀 Awesome (free) web apps that work without login</t>
+          <t>提供 GPT Image 2 中文提示词实战手册
+【原文】GPT Image 2 中文提示词实战手册（本站）。最新 Images 2.5 玩法请看 awesome-gpt-image2.5：https://xianyu110.github.io/awesome-gpt-image2.5/</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
@@ -6006,7 +5979,7 @@
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/aviaryan/awesome-no-login-web-apps</t>
+          <t>https://github.com/xianyu110/awesome-gptimage2</t>
         </is>
       </c>
       <c r="J55" s="3" t="inlineStr">
@@ -6015,7 +5988,7 @@
         </is>
       </c>
       <c r="K55" s="5" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.78</v>
       </c>
       <c r="L55" s="3" t="inlineStr">
         <is>
@@ -6024,7 +5997,7 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="N55" s="3" t="inlineStr">
@@ -6039,12 +6012,12 @@
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
-          <t>application, applications, awesome, awesome-list, awesomeness, list, no-login, no-login-web-apps, portableapps, web-app</t>
+          <t>chatgpt, gpt, gptimage, gptimage2</t>
         </is>
       </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
-          <t>2016-12-06</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="R55" s="3" t="inlineStr">
@@ -6053,38 +6026,38 @@
         </is>
       </c>
       <c r="S55" s="3" t="n">
-        <v>3565</v>
+        <v>150</v>
       </c>
       <c r="T55" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U55" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V55" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-11</t>
+          <t>提示词 in:name,description stars:&gt;200 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="56" ht="150" customHeight="1">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>wenhwu/awesome-remote-sensing-change-detection</t>
+          <t>fluxions-ai/vui</t>
         </is>
       </c>
       <c r="B56" s="4" t="n">
-        <v>2325</v>
+        <v>762</v>
       </c>
       <c r="C56" s="5" t="n">
-        <v>5.7</v>
+        <v>11.5</v>
       </c>
       <c r="D56" s="6" t="inlineStr">
         <is>
-          <t>收集远程传感变化检测的数据集和工具
-【原文】A comprehensive and up-to-date compilation of datasets, tools, methods, review papers, and competitions for remote sensing change detection.</t>
+          <t>提供实时文本到语音转换模型，支持CPU推理和边缘AI
+【原文】Vui Nano — a small, context-aware text-to-speech model trained on real conversations. 219M active params (305M total), Apache 2.0, voice cloning, streaming, runs on CPU (dependency-free C build). Ships with a full real-time voice assistant: WebRTC, ASR, local LLM, OpenAI Realtime API compatible.</t>
         </is>
       </c>
       <c r="E56" s="3" t="inlineStr">
@@ -6094,12 +6067,12 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>未知·需人工确认</t>
         </is>
       </c>
       <c r="H56" s="7" t="inlineStr">
@@ -6109,7 +6082,7 @@
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/wenhwu/awesome-remote-sensing-change-detection</t>
+          <t>https://github.com/fluxions-ai/vui</t>
         </is>
       </c>
       <c r="J56" s="3" t="inlineStr">
@@ -6118,14 +6091,18 @@
         </is>
       </c>
       <c r="K56" s="5" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.64</v>
       </c>
       <c r="L56" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M56" s="3" t="inlineStr"/>
+          <t>NOASSERTION</t>
+        </is>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N56" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6138,21 +6115,21 @@
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
-          <t>awesome, change-detection, dataset, deep-learning, remote-sensing</t>
+          <t>conversational-ai, conversational-speech, cpu-inference, edge-ai, lightweight, multi-speaker, on-device, openai-realtime, pytorch, realtime-api, realtime-tts, speech-synthesis</t>
         </is>
       </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
-          <t>2018-11-03</t>
+          <t>2025-06-05</t>
         </is>
       </c>
       <c r="R56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S56" s="3" t="n">
-        <v>2868</v>
+        <v>465</v>
       </c>
       <c r="T56" s="3" t="n">
         <v>1</v>
@@ -6164,41 +6141,41 @@
       </c>
       <c r="V56" s="6" t="inlineStr">
         <is>
-          <t>awesome in:name stars:&gt;2000 pushed:&gt;2026-08-11</t>
+          <t>free llm api in:name,description stars:&gt;200 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="57" ht="150" customHeight="1">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>zibo-chen/ocr-rs</t>
+          <t>skrstop/MCPHub-Desktop</t>
         </is>
       </c>
       <c r="B57" s="4" t="n">
-        <v>326</v>
+        <v>215</v>
       </c>
       <c r="C57" s="5" t="n">
-        <v>4.4</v>
+        <v>10.4</v>
       </c>
       <c r="D57" s="6" t="inlineStr">
         <is>
-          <t>提供高性能OCR识别库，支持多种语言和调用方式
-【原文】高性能OCR识别库，支持上百种语言，提供命令行、图形界面及C API多种调用方式，使用便捷高效。  High-performance OCR library powered by PaddleOCR v4/v5/v6 with MNN backend. Supports 10+ languages (Chinese, English, Japanese, Korean, Arabic, Cyrillic, Thai, etc). Provides Rust crate + C API + CLI tools. Fast, lightweight, easy-to-integrate.</t>
+          <t>桌面客户端，用于管理MCP服务器、Skills和RAG知识库
+【原文】MCPHub Desktop 是一款基于 Tauri 2 构建的桌面客户端，用于在个人电脑上统一管理 MCP服务器、Skills、RAG 知识库。所有进程、配置、密钥与向量数据都运行/保存在用户自己的机器上，不依赖任何远端服务。</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>古籍OCR线</t>
+          <t>AI免费池</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>MCP服务/代码库</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>宽松·可进闭源</t>
+          <t>无许可·不可用</t>
         </is>
       </c>
       <c r="H57" s="7" t="inlineStr">
@@ -6208,7 +6185,7 @@
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/zibo-chen/ocr-rs</t>
+          <t>https://github.com/skrstop/MCPHub-Desktop</t>
         </is>
       </c>
       <c r="J57" s="3" t="inlineStr">
@@ -6217,16 +6194,16 @@
         </is>
       </c>
       <c r="K57" s="5" t="n">
-        <v>0.63</v>
+        <v>1.48</v>
       </c>
       <c r="L57" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>NONE</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>Rust</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N57" s="3" t="inlineStr">
@@ -6239,23 +6216,19 @@
           <t>是</t>
         </is>
       </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>ocr, ocr-rs, paddleocr, tesseract-ocr</t>
-        </is>
-      </c>
+      <c r="P57" s="6" t="inlineStr"/>
       <c r="Q57" s="3" t="inlineStr">
         <is>
-          <t>2025-04-12</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="R57" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="S57" s="3" t="n">
-        <v>516</v>
+        <v>145</v>
       </c>
       <c r="T57" s="3" t="n">
         <v>1</v>
@@ -6267,41 +6240,41 @@
       </c>
       <c r="V57" s="6" t="inlineStr">
         <is>
-          <t>OCR 识别 in:name,description stars:&gt;100 pushed:&gt;2026-06-12</t>
+          <t>RAG 知识库 in:name,description stars:&gt;200</t>
         </is>
       </c>
     </row>
     <row r="58" ht="150" customHeight="1">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>iMoonLab/Hyper-RAG</t>
+          <t>SnapXL/SnapX</t>
         </is>
       </c>
       <c r="B58" s="4" t="n">
-        <v>319</v>
+        <v>1028</v>
       </c>
       <c r="C58" s="5" t="n">
-        <v>4.3</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D58" s="6" t="inlineStr">
         <is>
-          <t>提供使用超图驱动的检索增强生成来对抗LLM幻觉的Hyper-RAG工具
-【原文】"Hyper-RAG: Combating LLM Hallucinations using Hypergraph-Driven Retrieval-Augmented Generation" by Yifan Feng, Hao Hu, Shihui Ying, Xingliang Hou, Shiquan Liu, Mingyuan Yang, Junchang Li, Shaoyi Du, Nanning Zheng, Han Hu, and Yue Gao.</t>
+          <t>跨平台屏幕捕获和录制工具，支持上传图像、视频、文本等
+【原文】SnapX is a free, open-source, cross-platform tool that lets you capture or record any area of your screen and instantly share it with a single keypress. Upload images, videos, text, and more to multiple supported destinations—all with ease. ShareX fork</t>
         </is>
       </c>
       <c r="E58" s="3" t="inlineStr">
         <is>
-          <t>RAG检索线</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G58" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H58" s="7" t="inlineStr">
@@ -6311,7 +6284,7 @@
       </c>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/iMoonLab/Hyper-RAG</t>
+          <t>https://github.com/SnapXL/SnapX</t>
         </is>
       </c>
       <c r="J58" s="3" t="inlineStr">
@@ -6320,16 +6293,16 @@
         </is>
       </c>
       <c r="K58" s="5" t="n">
-        <v>0.61</v>
+        <v>1.33</v>
       </c>
       <c r="L58" s="3" t="inlineStr">
         <is>
-          <t>Apache-2.0</t>
+          <t>GPL-3.0</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>C#</t>
         </is>
       </c>
       <c r="N58" s="3" t="inlineStr">
@@ -6344,21 +6317,21 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
-          <t>graph-rag, hypergraph, llms, rag</t>
+          <t>avalonia, csharp, dotnet, ftp, gif, imgur, linux, macos, ocr, productivity, screen-capture, screenshot</t>
         </is>
       </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-08-03</t>
         </is>
       </c>
       <c r="R58" s="3" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S58" s="3" t="n">
-        <v>525</v>
+        <v>771</v>
       </c>
       <c r="T58" s="3" t="n">
         <v>1</v>
@@ -6370,26 +6343,27 @@
       </c>
       <c r="V58" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="59" ht="150" customHeight="1">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>heathersherry/Knowledge-Graph-Tutorials-and-Papers</t>
+          <t>scambier/obsidian-omnisearch</t>
         </is>
       </c>
       <c r="B59" s="4" t="n">
-        <v>1071</v>
+        <v>2140</v>
       </c>
       <c r="C59" s="5" t="n">
-        <v>2.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D59" s="6" t="inlineStr">
         <is>
-          <t>提供关于知识图谱的教程和论文
-【原文】Insightful Tutorials and Papers about Knowledge Graphs</t>
+          <t>Obsidian的搜索引擎，支持OCR和PDF索引
+【原文】A search engine that "just works" for Obsidian. Supports OCR and PDF indexing.
+【依据】A search engine that 'just works' for Obsidian. Supports OCR and PDF indexing.</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
@@ -6399,12 +6373,12 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>数据集</t>
-        </is>
-      </c>
-      <c r="G59" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G59" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H59" s="7" t="inlineStr">
@@ -6414,7 +6388,7 @@
       </c>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/heathersherry/Knowledge-Graph-Tutorials-and-Papers</t>
+          <t>https://github.com/scambier/obsidian-omnisearch</t>
         </is>
       </c>
       <c r="J59" s="3" t="inlineStr">
@@ -6423,14 +6397,18 @@
         </is>
       </c>
       <c r="K59" s="5" t="n">
-        <v>0.39</v>
+        <v>1.32</v>
       </c>
       <c r="L59" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
-        </is>
-      </c>
-      <c r="M59" s="3" t="inlineStr"/>
+          <t>GPL-3.0</t>
+        </is>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>TypeScript</t>
+        </is>
+      </c>
       <c r="N59" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6443,21 +6421,21 @@
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
-          <t>awesome, awesome-kg, awesome-list, data-integration, entity-linking, information-extration, kg, kgqa, knowledge-base, knowledge-graph, knowledge-graph-completion, knowledge-graph-construction</t>
+          <t>minisearch, obsidian, obsidian-md, obsidian-plugin, ocr, pdf, search</t>
         </is>
       </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
-          <t>2019-03-10</t>
+          <t>2022-04-10</t>
         </is>
       </c>
       <c r="R59" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S59" s="3" t="n">
-        <v>2741</v>
+        <v>1617</v>
       </c>
       <c r="T59" s="3" t="n">
         <v>1</v>
@@ -6469,26 +6447,26 @@
       </c>
       <c r="V59" s="6" t="inlineStr">
         <is>
-          <t>topic:knowledge-graph stars:&gt;1000 pushed:&gt;2026-08-11</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="60" ht="150" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>CYBIRD-D/FREE-LLM-API-Provider</t>
+          <t>eikek/docspell</t>
         </is>
       </c>
       <c r="B60" s="4" t="n">
-        <v>101</v>
+        <v>2324</v>
       </c>
       <c r="C60" s="5" t="n">
-        <v>2.2</v>
+        <v>6.2</v>
       </c>
       <c r="D60" s="6" t="inlineStr">
         <is>
-          <t>提供免费LLM API资源列表，包括cn平台
-【原文】This is a list of free LLM provider resources accessible via API. Including some cn platform  免费llm api平台（包括cn平台）</t>
+          <t>文档管理系统，帮助组织来自扫描仪、电子邮件等来源的文档
+【原文】Assist in organizing your piles of documents, resulting from scanners, e-mails and other sources with miminal effort.</t>
         </is>
       </c>
       <c r="E60" s="3" t="inlineStr">
@@ -6498,12 +6476,12 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t>无许可·不可用</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G60" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H60" s="7" t="inlineStr">
@@ -6513,7 +6491,7 @@
       </c>
       <c r="I60" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/CYBIRD-D/FREE-LLM-API-Provider</t>
+          <t>https://github.com/eikek/docspell</t>
         </is>
       </c>
       <c r="J60" s="3" t="inlineStr">
@@ -6522,14 +6500,18 @@
         </is>
       </c>
       <c r="K60" s="5" t="n">
-        <v>0.32</v>
+        <v>0.89</v>
       </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M60" s="3" t="inlineStr"/>
+          <t>AGPL-3.0</t>
+        </is>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>Elm</t>
+        </is>
+      </c>
       <c r="N60" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6542,67 +6524,67 @@
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
-          <t>api, free, freetier, gemini-api, groq, llm, llm-interface, nvidia, ollama, openrouter</t>
+          <t>dms, docspell, document, document-management, document-management-system, edms, elm, nlp, ocr, pdf, personal-document-system, scala</t>
         </is>
       </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2019-07-16</t>
         </is>
       </c>
       <c r="R60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="S60" s="3" t="n">
-        <v>311</v>
+        <v>2616</v>
       </c>
       <c r="T60" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U60" s="3" t="inlineStr">
         <is>
-          <t>chinese</t>
+          <t>category</t>
         </is>
       </c>
       <c r="V60" s="6" t="inlineStr">
         <is>
-          <t>免费 API in:name,description stars:&gt;100 pushed:&gt;2026-06-12</t>
+          <t>topic:ocr stars:&gt;1000 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
     <row r="61" ht="150" customHeight="1">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>jw9730/tokengt</t>
+          <t>silexlabs/Silex</t>
         </is>
       </c>
       <c r="B61" s="4" t="n">
-        <v>351</v>
+        <v>2964</v>
       </c>
       <c r="C61" s="5" t="n">
-        <v>1.6</v>
+        <v>4.4</v>
       </c>
       <c r="D61" s="6" t="inlineStr">
         <is>
-          <t>提供基于PyTorch的Tokenized Graph Transformer模型
-【原文】[NeurIPS'22] Tokenized Graph Transformer (TokenGT), in PyTorch</t>
+          <t>在线工具，用于可视创建静态网站，支持动态数据
+【原文】Silex is an online tool for visually creating static sites with dynamic data. With the free/libre spirit of internet, together.</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>AI免费池</t>
+          <t>未归类</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
-        </is>
-      </c>
-      <c r="G61" s="3" t="inlineStr">
-        <is>
-          <t>宽松·可进闭源</t>
+          <t>未定</t>
+        </is>
+      </c>
+      <c r="G61" s="8" t="inlineStr">
+        <is>
+          <t>传染·只能读架构</t>
         </is>
       </c>
       <c r="H61" s="7" t="inlineStr">
@@ -6612,7 +6594,7 @@
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/jw9730/tokengt</t>
+          <t>https://github.com/silexlabs/Silex</t>
         </is>
       </c>
       <c r="J61" s="3" t="inlineStr">
@@ -6621,16 +6603,16 @@
         </is>
       </c>
       <c r="K61" s="5" t="n">
-        <v>0.23</v>
+        <v>0.63</v>
       </c>
       <c r="L61" s="3" t="inlineStr">
         <is>
-          <t>MIT</t>
+          <t>AGPL-3.0</t>
         </is>
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>TypeScript</t>
         </is>
       </c>
       <c r="N61" s="3" t="inlineStr">
@@ -6645,52 +6627,52 @@
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
-          <t>equivariance, gnn, graph, hypergraph, pytorch, self-attention, transformer</t>
+          <t>composable, design, grapesjs, jamstack, javascript, mcp, mcp-server, no-code, nocode, nodejs, saas, silex</t>
         </is>
       </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
-          <t>2022-06-29</t>
+          <t>2013-09-29</t>
         </is>
       </c>
       <c r="R61" s="3" t="inlineStr">
         <is>
-          <t>2023-04-11</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="S61" s="3" t="n">
-        <v>1534</v>
+        <v>4732</v>
       </c>
       <c r="T61" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U61" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>stock</t>
         </is>
       </c>
       <c r="V61" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>topic:mcp-server stars:&gt;1000 pushed:&gt;2026-08-14</t>
         </is>
       </c>
     </row>
     <row r="62" ht="150" customHeight="1">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>gzcsudo/Awesome-Hypergraph-Network</t>
+          <t>toki-plus/ai-highlight-clip</t>
         </is>
       </c>
       <c r="B62" s="4" t="n">
-        <v>336</v>
+        <v>101</v>
       </c>
       <c r="C62" s="5" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="D62" s="6" t="inlineStr">
         <is>
-          <t>提供超图学习、超图理论、超图数据集和超图工具的精选列表
-【原文】A curated list of Hypergraph Learning, Hypergraph Theory, Hypergraph Dataset and Hypergraph Tool.</t>
+          <t>自动剪辑长视频为短视频，并生成标题和评分
+【原文】AI驱动的长视频高光剪辑工具，自动将数小时的课程、访谈、直播回放转化为数十个爆款短视频。内置Whisper语音识别、大模型(LLM)智能评分与标题生成。 video-processing, ai-content-creation, nlp, openai-whisper, llm, automation, pyqt5, ffmpeg, bot.</t>
         </is>
       </c>
       <c r="E62" s="3" t="inlineStr">
@@ -6700,12 +6682,12 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>代码库</t>
+          <t>未定</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>无许可·不可用</t>
+          <t>宽松·可进闭源</t>
         </is>
       </c>
       <c r="H62" s="7" t="inlineStr">
@@ -6715,7 +6697,7 @@
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>https://github.com/gzcsudo/Awesome-Hypergraph-Network</t>
+          <t>https://github.com/toki-plus/ai-highlight-clip</t>
         </is>
       </c>
       <c r="J62" s="3" t="inlineStr">
@@ -6724,14 +6706,18 @@
         </is>
       </c>
       <c r="K62" s="5" t="n">
-        <v>0.2</v>
+        <v>0.36</v>
       </c>
       <c r="L62" s="3" t="inlineStr">
         <is>
-          <t>NONE</t>
-        </is>
-      </c>
-      <c r="M62" s="3" t="inlineStr"/>
+          <t>MIT</t>
+        </is>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>Python</t>
+        </is>
+      </c>
       <c r="N62" s="3" t="inlineStr">
         <is>
           <t>否</t>
@@ -6744,33 +6730,33 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
-          <t>awesome-list, graph, graph-neural-network, higher-order-graph, hypergraph, hypergraph-neural-network, hypergraph-theory</t>
+          <t>ai-content-creation, automation, content-creation, ffmpeg, llm, nlp, openai-whisper, pyqt5, python, short-video, video-editing, video-processing</t>
         </is>
       </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
-          <t>2022-01-12</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="R62" s="3" t="inlineStr">
         <is>
-          <t>2025-02-03</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S62" s="3" t="n">
-        <v>1702</v>
+        <v>277</v>
       </c>
       <c r="T62" s="3" t="n">
         <v>1</v>
       </c>
       <c r="U62" s="3" t="inlineStr">
         <is>
-          <t>category</t>
+          <t>chinese</t>
         </is>
       </c>
       <c r="V62" s="6" t="inlineStr">
         <is>
-          <t>topic:hypergraph stars:&gt;300</t>
+          <t>短视频 in:name,description stars:&gt;100 pushed:&gt;2026-06-15</t>
         </is>
       </c>
     </row>
